--- a/导出_按分组.xlsx
+++ b/导出_按分组.xlsx
@@ -493,11 +493,11 @@
         <v>650000</v>
       </c>
       <c r="D2" t="n">
-        <v>22943.26</v>
+        <v>23309.26</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -510,23 +510,23 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>301.4%</t>
+          <t>296.7%</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>+385.8%</t>
+          <t>+260.5%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>-46215.74000000001</v>
+        <v>-45849.74000000001</v>
       </c>
       <c r="K2" t="n">
-        <v>264654</v>
+        <v>265386</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-117.5%</t>
+          <t>-117.3%</t>
         </is>
       </c>
     </row>
@@ -545,92 +545,92 @@
         <v>1000000</v>
       </c>
       <c r="D3" t="n">
-        <v>74781.79999999999</v>
+        <v>77011.07999999999</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>7.7%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-75.6%</t>
+          <t>-75.0%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>43382.67000000001</v>
+        <v>44005.67000000001</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>58.0%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-75.6%</t>
+          <t>-75.7%</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>31399.12999999998</v>
+        <v>33005.40999999998</v>
       </c>
       <c r="K3" t="n">
-        <v>128067</v>
+        <v>127080</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-75.5%</t>
+          <t>-74.0%</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>课程7组</t>
+          <t>班主任</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>销售</t>
+          <t>班主任</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>650000</v>
+        <v>1700000</v>
       </c>
       <c r="D4" t="n">
-        <v>78852.16</v>
+        <v>317341</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>18.7%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-21.4%</t>
+          <t>+7.3%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>14960</v>
+        <v>53574</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>19.0%</t>
+          <t>16.9%</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-71.8%</t>
+          <t>-74.1%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>63892.16</v>
+        <v>263767</v>
       </c>
       <c r="K4" t="n">
-        <v>47293</v>
+        <v>89252</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>+35.1%</t>
+          <t>+195.5%</t>
         </is>
       </c>
     </row>
@@ -649,92 +649,92 @@
         <v>100000</v>
       </c>
       <c r="D5" t="n">
-        <v>14430</v>
+        <v>18785</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-63.8%</t>
+          <t>-54.6%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>18154</v>
+        <v>24874</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>125.8%</t>
+          <t>132.4%</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-14.8%</t>
+          <t>-8.6%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>-3724</v>
+        <v>-6089</v>
       </c>
       <c r="K5" t="n">
-        <v>18580</v>
+        <v>14180</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-120.0%</t>
+          <t>-142.9%</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>班主任</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>班主任</t>
+          <t>销售</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1700000</v>
+        <v>700000</v>
       </c>
       <c r="D6" t="n">
-        <v>270721</v>
+        <v>135037</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>15.9%</t>
+          <t>19.3%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>+315.2%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>60174</v>
+        <v>41016.17</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>30.4%</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-68.8%</t>
+          <t>+187.6%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>210547</v>
+        <v>94020.83</v>
       </c>
       <c r="K6" t="n">
-        <v>78303</v>
+        <v>18261</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>+168.9%</t>
+          <t>+414.9%</t>
         </is>
       </c>
     </row>
@@ -753,47 +753,47 @@
         <v>550000</v>
       </c>
       <c r="D7" t="n">
-        <v>91112</v>
+        <v>117462</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>16.6%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-49.9%</t>
+          <t>-35.5%</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>37261</v>
+        <v>37267</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>40.9%</t>
+          <t>31.7%</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>-51.8%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>53851</v>
+        <v>80195</v>
       </c>
       <c r="K7" t="n">
-        <v>143580</v>
+        <v>104931</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-62.5%</t>
+          <t>-23.6%</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>课程3组</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -802,50 +802,50 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>700000</v>
+        <v>800000</v>
       </c>
       <c r="D8" t="n">
-        <v>117284</v>
+        <v>197067.26</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>16.8%</t>
+          <t>24.6%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>+344.4%</t>
+          <t>-12.5%</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>15437.17</v>
+        <v>81119.89999999999</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>+37.8%</t>
+          <t>+58.7%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>101846.83</v>
+        <v>115947.36</v>
       </c>
       <c r="K8" t="n">
-        <v>15187</v>
+        <v>174012</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>+570.6%</t>
+          <t>-33.4%</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>课程3组</t>
+          <t>课程7组</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -854,43 +854,43 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>800000</v>
+        <v>650000</v>
       </c>
       <c r="D9" t="n">
-        <v>163371.36</v>
+        <v>169398.16</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>26.1%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-21.2%</t>
+          <t>+47.8%</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>30315.9</v>
+        <v>15007</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-40.4%</t>
+          <t>-76.2%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>133055.46</v>
+        <v>154391.16</v>
       </c>
       <c r="K9" t="n">
-        <v>156480</v>
+        <v>51525</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-15.0%</t>
+          <t>+199.6%</t>
         </is>
       </c>
     </row>
@@ -909,20 +909,20 @@
         <v>450000</v>
       </c>
       <c r="D10" t="n">
-        <v>35614</v>
+        <v>38614</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-71.9%</t>
+          <t>-69.8%</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -935,21 +935,21 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>35614</v>
+        <v>38605</v>
       </c>
       <c r="K10" t="n">
-        <v>94950</v>
+        <v>95946</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-62.5%</t>
+          <t>-59.8%</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>福州</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -958,50 +958,50 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>400000</v>
+        <v>800000</v>
       </c>
       <c r="D11" t="n">
-        <v>42095</v>
+        <v>97456.82000000001</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>+40.4%</t>
+          <t>+10.0%</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>16937</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>17.4%</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-100.0%</t>
+          <t>-75.1%</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>42095</v>
+        <v>80519.82000000001</v>
       </c>
       <c r="K11" t="n">
-        <v>1701</v>
+        <v>8091</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>+2374.7%</t>
+          <t>+895.2%</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>福州</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1010,43 +1010,43 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>800000</v>
+        <v>400000</v>
       </c>
       <c r="D12" t="n">
-        <v>96514.62</v>
+        <v>50693</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+9.4%</t>
+          <t>+20.7%</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>16937</v>
+        <v>0</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>17.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-73.8%</t>
+          <t>-100.0%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>79577.62</v>
+        <v>50693</v>
       </c>
       <c r="K12" t="n">
-        <v>11489</v>
+        <v>13701</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>+592.6%</t>
+          <t>+270.0%</t>
         </is>
       </c>
     </row>
@@ -1065,47 +1065,47 @@
         <v>850000</v>
       </c>
       <c r="D13" t="n">
-        <v>117915.95</v>
+        <v>123246.11</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-1.3%</t>
+          <t>-16.8%</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>143159</v>
+        <v>143178</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>121.4%</t>
+          <t>116.2%</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>+297.0%</t>
+          <t>+297.1%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>-25243.05</v>
+        <v>-19931.89</v>
       </c>
       <c r="K13" t="n">
-        <v>79235</v>
+        <v>106453</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-131.9%</t>
+          <t>-118.7%</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1114,50 +1114,50 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>450000</v>
+        <v>850000</v>
       </c>
       <c r="D14" t="n">
-        <v>86520</v>
+        <v>190041.17</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>19.2%</t>
+          <t>22.4%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+18.5%</t>
+          <t>+34.1%</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>299</v>
+        <v>25781</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-96.7%</t>
+          <t>-41.1%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>86221</v>
+        <v>164260.17</v>
       </c>
       <c r="K14" t="n">
-        <v>63964</v>
+        <v>95500.89999999999</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>+34.8%</t>
+          <t>+72.0%</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1166,50 +1166,50 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>850000</v>
+        <v>700000</v>
       </c>
       <c r="D15" t="n">
-        <v>180041.17</v>
+        <v>166547.94</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>21.2%</t>
+          <t>23.8%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+49.3%</t>
+          <t>+10.3%</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>25781</v>
+        <v>299</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-16.1%</t>
+          <t>-97.7%</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>154260.17</v>
+        <v>166248.94</v>
       </c>
       <c r="K15" t="n">
-        <v>87681</v>
+        <v>117131.59</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>+75.9%</t>
+          <t>+41.9%</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1218,43 +1218,43 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>700000</v>
+        <v>800000</v>
       </c>
       <c r="D16" t="n">
-        <v>164643</v>
+        <v>223068.01</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>27.9%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>+9.6%</t>
+          <t>+74.5%</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>299</v>
+        <v>14056</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>6.3%</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-97.7%</t>
+          <t>-91.4%</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>164344</v>
+        <v>209012.01</v>
       </c>
       <c r="K16" t="n">
-        <v>116533.59</v>
+        <v>-34785.69</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>+41.0%</t>
+          <t>-700.9%</t>
         </is>
       </c>
     </row>
@@ -1273,11 +1273,11 @@
         <v>2000000</v>
       </c>
       <c r="D17" t="n">
-        <v>502848.7</v>
+        <v>563265.7</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>25.1%</t>
+          <t>28.2%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1295,25 +1295,25 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-99.5%</t>
+          <t>-99.7%</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>502829.7</v>
+        <v>563246.7</v>
       </c>
       <c r="K17" t="n">
-        <v>37597</v>
+        <v>34597</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>+1237.4%</t>
+          <t>+1528.0%</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1322,43 +1322,43 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>800000</v>
+        <v>450000</v>
       </c>
       <c r="D18" t="n">
-        <v>214431.01</v>
+        <v>126918</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>26.8%</t>
+          <t>28.2%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>+230.3%</t>
+          <t>+73.9%</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>4056</v>
+        <v>299</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-94.0%</t>
+          <t>-98.1%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>210375.01</v>
+        <v>126619</v>
       </c>
       <c r="K18" t="n">
-        <v>-2740.690000000002</v>
+        <v>57364</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-7776.0%</t>
+          <t>+120.7%</t>
         </is>
       </c>
     </row>
@@ -1377,40 +1377,40 @@
         <v>700000</v>
       </c>
       <c r="D19" t="n">
-        <v>199696.99</v>
+        <v>214684.99</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>28.5%</t>
+          <t>30.7%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>+19.2%</t>
+          <t>+14.2%</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>1800</v>
+        <v>8800</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-94.0%</t>
+          <t>-72.3%</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>197896.99</v>
+        <v>205884.99</v>
       </c>
       <c r="K19" t="n">
-        <v>137516.41</v>
+        <v>156133.41</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>+43.9%</t>
+          <t>+31.9%</t>
         </is>
       </c>
     </row>
@@ -1429,16 +1429,16 @@
         <v>260000</v>
       </c>
       <c r="D20" t="n">
-        <v>98788</v>
+        <v>110788</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>38.0%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>+522.4%</t>
+          <t>+598.0%</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>15.5%</t>
+          <t>13.8%</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1455,14 +1455,14 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>83511</v>
+        <v>95511</v>
       </c>
       <c r="K20" t="n">
         <v>15815</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>+428.0%</t>
+          <t>+503.9%</t>
         </is>
       </c>
     </row>

--- a/导出_按分组.xlsx
+++ b/导出_按分组.xlsx
@@ -493,7 +493,7 @@
         <v>650000</v>
       </c>
       <c r="D2" t="n">
-        <v>23309.26</v>
+        <v>23347.26</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -506,16 +506,16 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>69159</v>
+        <v>69197</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>296.7%</t>
+          <t>296.4%</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>+260.5%</t>
+          <t>+260.3%</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -545,99 +545,99 @@
         <v>1000000</v>
       </c>
       <c r="D3" t="n">
-        <v>77011.07999999999</v>
+        <v>79688.08</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>7.7%</t>
+          <t>8.0%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-75.0%</t>
+          <t>-76.7%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>44005.67000000001</v>
+        <v>73989.67</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>92.8%</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-75.7%</t>
+          <t>-59.1%</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>33005.40999999998</v>
+        <v>5698.410000000003</v>
       </c>
       <c r="K3" t="n">
-        <v>127080</v>
+        <v>160998</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-74.0%</t>
+          <t>-96.5%</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>班主任</t>
+          <t>课程2组</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>班主任</t>
+          <t>销售</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1700000</v>
+        <v>100000</v>
       </c>
       <c r="D4" t="n">
-        <v>317341</v>
+        <v>19175</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>19.2%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>+7.3%</t>
+          <t>-54.3%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>53574</v>
+        <v>24912</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>16.9%</t>
+          <t>129.9%</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-74.1%</t>
+          <t>-8.6%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>263767</v>
+        <v>-5737</v>
       </c>
       <c r="K4" t="n">
-        <v>89252</v>
+        <v>14721</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>+195.5%</t>
+          <t>-139.0%</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>课程2组</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -646,95 +646,95 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>100000</v>
+        <v>700000</v>
       </c>
       <c r="D5" t="n">
-        <v>18785</v>
+        <v>143565</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>20.5%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-54.6%</t>
+          <t>+318.7%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>24874</v>
+        <v>41506.07</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>132.4%</t>
+          <t>28.9%</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-8.6%</t>
+          <t>+189.9%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>-6089</v>
+        <v>102058.93</v>
       </c>
       <c r="K5" t="n">
-        <v>14180</v>
+        <v>19971</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-142.9%</t>
+          <t>+411.0%</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>班主任</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>销售</t>
+          <t>班主任</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>700000</v>
+        <v>1700000</v>
       </c>
       <c r="D6" t="n">
-        <v>135037</v>
+        <v>366721</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>19.3%</t>
+          <t>21.6%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+315.2%</t>
+          <t>+23.9%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>41016.17</v>
+        <v>53574</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>30.4%</t>
+          <t>14.6%</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>+187.6%</t>
+          <t>-74.1%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>94020.83</v>
+        <v>313147</v>
       </c>
       <c r="K6" t="n">
-        <v>18261</v>
+        <v>89252</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>+414.9%</t>
+          <t>+250.9%</t>
         </is>
       </c>
     </row>
@@ -753,47 +753,47 @@
         <v>550000</v>
       </c>
       <c r="D7" t="n">
-        <v>117462</v>
+        <v>132509</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-35.5%</t>
+          <t>-27.5%</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>37267</v>
+        <v>37324</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>31.7%</t>
+          <t>28.2%</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-51.8%</t>
+          <t>-51.7%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>80195</v>
+        <v>95185</v>
       </c>
       <c r="K7" t="n">
-        <v>104931</v>
+        <v>105404</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-23.6%</t>
+          <t>-9.7%</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>课程3组</t>
+          <t>课程7组</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -802,50 +802,50 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>800000</v>
+        <v>650000</v>
       </c>
       <c r="D8" t="n">
-        <v>197067.26</v>
+        <v>174229.16</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>24.6%</t>
+          <t>26.8%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-12.5%</t>
+          <t>+50.7%</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>81119.89999999999</v>
+        <v>15136</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>8.7%</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>+58.7%</t>
+          <t>-76.0%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>115947.36</v>
+        <v>159093.16</v>
       </c>
       <c r="K8" t="n">
-        <v>174012</v>
+        <v>52449</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-33.4%</t>
+          <t>+203.3%</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>课程7组</t>
+          <t>课程3组</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -854,43 +854,43 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>650000</v>
+        <v>800000</v>
       </c>
       <c r="D9" t="n">
-        <v>169398.16</v>
+        <v>220255.26</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>26.1%</t>
+          <t>27.5%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>+47.8%</t>
+          <t>-7.2%</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>15007</v>
+        <v>91493.89999999999</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>41.5%</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-76.2%</t>
+          <t>+73.9%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>154391.16</v>
+        <v>128761.36</v>
       </c>
       <c r="K9" t="n">
-        <v>51525</v>
+        <v>184658</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>+199.6%</t>
+          <t>-30.3%</t>
         </is>
       </c>
     </row>
@@ -909,16 +909,16 @@
         <v>450000</v>
       </c>
       <c r="D10" t="n">
-        <v>38614</v>
+        <v>52313</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-69.8%</t>
+          <t>-62.0%</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -935,14 +935,14 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>38605</v>
+        <v>52304</v>
       </c>
       <c r="K10" t="n">
-        <v>95946</v>
+        <v>105946</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-59.8%</t>
+          <t>-50.6%</t>
         </is>
       </c>
     </row>
@@ -961,16 +961,16 @@
         <v>800000</v>
       </c>
       <c r="D11" t="n">
-        <v>97456.82000000001</v>
+        <v>110005.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>13.8%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>+10.0%</t>
+          <t>+4.0%</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -978,7 +978,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>17.4%</t>
+          <t>15.4%</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -987,14 +987,14 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>80519.82000000001</v>
+        <v>93068.3</v>
       </c>
       <c r="K11" t="n">
-        <v>8091</v>
+        <v>22491</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>+895.2%</t>
+          <t>+313.8%</t>
         </is>
       </c>
     </row>
@@ -1013,40 +1013,40 @@
         <v>400000</v>
       </c>
       <c r="D12" t="n">
-        <v>50693</v>
+        <v>57489</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+20.7%</t>
+          <t>+36.9%</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>10200</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>17.7%</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-100.0%</t>
+          <t>-63.9%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>50693</v>
+        <v>47289</v>
       </c>
       <c r="K12" t="n">
         <v>13701</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>+270.0%</t>
+          <t>+245.1%</t>
         </is>
       </c>
     </row>
@@ -1065,16 +1065,16 @@
         <v>850000</v>
       </c>
       <c r="D13" t="n">
-        <v>123246.11</v>
+        <v>130765.11</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>15.4%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-16.8%</t>
+          <t>-17.9%</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1082,7 +1082,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>116.2%</t>
+          <t>109.5%</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1091,14 +1091,14 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>-19931.89</v>
+        <v>-12412.89</v>
       </c>
       <c r="K13" t="n">
-        <v>106453</v>
+        <v>117451</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-118.7%</t>
+          <t>-110.6%</t>
         </is>
       </c>
     </row>
@@ -1117,40 +1117,40 @@
         <v>850000</v>
       </c>
       <c r="D14" t="n">
-        <v>190041.17</v>
+        <v>216221.17</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>22.4%</t>
+          <t>25.4%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+34.1%</t>
+          <t>+41.2%</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>25781</v>
+        <v>30761</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>14.2%</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-41.1%</t>
+          <t>-29.7%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>164260.17</v>
+        <v>185460.17</v>
       </c>
       <c r="K14" t="n">
-        <v>95500.89999999999</v>
+        <v>107100.9</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>+72.0%</t>
+          <t>+73.2%</t>
         </is>
       </c>
     </row>
@@ -1169,16 +1169,16 @@
         <v>700000</v>
       </c>
       <c r="D15" t="n">
-        <v>166547.94</v>
+        <v>185595.94</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>23.8%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+10.3%</t>
+          <t>+24.9%</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -1195,21 +1195,21 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>166248.94</v>
+        <v>185296.94</v>
       </c>
       <c r="K15" t="n">
         <v>117131.59</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>+41.9%</t>
+          <t>+58.2%</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1218,43 +1218,43 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>800000</v>
+        <v>450000</v>
       </c>
       <c r="D16" t="n">
-        <v>223068.01</v>
+        <v>134314</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>27.9%</t>
+          <t>29.8%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>+74.5%</t>
+          <t>+34.0%</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>14056</v>
+        <v>299</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>6.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-91.4%</t>
+          <t>-98.1%</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>209012.01</v>
+        <v>134015</v>
       </c>
       <c r="K16" t="n">
-        <v>-34785.69</v>
+        <v>84601</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-700.9%</t>
+          <t>+58.4%</t>
         </is>
       </c>
     </row>
@@ -1273,16 +1273,16 @@
         <v>2000000</v>
       </c>
       <c r="D17" t="n">
-        <v>563265.7</v>
+        <v>603723.7</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>28.2%</t>
+          <t>30.2%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>+10.5%</t>
+          <t>+9.5%</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -1299,21 +1299,21 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>563246.7</v>
+        <v>603704.7</v>
       </c>
       <c r="K17" t="n">
-        <v>34597</v>
+        <v>34995</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>+1528.0%</t>
+          <t>+1625.1%</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1322,43 +1322,43 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>450000</v>
+        <v>800000</v>
       </c>
       <c r="D18" t="n">
-        <v>126918</v>
+        <v>270755.01</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>28.2%</t>
+          <t>33.8%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>+73.9%</t>
+          <t>+52.3%</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>299</v>
+        <v>14056</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>5.2%</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-98.1%</t>
+          <t>-91.7%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>126619</v>
+        <v>256699.01</v>
       </c>
       <c r="K18" t="n">
-        <v>57364</v>
+        <v>7700.309999999998</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>+120.7%</t>
+          <t>+3233.6%</t>
         </is>
       </c>
     </row>
@@ -1377,40 +1377,40 @@
         <v>700000</v>
       </c>
       <c r="D19" t="n">
-        <v>214684.99</v>
+        <v>258878.99</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>30.7%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>+14.2%</t>
+          <t>+32.4%</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>8800</v>
+        <v>20800</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>8.0%</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-72.3%</t>
+          <t>-19.3%</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>205884.99</v>
+        <v>238078.99</v>
       </c>
       <c r="K19" t="n">
-        <v>156133.41</v>
+        <v>169729.41</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>+31.9%</t>
+          <t>+40.3%</t>
         </is>
       </c>
     </row>
@@ -1438,7 +1438,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>+598.0%</t>
+          <t>+597.2%</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -1458,11 +1458,11 @@
         <v>95511</v>
       </c>
       <c r="K20" t="n">
-        <v>15815</v>
+        <v>15834</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>+503.9%</t>
+          <t>+503.2%</t>
         </is>
       </c>
     </row>

--- a/导出_按分组.xlsx
+++ b/导出_按分组.xlsx
@@ -481,7 +481,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>课程4组</t>
+          <t>课程1组</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -490,50 +490,50 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>650000</v>
+        <v>1000000</v>
       </c>
       <c r="D2" t="n">
-        <v>23347.26</v>
+        <v>109898.18</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-91.8%</t>
+          <t>-76.7%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>69197</v>
+        <v>74071.67</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>296.4%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>+260.3%</t>
+          <t>-59.1%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>-45849.74000000001</v>
+        <v>35826.51</v>
       </c>
       <c r="K2" t="n">
-        <v>265386</v>
+        <v>160998</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-117.3%</t>
+          <t>-96.5%</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>课程1组</t>
+          <t>课程2组</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -542,50 +542,50 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1000000</v>
+        <v>100000</v>
       </c>
       <c r="D3" t="n">
-        <v>79688.08</v>
+        <v>19573</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>8.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-76.7%</t>
+          <t>-54.3%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>73989.67</v>
+        <v>24918</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>92.8%</t>
+          <t>127.3%</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-59.1%</t>
+          <t>-8.6%</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>5698.410000000003</v>
+        <v>-5345</v>
       </c>
       <c r="K3" t="n">
-        <v>160998</v>
+        <v>14721</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-96.5%</t>
+          <t>-139.0%</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>课程2组</t>
+          <t>课程3组</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -594,50 +594,50 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>100000</v>
+        <v>800000</v>
       </c>
       <c r="D4" t="n">
-        <v>19175</v>
+        <v>219748.16</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>19.2%</t>
+          <t>27.0%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-54.3%</t>
+          <t>-7.2%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>24912</v>
+        <v>96943.89999999999</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>129.9%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-8.6%</t>
+          <t>+73.9%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>-5737</v>
+        <v>122804.26</v>
       </c>
       <c r="K4" t="n">
-        <v>14721</v>
+        <v>184658</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-139.0%</t>
+          <t>-30.3%</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>课程4组</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -646,95 +646,95 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>700000</v>
+        <v>650000</v>
       </c>
       <c r="D5" t="n">
-        <v>143565</v>
+        <v>192385.16</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>20.5%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>+318.7%</t>
+          <t>-91.8%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>41506.07</v>
+        <v>69197</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>28.9%</t>
+          <t>36.0%</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>+189.9%</t>
+          <t>+260.3%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>102058.93</v>
+        <v>123188.16</v>
       </c>
       <c r="K5" t="n">
-        <v>19971</v>
+        <v>265386</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>+411.0%</t>
+          <t>-117.3%</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>班主任</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>班主任</t>
+          <t>销售</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1700000</v>
+        <v>700000</v>
       </c>
       <c r="D6" t="n">
-        <v>366721</v>
+        <v>147918.99</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>21.0%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+23.9%</t>
+          <t>+318.7%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>53574</v>
+        <v>46623.07</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-74.1%</t>
+          <t>+189.9%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>313147</v>
+        <v>101295.92</v>
       </c>
       <c r="K6" t="n">
-        <v>89252</v>
+        <v>19971</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>+250.9%</t>
+          <t>+411.0%</t>
         </is>
       </c>
     </row>
@@ -753,11 +753,11 @@
         <v>550000</v>
       </c>
       <c r="D7" t="n">
-        <v>132509</v>
+        <v>147817</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>27.0%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -766,11 +766,11 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>37324</v>
+        <v>38333</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>28.2%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -779,7 +779,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>95185</v>
+        <v>109484</v>
       </c>
       <c r="K7" t="n">
         <v>105404</v>
@@ -805,11 +805,11 @@
         <v>650000</v>
       </c>
       <c r="D8" t="n">
-        <v>174229.16</v>
+        <v>183271.96</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>26.8%</t>
+          <t>28.0%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -818,11 +818,11 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>15136</v>
+        <v>19192</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>8.7%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>159093.16</v>
+        <v>164079.96</v>
       </c>
       <c r="K8" t="n">
         <v>52449</v>
@@ -845,59 +845,59 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>课程3组</t>
+          <t>班主任</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>销售</t>
+          <t>班主任</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>800000</v>
+        <v>1700000</v>
       </c>
       <c r="D9" t="n">
-        <v>220255.26</v>
+        <v>419321</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-7.2%</t>
+          <t>+23.9%</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>91493.89999999999</v>
+        <v>53574</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>41.5%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>+73.9%</t>
+          <t>-74.1%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>128761.36</v>
+        <v>365747</v>
       </c>
       <c r="K9" t="n">
-        <v>184658</v>
+        <v>89252</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-30.3%</t>
+          <t>+250.9%</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>昆明</t>
+          <t>普陀</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -906,23 +906,23 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>450000</v>
+        <v>2000000</v>
       </c>
       <c r="D10" t="n">
-        <v>52313</v>
+        <v>800599.34</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-62.0%</t>
+          <t>+9.5%</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -931,25 +931,25 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-100.0%</t>
+          <t>-99.7%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>52304</v>
+        <v>800599.34</v>
       </c>
       <c r="K10" t="n">
-        <v>105946</v>
+        <v>34995</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-50.6%</t>
+          <t>+1625.1%</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>昆明</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -958,50 +958,50 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>800000</v>
+        <v>450000</v>
       </c>
       <c r="D11" t="n">
-        <v>110005.3</v>
+        <v>77711</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>17.0%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>+4.0%</t>
+          <t>-62.0%</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>16937</v>
+        <v>24809</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>31.9%</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-75.1%</t>
+          <t>-100.0%</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>93068.3</v>
+        <v>52902</v>
       </c>
       <c r="K11" t="n">
-        <v>22491</v>
+        <v>105946</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>+313.8%</t>
+          <t>-50.6%</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>福州</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1010,50 +1010,50 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>400000</v>
+        <v>450000</v>
       </c>
       <c r="D12" t="n">
-        <v>57489</v>
+        <v>138916</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>31.0%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+36.9%</t>
+          <t>+34.0%</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>10200</v>
+        <v>1979</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>17.7%</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-63.9%</t>
+          <t>-98.1%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>47289</v>
+        <v>136937</v>
       </c>
       <c r="K12" t="n">
-        <v>13701</v>
+        <v>84601</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>+245.1%</t>
+          <t>+58.4%</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1065,47 +1065,47 @@
         <v>850000</v>
       </c>
       <c r="D13" t="n">
-        <v>130765.11</v>
+        <v>218307.17</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>26.0%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-17.9%</t>
+          <t>+41.2%</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>143178</v>
+        <v>36761</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>109.5%</t>
+          <t>16.8%</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>+297.1%</t>
+          <t>-29.7%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>-12412.89</v>
+        <v>181546.17</v>
       </c>
       <c r="K13" t="n">
-        <v>117451</v>
+        <v>107100.9</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-110.6%</t>
+          <t>+73.2%</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1114,50 +1114,50 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>850000</v>
+        <v>800000</v>
       </c>
       <c r="D14" t="n">
-        <v>216221.17</v>
+        <v>110973.4</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>25.4%</t>
+          <t>14.0%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+41.2%</t>
+          <t>+4.0%</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>30761</v>
+        <v>17549</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>15.8%</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-29.7%</t>
+          <t>-75.1%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>185460.17</v>
+        <v>93424.39999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>107100.9</v>
+        <v>22491</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>+73.2%</t>
+          <t>+313.8%</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>珠海</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1166,50 +1166,50 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>700000</v>
+        <v>260000</v>
       </c>
       <c r="D15" t="n">
-        <v>185595.94</v>
+        <v>128468</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>49.0%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+24.9%</t>
+          <t>+597.2%</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>299</v>
+        <v>15277</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-97.7%</t>
+          <t>+26701.8%</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>185296.94</v>
+        <v>113191</v>
       </c>
       <c r="K15" t="n">
-        <v>117131.59</v>
+        <v>15834</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>+58.2%</t>
+          <t>+503.2%</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>福州</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1218,50 +1218,50 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>450000</v>
+        <v>400000</v>
       </c>
       <c r="D16" t="n">
-        <v>134314</v>
+        <v>69489</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>29.8%</t>
+          <t>17.0%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>+34.0%</t>
+          <t>+36.9%</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>299</v>
+        <v>10200</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>14.7%</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-98.1%</t>
+          <t>-63.9%</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>134015</v>
+        <v>59289</v>
       </c>
       <c r="K16" t="n">
-        <v>84601</v>
+        <v>13701</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>+58.4%</t>
+          <t>+245.1%</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>普陀</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1270,43 +1270,43 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2000000</v>
+        <v>700000</v>
       </c>
       <c r="D17" t="n">
-        <v>603723.7</v>
+        <v>196791.94</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>30.2%</t>
+          <t>28.0%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>+9.5%</t>
+          <t>+24.9%</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>19</v>
+        <v>19466</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-99.7%</t>
+          <t>-97.7%</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>603704.7</v>
+        <v>177325.94</v>
       </c>
       <c r="K17" t="n">
-        <v>34995</v>
+        <v>117131.59</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>+1625.1%</t>
+          <t>+58.2%</t>
         </is>
       </c>
     </row>
@@ -1325,11 +1325,11 @@
         <v>800000</v>
       </c>
       <c r="D18" t="n">
-        <v>270755.01</v>
+        <v>283570.01</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>33.8%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1338,11 +1338,11 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>14056</v>
+        <v>20656</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>5.2%</t>
+          <t>7.3%</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1351,7 +1351,7 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>256699.01</v>
+        <v>262914.01</v>
       </c>
       <c r="K18" t="n">
         <v>7700.309999999998</v>
@@ -1365,7 +1365,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1374,50 +1374,50 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>700000</v>
+        <v>850000</v>
       </c>
       <c r="D19" t="n">
-        <v>258878.99</v>
+        <v>131104.11</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>15.0%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>+32.4%</t>
+          <t>-17.9%</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>20800</v>
+        <v>143498</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>8.0%</t>
+          <t>109.5%</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-19.3%</t>
+          <t>+297.1%</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>238078.99</v>
+        <v>-12393.89</v>
       </c>
       <c r="K19" t="n">
-        <v>169729.41</v>
+        <v>117451</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>+40.3%</t>
+          <t>-110.6%</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>珠海</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1426,43 +1426,43 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>260000</v>
+        <v>700000</v>
       </c>
       <c r="D20" t="n">
-        <v>110788</v>
+        <v>261354.99</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>+597.2%</t>
+          <t>+32.4%</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>15277</v>
+        <v>20800</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>8.0%</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>+26701.8%</t>
+          <t>-19.3%</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>95511</v>
+        <v>240554.99</v>
       </c>
       <c r="K20" t="n">
-        <v>15834</v>
+        <v>169729.41</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>+503.2%</t>
+          <t>+40.3%</t>
         </is>
       </c>
     </row>

--- a/导出_按分组.xlsx
+++ b/导出_按分组.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L20"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,37 +444,17 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>完成环比</t>
+          <t>本月退费</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>本月退费</t>
+          <t>退费率</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>退费率</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>退费环比</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
           <t>本月净流水</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>上月净流水</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>净流水环比</t>
         </is>
       </c>
     </row>
@@ -500,34 +480,16 @@
           <t>11.0%</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>-76.7%</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
+      <c r="F2" t="n">
         <v>74071.67</v>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>67.4%</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>-59.1%</t>
-        </is>
-      </c>
-      <c r="J2" t="n">
-        <v>35826.51</v>
-      </c>
-      <c r="K2" t="n">
-        <v>160998</v>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>-96.5%</t>
-        </is>
+      <c r="H2" t="n">
+        <v>35826.50999999999</v>
       </c>
     </row>
     <row r="3">
@@ -549,37 +511,19 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>20.0%</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>-54.3%</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
+          <t>19.6%</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
         <v>24918</v>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>127.3%</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>-8.6%</t>
-        </is>
-      </c>
-      <c r="J3" t="n">
+      <c r="H3" t="n">
         <v>-5345</v>
-      </c>
-      <c r="K3" t="n">
-        <v>14721</v>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>-139.0%</t>
-        </is>
       </c>
     </row>
     <row r="4">
@@ -601,37 +545,19 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>27.0%</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>-7.2%</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
+          <t>27.5%</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
         <v>96943.89999999999</v>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>44.1%</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>+73.9%</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
+      <c r="H4" t="n">
         <v>122804.26</v>
-      </c>
-      <c r="K4" t="n">
-        <v>184658</v>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>-30.3%</t>
-        </is>
       </c>
     </row>
     <row r="5">
@@ -653,37 +579,19 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>30.0%</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>-91.8%</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
+          <t>29.6%</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
         <v>69197</v>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>36.0%</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>+260.3%</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
+      <c r="H5" t="n">
         <v>123188.16</v>
-      </c>
-      <c r="K5" t="n">
-        <v>265386</v>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>-117.3%</t>
-        </is>
       </c>
     </row>
     <row r="6">
@@ -705,37 +613,19 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>21.0%</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>+318.7%</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
+          <t>21.1%</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
         <v>46623.07</v>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>31.5%</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>+189.9%</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
+      <c r="H6" t="n">
         <v>101295.92</v>
-      </c>
-      <c r="K6" t="n">
-        <v>19971</v>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>+411.0%</t>
-        </is>
       </c>
     </row>
     <row r="7">
@@ -757,37 +647,19 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>27.0%</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>-27.5%</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
+          <t>26.9%</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
         <v>38333</v>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>25.9%</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>-51.7%</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
+      <c r="H7" t="n">
         <v>109484</v>
-      </c>
-      <c r="K7" t="n">
-        <v>105404</v>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>-9.7%</t>
-        </is>
       </c>
     </row>
     <row r="8">
@@ -809,37 +681,19 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>28.0%</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>+50.7%</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
+          <t>28.2%</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
         <v>19192</v>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>10.5%</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>-76.0%</t>
-        </is>
-      </c>
-      <c r="J8" t="n">
+      <c r="H8" t="n">
         <v>164079.96</v>
-      </c>
-      <c r="K8" t="n">
-        <v>52449</v>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>+203.3%</t>
-        </is>
       </c>
     </row>
     <row r="9">
@@ -861,37 +715,19 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>+23.9%</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
+          <t>24.7%</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
         <v>53574</v>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>12.8%</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>-74.1%</t>
-        </is>
-      </c>
-      <c r="J9" t="n">
+      <c r="H9" t="n">
         <v>365747</v>
-      </c>
-      <c r="K9" t="n">
-        <v>89252</v>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>+250.9%</t>
-        </is>
       </c>
     </row>
     <row r="10">
@@ -909,41 +745,23 @@
         <v>2000000</v>
       </c>
       <c r="D10" t="n">
-        <v>800599.34</v>
+        <v>800599.3400000001</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>40.0%</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>+9.5%</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
+      <c r="F10" t="n">
         <v>0</v>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>-99.7%</t>
-        </is>
-      </c>
-      <c r="J10" t="n">
-        <v>800599.34</v>
-      </c>
-      <c r="K10" t="n">
-        <v>34995</v>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>+1625.1%</t>
-        </is>
+      <c r="H10" t="n">
+        <v>800599.3400000001</v>
       </c>
     </row>
     <row r="11">
@@ -965,37 +783,19 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>17.0%</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>-62.0%</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
+          <t>17.3%</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
         <v>24809</v>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>31.9%</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>-100.0%</t>
-        </is>
-      </c>
-      <c r="J11" t="n">
+      <c r="H11" t="n">
         <v>52902</v>
-      </c>
-      <c r="K11" t="n">
-        <v>105946</v>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>-50.6%</t>
-        </is>
       </c>
     </row>
     <row r="12">
@@ -1017,37 +817,19 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>31.0%</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>+34.0%</t>
-        </is>
-      </c>
-      <c r="G12" t="n">
+          <t>30.9%</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
         <v>1979</v>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>1.4%</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>-98.1%</t>
-        </is>
-      </c>
-      <c r="J12" t="n">
+      <c r="H12" t="n">
         <v>136937</v>
-      </c>
-      <c r="K12" t="n">
-        <v>84601</v>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>+58.4%</t>
-        </is>
       </c>
     </row>
     <row r="13">
@@ -1069,37 +851,19 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>26.0%</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>+41.2%</t>
-        </is>
-      </c>
-      <c r="G13" t="n">
+          <t>25.7%</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
         <v>36761</v>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>16.8%</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>-29.7%</t>
-        </is>
-      </c>
-      <c r="J13" t="n">
+      <c r="H13" t="n">
         <v>181546.17</v>
-      </c>
-      <c r="K13" t="n">
-        <v>107100.9</v>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>+73.2%</t>
-        </is>
       </c>
     </row>
     <row r="14">
@@ -1121,37 +885,19 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>14.0%</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>+4.0%</t>
-        </is>
-      </c>
-      <c r="G14" t="n">
+          <t>13.9%</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
         <v>17549</v>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>15.8%</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>-75.1%</t>
-        </is>
-      </c>
-      <c r="J14" t="n">
+      <c r="H14" t="n">
         <v>93424.39999999999</v>
-      </c>
-      <c r="K14" t="n">
-        <v>22491</v>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>+313.8%</t>
-        </is>
       </c>
     </row>
     <row r="15">
@@ -1173,37 +919,19 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>49.0%</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>+597.2%</t>
-        </is>
-      </c>
-      <c r="G15" t="n">
+          <t>49.4%</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
         <v>15277</v>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>11.9%</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>+26701.8%</t>
-        </is>
-      </c>
-      <c r="J15" t="n">
+      <c r="H15" t="n">
         <v>113191</v>
-      </c>
-      <c r="K15" t="n">
-        <v>15834</v>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>+503.2%</t>
-        </is>
       </c>
     </row>
     <row r="16">
@@ -1225,37 +953,19 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>17.0%</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>+36.9%</t>
-        </is>
-      </c>
-      <c r="G16" t="n">
+          <t>17.4%</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
         <v>10200</v>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>14.7%</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>-63.9%</t>
-        </is>
-      </c>
-      <c r="J16" t="n">
+      <c r="H16" t="n">
         <v>59289</v>
-      </c>
-      <c r="K16" t="n">
-        <v>13701</v>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>+245.1%</t>
-        </is>
       </c>
     </row>
     <row r="17">
@@ -1277,37 +987,19 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>28.0%</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>+24.9%</t>
-        </is>
-      </c>
-      <c r="G17" t="n">
+          <t>28.1%</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
         <v>19466</v>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>9.9%</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>-97.7%</t>
-        </is>
-      </c>
-      <c r="J17" t="n">
+      <c r="H17" t="n">
         <v>177325.94</v>
-      </c>
-      <c r="K17" t="n">
-        <v>117131.59</v>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>+58.2%</t>
-        </is>
       </c>
     </row>
     <row r="18">
@@ -1329,37 +1021,19 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>35.0%</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>+52.3%</t>
-        </is>
-      </c>
-      <c r="G18" t="n">
+          <t>35.4%</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
         <v>20656</v>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>7.3%</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>-91.7%</t>
-        </is>
-      </c>
-      <c r="J18" t="n">
+      <c r="H18" t="n">
         <v>262914.01</v>
-      </c>
-      <c r="K18" t="n">
-        <v>7700.309999999998</v>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>+3233.6%</t>
-        </is>
       </c>
     </row>
     <row r="19">
@@ -1381,37 +1055,19 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>15.0%</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>-17.9%</t>
-        </is>
-      </c>
-      <c r="G19" t="n">
+          <t>15.4%</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
         <v>143498</v>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>109.5%</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>+297.1%</t>
-        </is>
-      </c>
-      <c r="J19" t="n">
-        <v>-12393.89</v>
-      </c>
-      <c r="K19" t="n">
-        <v>117451</v>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>-110.6%</t>
-        </is>
+      <c r="H19" t="n">
+        <v>-12393.89000000001</v>
       </c>
     </row>
     <row r="20">
@@ -1433,37 +1089,19 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>37.0%</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>+32.4%</t>
-        </is>
-      </c>
-      <c r="G20" t="n">
+          <t>37.3%</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
         <v>20800</v>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>8.0%</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>-19.3%</t>
-        </is>
-      </c>
-      <c r="J20" t="n">
+      <c r="H20" t="n">
         <v>240554.99</v>
-      </c>
-      <c r="K20" t="n">
-        <v>169729.41</v>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>+40.3%</t>
-        </is>
       </c>
     </row>
   </sheetData>

--- a/导出_按分组.xlsx
+++ b/导出_按分组.xlsx
@@ -473,23 +473,23 @@
         <v>1000000</v>
       </c>
       <c r="D2" t="n">
-        <v>109898.18</v>
+        <v>138402.18</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>13.8%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>74071.67</v>
+        <v>136369.67</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>98.5%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>35826.50999999999</v>
+        <v>2032.50999999998</v>
       </c>
     </row>
     <row r="3">
@@ -507,23 +507,23 @@
         <v>100000</v>
       </c>
       <c r="D3" t="n">
-        <v>19573</v>
+        <v>20291.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>19.6%</t>
+          <t>20.3%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>24918</v>
+        <v>25136</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>127.3%</t>
+          <t>123.9%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>-5345</v>
+        <v>-4844.799999999999</v>
       </c>
     </row>
     <row r="4">
@@ -541,23 +541,23 @@
         <v>800000</v>
       </c>
       <c r="D4" t="n">
-        <v>219748.16</v>
+        <v>249236.16</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>96943.89999999999</v>
+        <v>110359.9</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>44.3%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>122804.26</v>
+        <v>138876.26</v>
       </c>
     </row>
     <row r="5">
@@ -575,23 +575,23 @@
         <v>650000</v>
       </c>
       <c r="D5" t="n">
-        <v>192385.16</v>
+        <v>236399.16</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>69197</v>
+        <v>69235</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>36.0%</t>
+          <t>29.3%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>123188.16</v>
+        <v>167164.16</v>
       </c>
     </row>
     <row r="6">
@@ -609,23 +609,23 @@
         <v>700000</v>
       </c>
       <c r="D6" t="n">
-        <v>147918.99</v>
+        <v>176308.99</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>21.1%</t>
+          <t>25.2%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>46623.07</v>
+        <v>46713.07</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>101295.92</v>
+        <v>129595.92</v>
       </c>
     </row>
     <row r="7">
@@ -643,11 +643,11 @@
         <v>550000</v>
       </c>
       <c r="D7" t="n">
-        <v>147817</v>
+        <v>162906</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -655,11 +655,11 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>109484</v>
+        <v>124573</v>
       </c>
     </row>
     <row r="8">
@@ -677,23 +677,23 @@
         <v>650000</v>
       </c>
       <c r="D8" t="n">
-        <v>183271.96</v>
+        <v>189181.96</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>28.2%</t>
+          <t>29.1%</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>19192</v>
+        <v>25944</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>164079.96</v>
+        <v>163237.96</v>
       </c>
     </row>
     <row r="9">
@@ -711,23 +711,23 @@
         <v>1700000</v>
       </c>
       <c r="D9" t="n">
-        <v>419321</v>
+        <v>437731</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>24.7%</t>
+          <t>25.7%</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>53574</v>
+        <v>83374</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>19.0%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>365747</v>
+        <v>354357</v>
       </c>
     </row>
     <row r="10">
@@ -745,11 +745,11 @@
         <v>2000000</v>
       </c>
       <c r="D10" t="n">
-        <v>800599.3400000001</v>
+        <v>840964.3400000001</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>42.0%</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>800599.3400000001</v>
+        <v>840964.3400000001</v>
       </c>
     </row>
     <row r="11">
@@ -779,11 +779,11 @@
         <v>450000</v>
       </c>
       <c r="D11" t="n">
-        <v>77711</v>
+        <v>112403.63</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>17.3%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -791,11 +791,11 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>31.9%</t>
+          <t>22.1%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>52902</v>
+        <v>87594.63</v>
       </c>
     </row>
     <row r="12">
@@ -813,11 +813,11 @@
         <v>450000</v>
       </c>
       <c r="D12" t="n">
-        <v>138916</v>
+        <v>149314</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>30.9%</t>
+          <t>33.2%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -825,11 +825,11 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>1.3%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>136937</v>
+        <v>147335</v>
       </c>
     </row>
     <row r="13">
@@ -847,23 +847,23 @@
         <v>850000</v>
       </c>
       <c r="D13" t="n">
-        <v>218307.17</v>
+        <v>250326.17</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>25.7%</t>
+          <t>29.5%</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>36761</v>
+        <v>59561</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>16.8%</t>
+          <t>23.8%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>181546.17</v>
+        <v>190765.17</v>
       </c>
     </row>
     <row r="14">
@@ -881,11 +881,11 @@
         <v>800000</v>
       </c>
       <c r="D14" t="n">
-        <v>110973.4</v>
+        <v>119769.4</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>15.0%</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -893,11 +893,11 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>15.8%</t>
+          <t>14.7%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>93424.39999999999</v>
+        <v>102220.4</v>
       </c>
     </row>
     <row r="15">
@@ -915,7 +915,7 @@
         <v>260000</v>
       </c>
       <c r="D15" t="n">
-        <v>128468</v>
+        <v>128497</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>15277</v>
+        <v>15306</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -949,11 +949,11 @@
         <v>400000</v>
       </c>
       <c r="D16" t="n">
-        <v>69489</v>
+        <v>73687</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>17.4%</t>
+          <t>18.4%</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -961,11 +961,11 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>13.8%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>59289</v>
+        <v>63487</v>
       </c>
     </row>
     <row r="17">
@@ -983,11 +983,11 @@
         <v>700000</v>
       </c>
       <c r="D17" t="n">
-        <v>196791.94</v>
+        <v>206492.94</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>28.1%</t>
+          <t>29.5%</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -995,11 +995,11 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>177325.94</v>
+        <v>187026.94</v>
       </c>
     </row>
     <row r="18">
@@ -1017,23 +1017,23 @@
         <v>800000</v>
       </c>
       <c r="D18" t="n">
-        <v>283570.01</v>
+        <v>333275.01</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>35.4%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>20656</v>
+        <v>35556</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>7.3%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>262914.01</v>
+        <v>297719.01</v>
       </c>
     </row>
     <row r="19">
@@ -1051,11 +1051,11 @@
         <v>850000</v>
       </c>
       <c r="D19" t="n">
-        <v>131104.11</v>
+        <v>131502.11</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>15.5%</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -1063,11 +1063,11 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>109.5%</t>
+          <t>109.1%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>-12393.89000000001</v>
+        <v>-11995.89000000001</v>
       </c>
     </row>
     <row r="20">
@@ -1085,23 +1085,23 @@
         <v>700000</v>
       </c>
       <c r="D20" t="n">
-        <v>261354.99</v>
+        <v>257036.99</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>37.3%</t>
+          <t>36.7%</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>20800</v>
+        <v>13800</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>8.0%</t>
+          <t>5.4%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>240554.99</v>
+        <v>243236.99</v>
       </c>
     </row>
   </sheetData>

--- a/导出_按分组.xlsx
+++ b/导出_按分组.xlsx
@@ -745,11 +745,11 @@
         <v>2000000</v>
       </c>
       <c r="D10" t="n">
-        <v>840964.3400000001</v>
+        <v>822566.3400000001</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>42.0%</t>
+          <t>41.1%</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>840964.3400000001</v>
+        <v>822566.3400000001</v>
       </c>
     </row>
     <row r="11">
@@ -1085,23 +1085,23 @@
         <v>700000</v>
       </c>
       <c r="D20" t="n">
-        <v>257036.99</v>
+        <v>282434.99</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>36.7%</t>
+          <t>40.3%</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>13800</v>
+        <v>20800</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>5.4%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>243236.99</v>
+        <v>261634.99</v>
       </c>
     </row>
   </sheetData>

--- a/导出_按分组.xlsx
+++ b/导出_按分组.xlsx
@@ -473,23 +473,23 @@
         <v>1000000</v>
       </c>
       <c r="D2" t="n">
-        <v>138402.18</v>
+        <v>147117.18</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>14.7%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>136369.67</v>
+        <v>141387.67</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>98.5%</t>
+          <t>96.1%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2032.50999999998</v>
+        <v>5729.50999999998</v>
       </c>
     </row>
     <row r="3">
@@ -507,23 +507,23 @@
         <v>100000</v>
       </c>
       <c r="D3" t="n">
-        <v>20291.2</v>
+        <v>20685.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>20.3%</t>
+          <t>20.7%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>25136</v>
+        <v>25174</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>123.9%</t>
+          <t>121.7%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>-4844.799999999999</v>
+        <v>-4488.799999999999</v>
       </c>
     </row>
     <row r="4">
@@ -541,23 +541,23 @@
         <v>800000</v>
       </c>
       <c r="D4" t="n">
-        <v>249236.16</v>
+        <v>269519.16</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>33.7%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>110359.9</v>
+        <v>110444.9</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>44.3%</t>
+          <t>41.0%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>138876.26</v>
+        <v>159074.26</v>
       </c>
     </row>
     <row r="5">
@@ -575,23 +575,23 @@
         <v>650000</v>
       </c>
       <c r="D5" t="n">
-        <v>236399.16</v>
+        <v>241463.16</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>37.1%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>69235</v>
+        <v>106052</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>29.3%</t>
+          <t>43.9%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>167164.16</v>
+        <v>135411.16</v>
       </c>
     </row>
     <row r="6">
@@ -609,23 +609,23 @@
         <v>700000</v>
       </c>
       <c r="D6" t="n">
-        <v>176308.99</v>
+        <v>192883.99</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>27.6%</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>48617.07</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
           <t>25.2%</t>
         </is>
       </c>
-      <c r="F6" t="n">
-        <v>46713.07</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>26.5%</t>
-        </is>
-      </c>
       <c r="H6" t="n">
-        <v>129595.92</v>
+        <v>144266.92</v>
       </c>
     </row>
     <row r="7">
@@ -643,23 +643,23 @@
         <v>550000</v>
       </c>
       <c r="D7" t="n">
-        <v>162906</v>
+        <v>167916</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>30.5%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>38333</v>
+        <v>38351</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>22.8%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>124573</v>
+        <v>129565</v>
       </c>
     </row>
     <row r="8">
@@ -677,23 +677,23 @@
         <v>650000</v>
       </c>
       <c r="D8" t="n">
-        <v>189181.96</v>
+        <v>213469.96</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>29.1%</t>
+          <t>32.8%</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>25944</v>
+        <v>27703</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>163237.96</v>
+        <v>185766.96</v>
       </c>
     </row>
     <row r="9">
@@ -711,23 +711,23 @@
         <v>1700000</v>
       </c>
       <c r="D9" t="n">
-        <v>437731</v>
+        <v>565827</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>25.7%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>83374</v>
+        <v>136924</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>19.0%</t>
+          <t>24.2%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>354357</v>
+        <v>428903</v>
       </c>
     </row>
     <row r="10">
@@ -779,23 +779,23 @@
         <v>450000</v>
       </c>
       <c r="D11" t="n">
-        <v>112403.63</v>
+        <v>123100.63</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>27.4%</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>24809</v>
+        <v>25108</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>22.1%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>87594.63</v>
+        <v>97992.63</v>
       </c>
     </row>
     <row r="12">
@@ -847,11 +847,11 @@
         <v>850000</v>
       </c>
       <c r="D13" t="n">
-        <v>250326.17</v>
+        <v>251724.17</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>29.5%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -859,11 +859,11 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>23.8%</t>
+          <t>23.7%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>190765.17</v>
+        <v>192163.17</v>
       </c>
     </row>
     <row r="14">
@@ -881,23 +881,23 @@
         <v>800000</v>
       </c>
       <c r="D14" t="n">
-        <v>119769.4</v>
+        <v>129361.4</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>16.2%</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>17549</v>
+        <v>17578</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>102220.4</v>
+        <v>111783.4</v>
       </c>
     </row>
     <row r="15">
@@ -915,11 +915,11 @@
         <v>260000</v>
       </c>
       <c r="D15" t="n">
-        <v>128497</v>
+        <v>130575</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>49.4%</t>
+          <t>50.2%</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -927,11 +927,11 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>113191</v>
+        <v>115269</v>
       </c>
     </row>
     <row r="16">
@@ -983,23 +983,23 @@
         <v>700000</v>
       </c>
       <c r="D17" t="n">
-        <v>206492.94</v>
+        <v>235988.94</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>29.5%</t>
+          <t>33.7%</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>19466</v>
+        <v>35866</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>15.2%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>187026.94</v>
+        <v>200122.94</v>
       </c>
     </row>
     <row r="18">
@@ -1017,23 +1017,23 @@
         <v>800000</v>
       </c>
       <c r="D18" t="n">
-        <v>333275.01</v>
+        <v>345194.01</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>43.1%</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>35556</v>
+        <v>51556</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>14.9%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>297719.01</v>
+        <v>293638.01</v>
       </c>
     </row>
     <row r="19">
@@ -1051,11 +1051,11 @@
         <v>850000</v>
       </c>
       <c r="D19" t="n">
-        <v>131502.11</v>
+        <v>172871.11</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>15.5%</t>
+          <t>20.3%</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -1063,11 +1063,11 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>109.1%</t>
+          <t>83.0%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>-11995.89000000001</v>
+        <v>29373.10999999999</v>
       </c>
     </row>
     <row r="20">
@@ -1085,23 +1085,23 @@
         <v>700000</v>
       </c>
       <c r="D20" t="n">
-        <v>282434.99</v>
+        <v>328034.99</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>40.3%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>20800</v>
+        <v>68000</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>20.7%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>261634.99</v>
+        <v>260034.99</v>
       </c>
     </row>
   </sheetData>

--- a/导出_按分组.xlsx
+++ b/导出_按分组.xlsx
@@ -473,23 +473,23 @@
         <v>1000000</v>
       </c>
       <c r="D2" t="n">
-        <v>147117.18</v>
+        <v>152458.18</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>15.2%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>141387.67</v>
+        <v>141434.67</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>96.1%</t>
+          <t>92.8%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>5729.50999999998</v>
+        <v>11023.50999999998</v>
       </c>
     </row>
     <row r="3">
@@ -507,23 +507,23 @@
         <v>100000</v>
       </c>
       <c r="D3" t="n">
-        <v>20685.2</v>
+        <v>20954.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>20.7%</t>
+          <t>21.0%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>25174</v>
+        <v>25202</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>121.7%</t>
+          <t>120.3%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>-4488.799999999999</v>
+        <v>-4247.799999999999</v>
       </c>
     </row>
     <row r="4">
@@ -541,23 +541,23 @@
         <v>800000</v>
       </c>
       <c r="D4" t="n">
-        <v>269519.16</v>
+        <v>300692.16</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>33.7%</t>
+          <t>37.6%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>110444.9</v>
+        <v>110614.8</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>41.0%</t>
+          <t>36.8%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>159074.26</v>
+        <v>190077.36</v>
       </c>
     </row>
     <row r="5">
@@ -575,11 +575,11 @@
         <v>650000</v>
       </c>
       <c r="D5" t="n">
-        <v>241463.16</v>
+        <v>241492.16</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>37.1%</t>
+          <t>37.2%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>135411.16</v>
+        <v>135440.16</v>
       </c>
     </row>
     <row r="6">
@@ -609,23 +609,23 @@
         <v>700000</v>
       </c>
       <c r="D6" t="n">
-        <v>192883.99</v>
+        <v>194727.99</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>27.6%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>48617.07</v>
+        <v>49416.07</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>25.2%</t>
+          <t>25.4%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>144266.92</v>
+        <v>145311.92</v>
       </c>
     </row>
     <row r="7">
@@ -643,15 +643,15 @@
         <v>550000</v>
       </c>
       <c r="D7" t="n">
-        <v>167916</v>
+        <v>168381</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>30.5%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>38351</v>
+        <v>38389</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>129565</v>
+        <v>129992</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         <v>650000</v>
       </c>
       <c r="D8" t="n">
-        <v>213469.96</v>
+        <v>213516.96</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -685,7 +685,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>27703</v>
+        <v>27797</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -693,7 +693,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>185766.96</v>
+        <v>185719.96</v>
       </c>
     </row>
     <row r="9">
@@ -711,11 +711,11 @@
         <v>1700000</v>
       </c>
       <c r="D9" t="n">
-        <v>565827</v>
+        <v>575827</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>33.9%</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -723,11 +723,11 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>24.2%</t>
+          <t>23.8%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>428903</v>
+        <v>438903</v>
       </c>
     </row>
     <row r="10">
@@ -779,11 +779,11 @@
         <v>450000</v>
       </c>
       <c r="D11" t="n">
-        <v>123100.63</v>
+        <v>135100.63</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>27.4%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -791,11 +791,11 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>97992.63</v>
+        <v>109992.63</v>
       </c>
     </row>
     <row r="12">
@@ -813,11 +813,11 @@
         <v>450000</v>
       </c>
       <c r="D12" t="n">
-        <v>149314</v>
+        <v>190906</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>33.2%</t>
+          <t>42.4%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -825,11 +825,11 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>1.0%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>147335</v>
+        <v>188927</v>
       </c>
     </row>
     <row r="13">
@@ -847,11 +847,11 @@
         <v>850000</v>
       </c>
       <c r="D13" t="n">
-        <v>251724.17</v>
+        <v>260039.17</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -859,11 +859,11 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>23.7%</t>
+          <t>22.9%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>192163.17</v>
+        <v>200478.17</v>
       </c>
     </row>
     <row r="14">
@@ -881,11 +881,11 @@
         <v>800000</v>
       </c>
       <c r="D14" t="n">
-        <v>129361.4</v>
+        <v>162961.4</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>16.2%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -893,11 +893,11 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>111783.4</v>
+        <v>145383.4</v>
       </c>
     </row>
     <row r="15">
@@ -915,11 +915,11 @@
         <v>260000</v>
       </c>
       <c r="D15" t="n">
-        <v>130575</v>
+        <v>132963</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>50.2%</t>
+          <t>51.1%</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -927,11 +927,11 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>115269</v>
+        <v>117657</v>
       </c>
     </row>
     <row r="16">
@@ -949,11 +949,11 @@
         <v>400000</v>
       </c>
       <c r="D16" t="n">
-        <v>73687</v>
+        <v>173061.99</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>18.4%</t>
+          <t>43.3%</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -961,11 +961,11 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>63487</v>
+        <v>162861.99</v>
       </c>
     </row>
     <row r="17">
@@ -983,11 +983,11 @@
         <v>700000</v>
       </c>
       <c r="D17" t="n">
-        <v>235988.94</v>
+        <v>249780.94</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>33.7%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -995,11 +995,11 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>15.2%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>200122.94</v>
+        <v>213914.94</v>
       </c>
     </row>
     <row r="18">
@@ -1017,11 +1017,11 @@
         <v>800000</v>
       </c>
       <c r="D18" t="n">
-        <v>345194.01</v>
+        <v>361309.77</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>43.1%</t>
+          <t>45.2%</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -1029,11 +1029,11 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>14.9%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>293638.01</v>
+        <v>309753.77</v>
       </c>
     </row>
     <row r="19">
@@ -1051,11 +1051,11 @@
         <v>850000</v>
       </c>
       <c r="D19" t="n">
-        <v>172871.11</v>
+        <v>180788.11</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>20.3%</t>
+          <t>21.3%</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -1063,11 +1063,11 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>83.0%</t>
+          <t>79.4%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>29373.10999999999</v>
+        <v>37290.10999999999</v>
       </c>
     </row>
     <row r="20">
@@ -1085,11 +1085,11 @@
         <v>700000</v>
       </c>
       <c r="D20" t="n">
-        <v>328034.99</v>
+        <v>343028.99</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>49.0%</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -1097,11 +1097,11 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>20.7%</t>
+          <t>19.8%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>260034.99</v>
+        <v>275028.99</v>
       </c>
     </row>
   </sheetData>

--- a/导出_按分组.xlsx
+++ b/导出_按分组.xlsx
@@ -609,7 +609,7 @@
         <v>700000</v>
       </c>
       <c r="D6" t="n">
-        <v>194727.99</v>
+        <v>194756.99</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -625,7 +625,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>145311.92</v>
+        <v>145340.92</v>
       </c>
     </row>
     <row r="7">

--- a/导出_按分组.xlsx
+++ b/导出_按分组.xlsx
@@ -473,23 +473,23 @@
         <v>1000000</v>
       </c>
       <c r="D2" t="n">
-        <v>152458.18</v>
+        <v>223057.18</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>15.2%</t>
+          <t>22.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>141434.67</v>
+        <v>145970.67</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>92.8%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>11023.50999999998</v>
+        <v>77086.50999999998</v>
       </c>
     </row>
     <row r="3">
@@ -507,23 +507,23 @@
         <v>100000</v>
       </c>
       <c r="D3" t="n">
-        <v>20954.2</v>
+        <v>19889.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>19.9%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>25202</v>
+        <v>25030</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>120.3%</t>
+          <t>125.8%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>-4247.799999999999</v>
+        <v>-5140.799999999999</v>
       </c>
     </row>
     <row r="4">
@@ -541,23 +541,23 @@
         <v>800000</v>
       </c>
       <c r="D4" t="n">
-        <v>300692.16</v>
+        <v>340979.12</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>37.6%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>110614.8</v>
+        <v>115969.8</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>36.8%</t>
+          <t>34.0%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>190077.36</v>
+        <v>225009.32</v>
       </c>
     </row>
     <row r="5">
@@ -575,11 +575,11 @@
         <v>650000</v>
       </c>
       <c r="D5" t="n">
-        <v>241492.16</v>
+        <v>391449.17</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>37.2%</t>
+          <t>60.2%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -587,11 +587,11 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>43.9%</t>
+          <t>27.1%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>135440.16</v>
+        <v>285397.17</v>
       </c>
     </row>
     <row r="6">
@@ -609,23 +609,23 @@
         <v>700000</v>
       </c>
       <c r="D6" t="n">
-        <v>194756.99</v>
+        <v>198996.99</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>28.4%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>49416.07</v>
+        <v>57694.07</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>25.4%</t>
+          <t>29.0%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>145340.92</v>
+        <v>141302.92</v>
       </c>
     </row>
     <row r="7">
@@ -643,23 +643,23 @@
         <v>550000</v>
       </c>
       <c r="D7" t="n">
-        <v>168381</v>
+        <v>230370</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>41.9%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>38389</v>
+        <v>58681</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>22.8%</t>
+          <t>25.5%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>129992</v>
+        <v>171689</v>
       </c>
     </row>
     <row r="8">
@@ -677,23 +677,23 @@
         <v>650000</v>
       </c>
       <c r="D8" t="n">
-        <v>213516.96</v>
+        <v>276643.96</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>32.8%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>27797</v>
+        <v>33123</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>185719.96</v>
+        <v>243520.96</v>
       </c>
     </row>
     <row r="9">
@@ -711,23 +711,23 @@
         <v>1700000</v>
       </c>
       <c r="D9" t="n">
-        <v>575827</v>
+        <v>612146</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>33.9%</t>
+          <t>36.0%</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>136924</v>
+        <v>140924</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>23.8%</t>
+          <t>23.0%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>438903</v>
+        <v>471222</v>
       </c>
     </row>
     <row r="10">
@@ -745,11 +745,11 @@
         <v>2000000</v>
       </c>
       <c r="D10" t="n">
-        <v>822566.3400000001</v>
+        <v>1118761.8</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>41.1%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>822566.3400000001</v>
+        <v>1118761.8</v>
       </c>
     </row>
     <row r="11">
@@ -779,11 +779,11 @@
         <v>450000</v>
       </c>
       <c r="D11" t="n">
-        <v>135100.63</v>
+        <v>169833.63</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>37.7%</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -791,11 +791,11 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>109992.63</v>
+        <v>144725.63</v>
       </c>
     </row>
     <row r="12">
@@ -813,11 +813,11 @@
         <v>450000</v>
       </c>
       <c r="D12" t="n">
-        <v>190906</v>
+        <v>202119</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>42.4%</t>
+          <t>44.9%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>188927</v>
+        <v>200140</v>
       </c>
     </row>
     <row r="13">
@@ -847,11 +847,11 @@
         <v>850000</v>
       </c>
       <c r="D13" t="n">
-        <v>260039.17</v>
+        <v>297977.67</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>35.1%</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -859,11 +859,11 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>22.9%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>200478.17</v>
+        <v>238416.67</v>
       </c>
     </row>
     <row r="14">
@@ -881,23 +881,23 @@
         <v>800000</v>
       </c>
       <c r="D14" t="n">
-        <v>162961.4</v>
+        <v>214688.1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>26.8%</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>17578</v>
+        <v>18378</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>145383.4</v>
+        <v>196310.1</v>
       </c>
     </row>
     <row r="15">
@@ -915,11 +915,11 @@
         <v>260000</v>
       </c>
       <c r="D15" t="n">
-        <v>132963</v>
+        <v>134176</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>51.1%</t>
+          <t>51.6%</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -927,11 +927,11 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>117657</v>
+        <v>118870</v>
       </c>
     </row>
     <row r="16">
@@ -949,11 +949,11 @@
         <v>400000</v>
       </c>
       <c r="D16" t="n">
-        <v>173061.99</v>
+        <v>213446.98</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>43.3%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -961,11 +961,11 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>4.8%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>162861.99</v>
+        <v>203246.98</v>
       </c>
     </row>
     <row r="17">
@@ -983,11 +983,11 @@
         <v>700000</v>
       </c>
       <c r="D17" t="n">
-        <v>249780.94</v>
+        <v>257611.94</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>36.8%</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -995,11 +995,11 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>213914.94</v>
+        <v>221745.94</v>
       </c>
     </row>
     <row r="18">
@@ -1017,11 +1017,11 @@
         <v>800000</v>
       </c>
       <c r="D18" t="n">
-        <v>361309.77</v>
+        <v>386981.71</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>45.2%</t>
+          <t>48.4%</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -1029,11 +1029,11 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>309753.77</v>
+        <v>335425.71</v>
       </c>
     </row>
     <row r="19">
@@ -1051,11 +1051,11 @@
         <v>850000</v>
       </c>
       <c r="D19" t="n">
-        <v>180788.11</v>
+        <v>201978.54</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>21.3%</t>
+          <t>23.8%</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -1063,11 +1063,11 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>79.4%</t>
+          <t>71.0%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>37290.10999999999</v>
+        <v>58480.54000000001</v>
       </c>
     </row>
     <row r="20">
@@ -1085,23 +1085,23 @@
         <v>700000</v>
       </c>
       <c r="D20" t="n">
-        <v>343028.99</v>
+        <v>367724.99</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>49.0%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>68000</v>
+        <v>73000</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>19.8%</t>
+          <t>19.9%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>275028.99</v>
+        <v>294724.99</v>
       </c>
     </row>
   </sheetData>

--- a/导出_按分组.xlsx
+++ b/导出_按分组.xlsx
@@ -473,23 +473,23 @@
         <v>1000000</v>
       </c>
       <c r="D2" t="n">
-        <v>223057.18</v>
+        <v>177958.18</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>22.3%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>145970.67</v>
+        <v>141557.67</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>79.5%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>77086.50999999998</v>
+        <v>36400.51000000001</v>
       </c>
     </row>
     <row r="3">
@@ -507,23 +507,23 @@
         <v>100000</v>
       </c>
       <c r="D3" t="n">
-        <v>19889.2</v>
+        <v>15875.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>19.9%</t>
+          <t>15.9%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>25030</v>
+        <v>25024</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>125.8%</t>
+          <t>157.6%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>-5140.799999999999</v>
+        <v>-9148.799999999999</v>
       </c>
     </row>
     <row r="4">
@@ -541,23 +541,23 @@
         <v>800000</v>
       </c>
       <c r="D4" t="n">
-        <v>340979.12</v>
+        <v>289068.12</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>115969.8</v>
+        <v>110671.8</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>34.0%</t>
+          <t>38.3%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>225009.32</v>
+        <v>178396.32</v>
       </c>
     </row>
     <row r="5">
@@ -575,11 +575,11 @@
         <v>650000</v>
       </c>
       <c r="D5" t="n">
-        <v>391449.17</v>
+        <v>324974.16</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>60.2%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -587,11 +587,11 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>27.1%</t>
+          <t>32.6%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>285397.17</v>
+        <v>218922.16</v>
       </c>
     </row>
     <row r="6">
@@ -609,23 +609,23 @@
         <v>700000</v>
       </c>
       <c r="D6" t="n">
-        <v>198996.99</v>
+        <v>196193.99</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>28.4%</t>
+          <t>28.0%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>57694.07</v>
+        <v>49631.07</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>29.0%</t>
+          <t>25.3%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>141302.92</v>
+        <v>146562.92</v>
       </c>
     </row>
     <row r="7">
@@ -643,23 +643,23 @@
         <v>550000</v>
       </c>
       <c r="D7" t="n">
-        <v>230370</v>
+        <v>200489</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>41.9%</t>
+          <t>36.5%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>58681</v>
+        <v>38586</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>25.5%</t>
+          <t>19.2%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>171689</v>
+        <v>161903</v>
       </c>
     </row>
     <row r="8">
@@ -677,23 +677,23 @@
         <v>650000</v>
       </c>
       <c r="D8" t="n">
-        <v>276643.96</v>
+        <v>217769.96</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>33.5%</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>33123</v>
+        <v>33114</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>15.2%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>243520.96</v>
+        <v>184655.96</v>
       </c>
     </row>
     <row r="9">
@@ -711,23 +711,23 @@
         <v>1700000</v>
       </c>
       <c r="D9" t="n">
-        <v>612146</v>
+        <v>587346</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>36.0%</t>
+          <t>34.5%</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>140924</v>
+        <v>136924</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>23.0%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>471222</v>
+        <v>450422</v>
       </c>
     </row>
     <row r="10">
@@ -745,11 +745,11 @@
         <v>2000000</v>
       </c>
       <c r="D10" t="n">
-        <v>1118761.8</v>
+        <v>1148313.8</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1118761.8</v>
+        <v>1148313.8</v>
       </c>
     </row>
     <row r="11">
@@ -779,11 +779,11 @@
         <v>450000</v>
       </c>
       <c r="D11" t="n">
-        <v>169833.63</v>
+        <v>151700.63</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>37.7%</t>
+          <t>33.7%</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -791,11 +791,11 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>16.6%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>144725.63</v>
+        <v>126592.63</v>
       </c>
     </row>
     <row r="12">
@@ -813,11 +813,11 @@
         <v>450000</v>
       </c>
       <c r="D12" t="n">
-        <v>202119</v>
+        <v>191702</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>44.9%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>200140</v>
+        <v>189723</v>
       </c>
     </row>
     <row r="13">
@@ -847,11 +847,11 @@
         <v>850000</v>
       </c>
       <c r="D13" t="n">
-        <v>297977.67</v>
+        <v>267336.17</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>35.1%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -859,11 +859,11 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>22.3%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>238416.67</v>
+        <v>207775.17</v>
       </c>
     </row>
     <row r="14">
@@ -881,11 +881,11 @@
         <v>800000</v>
       </c>
       <c r="D14" t="n">
-        <v>214688.1</v>
+        <v>204536.4</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>26.8%</t>
+          <t>25.6%</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -893,11 +893,11 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>9.0%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>196310.1</v>
+        <v>186158.4</v>
       </c>
     </row>
     <row r="15">
@@ -915,11 +915,11 @@
         <v>260000</v>
       </c>
       <c r="D15" t="n">
-        <v>134176</v>
+        <v>132963</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>51.6%</t>
+          <t>51.1%</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -927,11 +927,11 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>118870</v>
+        <v>117657</v>
       </c>
     </row>
     <row r="16">
@@ -983,11 +983,11 @@
         <v>700000</v>
       </c>
       <c r="D17" t="n">
-        <v>257611.94</v>
+        <v>256910.94</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>36.8%</t>
+          <t>36.7%</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -995,11 +995,11 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>14.0%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>221745.94</v>
+        <v>221044.94</v>
       </c>
     </row>
     <row r="18">
@@ -1017,11 +1017,11 @@
         <v>800000</v>
       </c>
       <c r="D18" t="n">
-        <v>386981.71</v>
+        <v>379683.71</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>48.4%</t>
+          <t>47.5%</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -1029,11 +1029,11 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>335425.71</v>
+        <v>328127.71</v>
       </c>
     </row>
     <row r="19">
@@ -1051,11 +1051,11 @@
         <v>850000</v>
       </c>
       <c r="D19" t="n">
-        <v>201978.54</v>
+        <v>186580.54</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>23.8%</t>
+          <t>22.0%</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -1063,11 +1063,11 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>71.0%</t>
+          <t>76.9%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>58480.54000000001</v>
+        <v>43082.54000000001</v>
       </c>
     </row>
     <row r="20">
@@ -1085,23 +1085,23 @@
         <v>700000</v>
       </c>
       <c r="D20" t="n">
-        <v>367724.99</v>
+        <v>365128.99</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>73000</v>
+        <v>68000</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>19.9%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>294724.99</v>
+        <v>297128.99</v>
       </c>
     </row>
   </sheetData>

--- a/导出_按分组.xlsx
+++ b/导出_按分组.xlsx
@@ -473,23 +473,23 @@
         <v>1000000</v>
       </c>
       <c r="D2" t="n">
-        <v>177958.18</v>
+        <v>223057.18</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>22.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>141557.67</v>
+        <v>145970.67</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>79.5%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>36400.51000000001</v>
+        <v>77086.50999999998</v>
       </c>
     </row>
     <row r="3">
@@ -507,23 +507,23 @@
         <v>100000</v>
       </c>
       <c r="D3" t="n">
-        <v>15875.2</v>
+        <v>19889.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>15.9%</t>
+          <t>19.9%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>25024</v>
+        <v>25030</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>157.6%</t>
+          <t>125.8%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>-9148.799999999999</v>
+        <v>-5140.799999999999</v>
       </c>
     </row>
     <row r="4">
@@ -541,23 +541,23 @@
         <v>800000</v>
       </c>
       <c r="D4" t="n">
-        <v>289068.12</v>
+        <v>340979.12</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>110671.8</v>
+        <v>115969.8</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>38.3%</t>
+          <t>34.0%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>178396.32</v>
+        <v>225009.32</v>
       </c>
     </row>
     <row r="5">
@@ -575,11 +575,11 @@
         <v>650000</v>
       </c>
       <c r="D5" t="n">
-        <v>324974.16</v>
+        <v>391449.17</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>60.2%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -587,11 +587,11 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>32.6%</t>
+          <t>27.1%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>218922.16</v>
+        <v>285397.17</v>
       </c>
     </row>
     <row r="6">
@@ -609,23 +609,23 @@
         <v>700000</v>
       </c>
       <c r="D6" t="n">
-        <v>196193.99</v>
+        <v>198996.99</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>28.0%</t>
+          <t>28.4%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>49631.07</v>
+        <v>57694.07</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>25.3%</t>
+          <t>29.0%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>146562.92</v>
+        <v>141302.92</v>
       </c>
     </row>
     <row r="7">
@@ -643,23 +643,23 @@
         <v>550000</v>
       </c>
       <c r="D7" t="n">
-        <v>200489</v>
+        <v>230370</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>36.5%</t>
+          <t>41.9%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>38586</v>
+        <v>58681</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>19.2%</t>
+          <t>25.5%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>161903</v>
+        <v>171689</v>
       </c>
     </row>
     <row r="8">
@@ -677,23 +677,23 @@
         <v>650000</v>
       </c>
       <c r="D8" t="n">
-        <v>217769.96</v>
+        <v>276643.96</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>33.5%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>33114</v>
+        <v>33123</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>15.2%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>184655.96</v>
+        <v>243520.96</v>
       </c>
     </row>
     <row r="9">
@@ -711,23 +711,23 @@
         <v>1700000</v>
       </c>
       <c r="D9" t="n">
-        <v>587346</v>
+        <v>612146</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>34.5%</t>
+          <t>36.0%</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>136924</v>
+        <v>140924</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>23.3%</t>
+          <t>23.0%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>450422</v>
+        <v>471222</v>
       </c>
     </row>
     <row r="10">
@@ -745,11 +745,11 @@
         <v>2000000</v>
       </c>
       <c r="D10" t="n">
-        <v>1148313.8</v>
+        <v>1118761.8</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1148313.8</v>
+        <v>1118761.8</v>
       </c>
     </row>
     <row r="11">
@@ -779,11 +779,11 @@
         <v>450000</v>
       </c>
       <c r="D11" t="n">
-        <v>151700.63</v>
+        <v>169833.63</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>33.7%</t>
+          <t>37.7%</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -791,11 +791,11 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>16.6%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>126592.63</v>
+        <v>144725.63</v>
       </c>
     </row>
     <row r="12">
@@ -813,11 +813,11 @@
         <v>450000</v>
       </c>
       <c r="D12" t="n">
-        <v>191702</v>
+        <v>202119</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>44.9%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>189723</v>
+        <v>200140</v>
       </c>
     </row>
     <row r="13">
@@ -847,11 +847,11 @@
         <v>850000</v>
       </c>
       <c r="D13" t="n">
-        <v>267336.17</v>
+        <v>297977.67</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>35.1%</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -859,11 +859,11 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>22.3%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>207775.17</v>
+        <v>238416.67</v>
       </c>
     </row>
     <row r="14">
@@ -881,11 +881,11 @@
         <v>800000</v>
       </c>
       <c r="D14" t="n">
-        <v>204536.4</v>
+        <v>214688.1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>25.6%</t>
+          <t>26.8%</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -893,11 +893,11 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>9.0%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>186158.4</v>
+        <v>196310.1</v>
       </c>
     </row>
     <row r="15">
@@ -915,11 +915,11 @@
         <v>260000</v>
       </c>
       <c r="D15" t="n">
-        <v>132963</v>
+        <v>134176</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>51.1%</t>
+          <t>51.6%</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -927,11 +927,11 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>117657</v>
+        <v>118870</v>
       </c>
     </row>
     <row r="16">
@@ -983,11 +983,11 @@
         <v>700000</v>
       </c>
       <c r="D17" t="n">
-        <v>256910.94</v>
+        <v>257611.94</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>36.7%</t>
+          <t>36.8%</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -995,11 +995,11 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>221044.94</v>
+        <v>221745.94</v>
       </c>
     </row>
     <row r="18">
@@ -1017,11 +1017,11 @@
         <v>800000</v>
       </c>
       <c r="D18" t="n">
-        <v>379683.71</v>
+        <v>386981.71</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>47.5%</t>
+          <t>48.4%</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -1029,11 +1029,11 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>328127.71</v>
+        <v>335425.71</v>
       </c>
     </row>
     <row r="19">
@@ -1051,11 +1051,11 @@
         <v>850000</v>
       </c>
       <c r="D19" t="n">
-        <v>186580.54</v>
+        <v>201978.54</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>22.0%</t>
+          <t>23.8%</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -1063,11 +1063,11 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>71.0%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>43082.54000000001</v>
+        <v>58480.54000000001</v>
       </c>
     </row>
     <row r="20">
@@ -1085,23 +1085,23 @@
         <v>700000</v>
       </c>
       <c r="D20" t="n">
-        <v>365128.99</v>
+        <v>367724.99</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>68000</v>
+        <v>73000</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>19.9%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>297128.99</v>
+        <v>294724.99</v>
       </c>
     </row>
   </sheetData>

--- a/导出_按分组.xlsx
+++ b/导出_按分组.xlsx
@@ -745,11 +745,11 @@
         <v>2000000</v>
       </c>
       <c r="D10" t="n">
-        <v>1118761.8</v>
+        <v>1001391.8</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>50.1%</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1118761.8</v>
+        <v>1001391.8</v>
       </c>
     </row>
     <row r="11">

--- a/导出_按分组.xlsx
+++ b/导出_按分组.xlsx
@@ -473,23 +473,23 @@
         <v>1000000</v>
       </c>
       <c r="D2" t="n">
-        <v>223057.18</v>
+        <v>233339.18</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>22.3%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>145970.67</v>
+        <v>151243.67</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>64.8%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>77086.50999999998</v>
+        <v>82095.50999999998</v>
       </c>
     </row>
     <row r="3">
@@ -507,23 +507,23 @@
         <v>100000</v>
       </c>
       <c r="D3" t="n">
-        <v>19889.2</v>
+        <v>20351.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>19.9%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>25030</v>
+        <v>27035</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>125.8%</t>
+          <t>132.8%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>-5140.799999999999</v>
+        <v>-6683.799999999999</v>
       </c>
     </row>
     <row r="4">
@@ -541,23 +541,23 @@
         <v>800000</v>
       </c>
       <c r="D4" t="n">
-        <v>340979.12</v>
+        <v>391271.02</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>48.9%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>115969.8</v>
+        <v>117731.8</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>34.0%</t>
+          <t>30.1%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>225009.32</v>
+        <v>273539.22</v>
       </c>
     </row>
     <row r="5">
@@ -575,23 +575,23 @@
         <v>650000</v>
       </c>
       <c r="D5" t="n">
-        <v>391449.17</v>
+        <v>397481.17</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>60.2%</t>
+          <t>61.2%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>106052</v>
+        <v>106071</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>27.1%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>285397.17</v>
+        <v>291410.17</v>
       </c>
     </row>
     <row r="6">
@@ -609,23 +609,23 @@
         <v>700000</v>
       </c>
       <c r="D6" t="n">
-        <v>198996.99</v>
+        <v>203275.99</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>28.4%</t>
+          <t>29.0%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>57694.07</v>
+        <v>63093.07</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>29.0%</t>
+          <t>31.0%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>141302.92</v>
+        <v>140182.92</v>
       </c>
     </row>
     <row r="7">
@@ -643,23 +643,23 @@
         <v>550000</v>
       </c>
       <c r="D7" t="n">
-        <v>230370</v>
+        <v>233541</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>41.9%</t>
+          <t>42.5%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>58681</v>
+        <v>58719</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>25.5%</t>
+          <t>25.1%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>171689</v>
+        <v>174822</v>
       </c>
     </row>
     <row r="8">
@@ -677,23 +677,23 @@
         <v>650000</v>
       </c>
       <c r="D8" t="n">
-        <v>276643.96</v>
+        <v>289043.86</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>44.5%</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>33123</v>
+        <v>33199</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>243520.96</v>
+        <v>255844.86</v>
       </c>
     </row>
     <row r="9">
@@ -711,23 +711,23 @@
         <v>1700000</v>
       </c>
       <c r="D9" t="n">
-        <v>612146</v>
+        <v>669666</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>36.0%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>140924</v>
+        <v>146924</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>23.0%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>471222</v>
+        <v>522742</v>
       </c>
     </row>
     <row r="10">
@@ -745,11 +745,11 @@
         <v>2000000</v>
       </c>
       <c r="D10" t="n">
-        <v>1001391.8</v>
+        <v>2003627.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>50.1%</t>
+          <t>100.2%</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1001391.8</v>
+        <v>2003627.6</v>
       </c>
     </row>
     <row r="11">
@@ -779,11 +779,11 @@
         <v>450000</v>
       </c>
       <c r="D11" t="n">
-        <v>169833.63</v>
+        <v>186033.63</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>37.7%</t>
+          <t>41.3%</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -791,11 +791,11 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>144725.63</v>
+        <v>160925.63</v>
       </c>
     </row>
     <row r="12">
@@ -813,11 +813,11 @@
         <v>450000</v>
       </c>
       <c r="D12" t="n">
-        <v>202119</v>
+        <v>202517</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>44.9%</t>
+          <t>45.0%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>200140</v>
+        <v>200538</v>
       </c>
     </row>
     <row r="13">
@@ -847,15 +847,15 @@
         <v>850000</v>
       </c>
       <c r="D13" t="n">
-        <v>297977.67</v>
+        <v>309005.77</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>35.1%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>59561</v>
+        <v>61761</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>238416.67</v>
+        <v>247244.77</v>
       </c>
     </row>
     <row r="14">
@@ -881,7 +881,7 @@
         <v>800000</v>
       </c>
       <c r="D14" t="n">
-        <v>214688.1</v>
+        <v>214429.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>196310.1</v>
+        <v>196051.3</v>
       </c>
     </row>
     <row r="15">
@@ -915,11 +915,11 @@
         <v>260000</v>
       </c>
       <c r="D15" t="n">
-        <v>134176</v>
+        <v>155694</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>51.6%</t>
+          <t>59.9%</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -927,11 +927,11 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>118870</v>
+        <v>140388</v>
       </c>
     </row>
     <row r="16">
@@ -949,11 +949,11 @@
         <v>400000</v>
       </c>
       <c r="D16" t="n">
-        <v>213446.98</v>
+        <v>218434.98</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -961,11 +961,11 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>4.8%</t>
+          <t>4.7%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>203246.98</v>
+        <v>208234.98</v>
       </c>
     </row>
     <row r="17">
@@ -983,11 +983,11 @@
         <v>700000</v>
       </c>
       <c r="D17" t="n">
-        <v>257611.94</v>
+        <v>258047.94</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>36.8%</t>
+          <t>36.9%</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>221745.94</v>
+        <v>222181.94</v>
       </c>
     </row>
     <row r="18">
@@ -1017,11 +1017,11 @@
         <v>800000</v>
       </c>
       <c r="D18" t="n">
-        <v>386981.71</v>
+        <v>391172.71</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>48.4%</t>
+          <t>48.9%</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -1029,11 +1029,11 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>335425.71</v>
+        <v>339616.71</v>
       </c>
     </row>
     <row r="19">
@@ -1051,11 +1051,11 @@
         <v>850000</v>
       </c>
       <c r="D19" t="n">
-        <v>201978.54</v>
+        <v>213091.54</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>23.8%</t>
+          <t>25.1%</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -1063,11 +1063,11 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>71.0%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>58480.54000000001</v>
+        <v>69593.54000000001</v>
       </c>
     </row>
     <row r="20">
@@ -1085,11 +1085,11 @@
         <v>700000</v>
       </c>
       <c r="D20" t="n">
-        <v>367724.99</v>
+        <v>368141.99</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>52.6%</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -1097,11 +1097,11 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>19.9%</t>
+          <t>19.8%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>294724.99</v>
+        <v>295141.99</v>
       </c>
     </row>
   </sheetData>

--- a/导出_按分组.xlsx
+++ b/导出_按分组.xlsx
@@ -745,11 +745,11 @@
         <v>2000000</v>
       </c>
       <c r="D10" t="n">
-        <v>2003627.6</v>
+        <v>1027177.8</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>100.2%</t>
+          <t>51.4%</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>2003627.6</v>
+        <v>1027177.8</v>
       </c>
     </row>
     <row r="11">

--- a/导出_按分组.xlsx
+++ b/导出_按分组.xlsx
@@ -473,15 +473,15 @@
         <v>1000000</v>
       </c>
       <c r="D2" t="n">
-        <v>233339.18</v>
+        <v>233638.18</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>23.3%</t>
+          <t>23.4%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>151243.67</v>
+        <v>151290.67</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -489,7 +489,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>82095.50999999998</v>
+        <v>82347.50999999998</v>
       </c>
     </row>
     <row r="3">
@@ -541,23 +541,23 @@
         <v>800000</v>
       </c>
       <c r="D4" t="n">
-        <v>391271.02</v>
+        <v>393033.02</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>48.9%</t>
+          <t>49.1%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>117731.8</v>
+        <v>122034.8</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>30.1%</t>
+          <t>31.0%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>273539.22</v>
+        <v>270998.22</v>
       </c>
     </row>
     <row r="5">
@@ -575,23 +575,23 @@
         <v>650000</v>
       </c>
       <c r="D5" t="n">
-        <v>397481.17</v>
+        <v>399527.17</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>61.2%</t>
+          <t>61.5%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>106071</v>
+        <v>106176</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>26.6%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>291410.17</v>
+        <v>293351.17</v>
       </c>
     </row>
     <row r="6">
@@ -609,23 +609,23 @@
         <v>700000</v>
       </c>
       <c r="D6" t="n">
-        <v>203275.99</v>
+        <v>212385.99</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>29.0%</t>
+          <t>30.3%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>63093.07</v>
+        <v>63477.07</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>31.0%</t>
+          <t>29.9%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>140182.92</v>
+        <v>148908.92</v>
       </c>
     </row>
     <row r="7">
@@ -643,15 +643,15 @@
         <v>550000</v>
       </c>
       <c r="D7" t="n">
-        <v>233541</v>
+        <v>245788</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>42.5%</t>
+          <t>44.7%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>58719</v>
+        <v>61614</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>174822</v>
+        <v>184174</v>
       </c>
     </row>
     <row r="8">
@@ -677,15 +677,15 @@
         <v>650000</v>
       </c>
       <c r="D8" t="n">
-        <v>289043.86</v>
+        <v>290524.86</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>44.5%</t>
+          <t>44.7%</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>33199</v>
+        <v>33303</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -693,7 +693,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>255844.86</v>
+        <v>257221.86</v>
       </c>
     </row>
     <row r="9">
@@ -711,11 +711,11 @@
         <v>1700000</v>
       </c>
       <c r="D9" t="n">
-        <v>669666</v>
+        <v>680573</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -723,11 +723,11 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>21.6%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>522742</v>
+        <v>533649</v>
       </c>
     </row>
     <row r="10">
@@ -745,11 +745,11 @@
         <v>2000000</v>
       </c>
       <c r="D10" t="n">
-        <v>1027177.8</v>
+        <v>1081485</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>51.4%</t>
+          <t>54.1%</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1027177.8</v>
+        <v>1081485</v>
       </c>
     </row>
     <row r="11">
@@ -779,11 +779,11 @@
         <v>450000</v>
       </c>
       <c r="D11" t="n">
-        <v>186033.63</v>
+        <v>214233.63</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>41.3%</t>
+          <t>47.6%</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -791,11 +791,11 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>160925.63</v>
+        <v>189125.63</v>
       </c>
     </row>
     <row r="12">
@@ -813,15 +813,15 @@
         <v>450000</v>
       </c>
       <c r="D12" t="n">
-        <v>202517</v>
+        <v>202915</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>45.0%</t>
+          <t>45.1%</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1979</v>
+        <v>1998</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>200538</v>
+        <v>200917</v>
       </c>
     </row>
     <row r="13">
@@ -847,23 +847,23 @@
         <v>850000</v>
       </c>
       <c r="D13" t="n">
-        <v>309005.77</v>
+        <v>336875.77</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>39.6%</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>61761</v>
+        <v>65761</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>19.5%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>247244.77</v>
+        <v>271114.77</v>
       </c>
     </row>
     <row r="14">
@@ -881,11 +881,11 @@
         <v>800000</v>
       </c>
       <c r="D14" t="n">
-        <v>214429.3</v>
+        <v>216621.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>26.8%</t>
+          <t>27.1%</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -893,11 +893,11 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>196051.3</v>
+        <v>198243.3</v>
       </c>
     </row>
     <row r="15">
@@ -915,11 +915,11 @@
         <v>260000</v>
       </c>
       <c r="D15" t="n">
-        <v>155694</v>
+        <v>164092</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>59.9%</t>
+          <t>63.1%</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -927,11 +927,11 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>140388</v>
+        <v>148786</v>
       </c>
     </row>
     <row r="16">
@@ -983,11 +983,11 @@
         <v>700000</v>
       </c>
       <c r="D17" t="n">
-        <v>258047.94</v>
+        <v>288451.94</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>36.9%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -995,11 +995,11 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>222181.94</v>
+        <v>252585.94</v>
       </c>
     </row>
     <row r="18">
@@ -1017,11 +1017,11 @@
         <v>800000</v>
       </c>
       <c r="D18" t="n">
-        <v>391172.71</v>
+        <v>419490.71</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>48.9%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -1029,11 +1029,11 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>339616.71</v>
+        <v>367934.71</v>
       </c>
     </row>
     <row r="19">
@@ -1051,23 +1051,23 @@
         <v>850000</v>
       </c>
       <c r="D19" t="n">
-        <v>213091.54</v>
+        <v>224526.54</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>25.1%</t>
+          <t>26.4%</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>143498</v>
+        <v>143527</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>63.9%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>69593.54000000001</v>
+        <v>80999.54000000001</v>
       </c>
     </row>
     <row r="20">
@@ -1085,7 +1085,7 @@
         <v>700000</v>
       </c>
       <c r="D20" t="n">
-        <v>368141.99</v>
+        <v>368539.99</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>295141.99</v>
+        <v>295539.99</v>
       </c>
     </row>
   </sheetData>

--- a/导出_按分组.xlsx
+++ b/导出_按分组.xlsx
@@ -473,23 +473,23 @@
         <v>1000000</v>
       </c>
       <c r="D2" t="n">
-        <v>233638.18</v>
+        <v>303384.18</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>30.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>151290.67</v>
+        <v>155459.67</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>64.8%</t>
+          <t>51.2%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>82347.50999999998</v>
+        <v>147924.51</v>
       </c>
     </row>
     <row r="3">
@@ -507,7 +507,7 @@
         <v>100000</v>
       </c>
       <c r="D3" t="n">
-        <v>20351.2</v>
+        <v>20389.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -515,15 +515,15 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>27035</v>
+        <v>30421</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>132.8%</t>
+          <t>149.2%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>-6683.799999999999</v>
+        <v>-10031.8</v>
       </c>
     </row>
     <row r="4">
@@ -541,23 +541,23 @@
         <v>800000</v>
       </c>
       <c r="D4" t="n">
-        <v>393033.02</v>
+        <v>408358.02</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>49.1%</t>
+          <t>51.0%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>122034.8</v>
+        <v>123086.8</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>31.0%</t>
+          <t>30.1%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>270998.22</v>
+        <v>285271.22</v>
       </c>
     </row>
     <row r="5">
@@ -575,7 +575,7 @@
         <v>650000</v>
       </c>
       <c r="D5" t="n">
-        <v>399527.17</v>
+        <v>399845.17</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>293351.17</v>
+        <v>293669.17</v>
       </c>
     </row>
     <row r="6">
@@ -609,23 +609,23 @@
         <v>700000</v>
       </c>
       <c r="D6" t="n">
-        <v>212385.99</v>
+        <v>253411.9</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>30.3%</t>
+          <t>36.2%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>63477.07</v>
+        <v>64218.07</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>29.9%</t>
+          <t>25.3%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>148908.92</v>
+        <v>189193.83</v>
       </c>
     </row>
     <row r="7">
@@ -643,23 +643,23 @@
         <v>550000</v>
       </c>
       <c r="D7" t="n">
-        <v>245788</v>
+        <v>258264</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>44.7%</t>
+          <t>47.0%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>61614</v>
+        <v>62250</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>25.1%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>184174</v>
+        <v>196014</v>
       </c>
     </row>
     <row r="8">
@@ -677,23 +677,23 @@
         <v>650000</v>
       </c>
       <c r="D8" t="n">
-        <v>290524.86</v>
+        <v>292471.86</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>44.7%</t>
+          <t>45.0%</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>33303</v>
+        <v>33474</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>257221.86</v>
+        <v>258997.86</v>
       </c>
     </row>
     <row r="9">
@@ -711,23 +711,23 @@
         <v>1700000</v>
       </c>
       <c r="D9" t="n">
-        <v>680573</v>
+        <v>670632</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>146924</v>
+        <v>160124</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>23.9%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>533649</v>
+        <v>510508</v>
       </c>
     </row>
     <row r="10">
@@ -745,11 +745,11 @@
         <v>2000000</v>
       </c>
       <c r="D10" t="n">
-        <v>1081485</v>
+        <v>1107289.5</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>54.1%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1081485</v>
+        <v>1107289.5</v>
       </c>
     </row>
     <row r="11">
@@ -779,11 +779,11 @@
         <v>450000</v>
       </c>
       <c r="D11" t="n">
-        <v>214233.63</v>
+        <v>231252.63</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>47.6%</t>
+          <t>51.4%</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -791,11 +791,11 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>189125.63</v>
+        <v>206144.63</v>
       </c>
     </row>
     <row r="12">
@@ -813,11 +813,11 @@
         <v>450000</v>
       </c>
       <c r="D12" t="n">
-        <v>202915</v>
+        <v>246715</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>45.1%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -825,11 +825,11 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1.0%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>200917</v>
+        <v>244717</v>
       </c>
     </row>
     <row r="13">
@@ -847,23 +847,23 @@
         <v>850000</v>
       </c>
       <c r="D13" t="n">
-        <v>336875.77</v>
+        <v>379795.77</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>44.7%</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>65761</v>
+        <v>76509</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>19.5%</t>
+          <t>20.1%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>271114.77</v>
+        <v>303286.77</v>
       </c>
     </row>
     <row r="14">
@@ -881,7 +881,7 @@
         <v>800000</v>
       </c>
       <c r="D14" t="n">
-        <v>216621.3</v>
+        <v>217019.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -889,15 +889,15 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>18378</v>
+        <v>21378</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>8.5%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>198243.3</v>
+        <v>195641.3</v>
       </c>
     </row>
     <row r="15">
@@ -915,11 +915,11 @@
         <v>260000</v>
       </c>
       <c r="D15" t="n">
-        <v>164092</v>
+        <v>164490</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>63.1%</t>
+          <t>63.3%</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>148786</v>
+        <v>149184</v>
       </c>
     </row>
     <row r="16">
@@ -949,23 +949,23 @@
         <v>400000</v>
       </c>
       <c r="D16" t="n">
-        <v>218434.98</v>
+        <v>218833.97</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>10200</v>
+        <v>43000</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>4.7%</t>
+          <t>19.6%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>208234.98</v>
+        <v>175833.97</v>
       </c>
     </row>
     <row r="17">
@@ -983,11 +983,11 @@
         <v>700000</v>
       </c>
       <c r="D17" t="n">
-        <v>288451.94</v>
+        <v>296047.94</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>42.3%</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -995,11 +995,11 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>252585.94</v>
+        <v>260181.94</v>
       </c>
     </row>
     <row r="18">
@@ -1017,23 +1017,23 @@
         <v>800000</v>
       </c>
       <c r="D18" t="n">
-        <v>419490.71</v>
+        <v>420707.71</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>52.6%</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>51556</v>
+        <v>115542</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>27.5%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>367934.71</v>
+        <v>305165.71</v>
       </c>
     </row>
     <row r="19">
@@ -1051,11 +1051,11 @@
         <v>850000</v>
       </c>
       <c r="D19" t="n">
-        <v>224526.54</v>
+        <v>232443.54</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>26.4%</t>
+          <t>27.3%</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -1063,11 +1063,11 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>63.9%</t>
+          <t>61.7%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>80999.54000000001</v>
+        <v>88916.54000000001</v>
       </c>
     </row>
     <row r="20">
@@ -1085,23 +1085,23 @@
         <v>700000</v>
       </c>
       <c r="D20" t="n">
-        <v>368539.99</v>
+        <v>385933.99</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>52.6%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>73000</v>
+        <v>76000</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>19.8%</t>
+          <t>19.7%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>295539.99</v>
+        <v>309933.99</v>
       </c>
     </row>
   </sheetData>

--- a/导出_按分组.xlsx
+++ b/导出_按分组.xlsx
@@ -779,7 +779,7 @@
         <v>450000</v>
       </c>
       <c r="D11" t="n">
-        <v>231252.63</v>
+        <v>231516.94</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -791,11 +791,11 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>206144.63</v>
+        <v>206408.94</v>
       </c>
     </row>
     <row r="12">
@@ -1017,11 +1017,11 @@
         <v>800000</v>
       </c>
       <c r="D18" t="n">
-        <v>420707.71</v>
+        <v>442207.71</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>52.6%</t>
+          <t>55.3%</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -1029,11 +1029,11 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>26.1%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>305165.71</v>
+        <v>326665.71</v>
       </c>
     </row>
     <row r="19">

--- a/导出_按分组.xlsx
+++ b/导出_按分组.xlsx
@@ -473,23 +473,23 @@
         <v>1000000</v>
       </c>
       <c r="D2" t="n">
-        <v>303384.18</v>
+        <v>358707.18</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>30.3%</t>
+          <t>35.9%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>155459.67</v>
+        <v>186034.67</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>51.2%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>147924.51</v>
+        <v>172672.51</v>
       </c>
     </row>
     <row r="3">
@@ -507,23 +507,23 @@
         <v>100000</v>
       </c>
       <c r="D3" t="n">
-        <v>20389.2</v>
+        <v>20493.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>20.5%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>30421</v>
+        <v>35429</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>149.2%</t>
+          <t>172.9%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>-10031.8</v>
+        <v>-14935.8</v>
       </c>
     </row>
     <row r="4">
@@ -541,23 +541,23 @@
         <v>800000</v>
       </c>
       <c r="D4" t="n">
-        <v>408358.02</v>
+        <v>523438.87</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>51.0%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>123086.8</v>
+        <v>125376.8</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>30.1%</t>
+          <t>24.0%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>285271.22</v>
+        <v>398062.07</v>
       </c>
     </row>
     <row r="5">
@@ -575,23 +575,23 @@
         <v>650000</v>
       </c>
       <c r="D5" t="n">
-        <v>399845.17</v>
+        <v>410568.17</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>63.2%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>106176</v>
+        <v>106195</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>26.6%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>293669.17</v>
+        <v>304373.17</v>
       </c>
     </row>
     <row r="6">
@@ -609,23 +609,23 @@
         <v>700000</v>
       </c>
       <c r="D6" t="n">
-        <v>253411.9</v>
+        <v>284437.9</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>36.2%</t>
+          <t>40.6%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>64218.07</v>
+        <v>70080.98000000001</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>25.3%</t>
+          <t>24.6%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>189193.83</v>
+        <v>214356.92</v>
       </c>
     </row>
     <row r="7">
@@ -643,23 +643,23 @@
         <v>550000</v>
       </c>
       <c r="D7" t="n">
-        <v>258264</v>
+        <v>288379</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>47.0%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>62250</v>
+        <v>63732</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>22.1%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>196014</v>
+        <v>224647</v>
       </c>
     </row>
     <row r="8">
@@ -677,23 +677,23 @@
         <v>650000</v>
       </c>
       <c r="D8" t="n">
-        <v>292471.86</v>
+        <v>311321.76</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>45.0%</t>
+          <t>47.9%</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>33474</v>
+        <v>65388</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>21.0%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>258997.86</v>
+        <v>245933.76</v>
       </c>
     </row>
     <row r="9">
@@ -711,23 +711,23 @@
         <v>1700000</v>
       </c>
       <c r="D9" t="n">
-        <v>670632</v>
+        <v>738629</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>43.4%</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>160124</v>
+        <v>170124</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>23.9%</t>
+          <t>23.0%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>510508</v>
+        <v>568505</v>
       </c>
     </row>
     <row r="10">
@@ -745,11 +745,11 @@
         <v>2000000</v>
       </c>
       <c r="D10" t="n">
-        <v>1107289.5</v>
+        <v>1385492.57</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>69.3%</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1107289.5</v>
+        <v>1385492.57</v>
       </c>
     </row>
     <row r="11">
@@ -779,11 +779,11 @@
         <v>450000</v>
       </c>
       <c r="D11" t="n">
-        <v>231516.94</v>
+        <v>258196.96</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>51.4%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -791,11 +791,11 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>206408.94</v>
+        <v>233088.96</v>
       </c>
     </row>
     <row r="12">
@@ -813,11 +813,11 @@
         <v>450000</v>
       </c>
       <c r="D12" t="n">
-        <v>246715</v>
+        <v>284528</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>63.2%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -825,11 +825,11 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>244717</v>
+        <v>282530</v>
       </c>
     </row>
     <row r="13">
@@ -847,11 +847,11 @@
         <v>850000</v>
       </c>
       <c r="D13" t="n">
-        <v>379795.77</v>
+        <v>502163.76</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>44.7%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -859,11 +859,11 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>20.1%</t>
+          <t>15.2%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>303286.77</v>
+        <v>425654.76</v>
       </c>
     </row>
     <row r="14">
@@ -881,23 +881,23 @@
         <v>800000</v>
       </c>
       <c r="D14" t="n">
-        <v>217019.3</v>
+        <v>334007.7</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>27.1%</t>
+          <t>41.8%</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>21378</v>
+        <v>31378</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>195641.3</v>
+        <v>302629.7</v>
       </c>
     </row>
     <row r="15">
@@ -915,11 +915,11 @@
         <v>260000</v>
       </c>
       <c r="D15" t="n">
-        <v>164490</v>
+        <v>171426</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>63.3%</t>
+          <t>65.9%</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -927,11 +927,11 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>149184</v>
+        <v>156120</v>
       </c>
     </row>
     <row r="16">
@@ -949,11 +949,11 @@
         <v>400000</v>
       </c>
       <c r="D16" t="n">
-        <v>218833.97</v>
+        <v>250448.97</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>62.6%</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -961,11 +961,11 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>19.6%</t>
+          <t>17.2%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>175833.97</v>
+        <v>207448.97</v>
       </c>
     </row>
     <row r="17">
@@ -983,23 +983,23 @@
         <v>700000</v>
       </c>
       <c r="D17" t="n">
-        <v>296047.94</v>
+        <v>381202.14</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>42.3%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>35866</v>
+        <v>42366</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>260181.94</v>
+        <v>338836.14</v>
       </c>
     </row>
     <row r="18">
@@ -1017,23 +1017,23 @@
         <v>800000</v>
       </c>
       <c r="D18" t="n">
-        <v>442207.71</v>
+        <v>542985.72</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>67.9%</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>115542</v>
+        <v>128005.48</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>26.1%</t>
+          <t>23.6%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>326665.71</v>
+        <v>414980.24</v>
       </c>
     </row>
     <row r="19">
@@ -1051,11 +1051,11 @@
         <v>850000</v>
       </c>
       <c r="D19" t="n">
-        <v>232443.54</v>
+        <v>300393.05</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>27.3%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -1063,11 +1063,11 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>61.7%</t>
+          <t>47.8%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>88916.54000000001</v>
+        <v>156866.05</v>
       </c>
     </row>
     <row r="20">
@@ -1085,11 +1085,11 @@
         <v>700000</v>
       </c>
       <c r="D20" t="n">
-        <v>385933.99</v>
+        <v>490146.99</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>70.0%</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -1097,11 +1097,11 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>19.7%</t>
+          <t>15.5%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>309933.99</v>
+        <v>414146.99</v>
       </c>
     </row>
   </sheetData>

--- a/导出_按分组.xlsx
+++ b/导出_按分组.xlsx
@@ -473,23 +473,23 @@
         <v>1000000</v>
       </c>
       <c r="D2" t="n">
-        <v>358707.18</v>
+        <v>396266.18</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>35.9%</t>
+          <t>39.6%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>186034.67</v>
+        <v>251415.67</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>63.4%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>172672.51</v>
+        <v>144850.51</v>
       </c>
     </row>
     <row r="3">
@@ -507,7 +507,7 @@
         <v>100000</v>
       </c>
       <c r="D3" t="n">
-        <v>20493.2</v>
+        <v>20518.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -515,15 +515,15 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>35429</v>
+        <v>35448</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>172.9%</t>
+          <t>172.8%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>-14935.8</v>
+        <v>-14929.8</v>
       </c>
     </row>
     <row r="4">
@@ -541,23 +541,23 @@
         <v>800000</v>
       </c>
       <c r="D4" t="n">
-        <v>523438.87</v>
+        <v>633382.87</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>79.2%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>125376.8</v>
+        <v>158586.8</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>24.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>398062.07</v>
+        <v>474796.07</v>
       </c>
     </row>
     <row r="5">
@@ -575,23 +575,23 @@
         <v>650000</v>
       </c>
       <c r="D5" t="n">
-        <v>410568.17</v>
+        <v>421312.17</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>63.2%</t>
+          <t>64.8%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>106195</v>
+        <v>111094</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>26.4%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>304373.17</v>
+        <v>310218.17</v>
       </c>
     </row>
     <row r="6">
@@ -609,23 +609,23 @@
         <v>700000</v>
       </c>
       <c r="D6" t="n">
-        <v>284437.9</v>
+        <v>290941.9</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>40.6%</t>
+          <t>41.6%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>70080.98000000001</v>
+        <v>75540.98</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>24.6%</t>
+          <t>26.0%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>214356.92</v>
+        <v>215400.92</v>
       </c>
     </row>
     <row r="7">
@@ -643,23 +643,23 @@
         <v>550000</v>
       </c>
       <c r="D7" t="n">
-        <v>288379</v>
+        <v>299151</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>54.4%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>63732</v>
+        <v>68243</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>22.1%</t>
+          <t>22.8%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>224647</v>
+        <v>230908</v>
       </c>
     </row>
     <row r="8">
@@ -677,23 +677,23 @@
         <v>650000</v>
       </c>
       <c r="D8" t="n">
-        <v>311321.76</v>
+        <v>345862.76</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>47.9%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>65388</v>
+        <v>76166.33</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>22.0%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>245933.76</v>
+        <v>269696.43</v>
       </c>
     </row>
     <row r="9">
@@ -711,23 +711,23 @@
         <v>1700000</v>
       </c>
       <c r="D9" t="n">
-        <v>738629</v>
+        <v>788848</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>43.4%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>170124</v>
+        <v>190872</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>23.0%</t>
+          <t>24.2%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>568505</v>
+        <v>597976</v>
       </c>
     </row>
     <row r="10">
@@ -745,11 +745,11 @@
         <v>2000000</v>
       </c>
       <c r="D10" t="n">
-        <v>1385492.57</v>
+        <v>1389928.57</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>69.3%</t>
+          <t>69.5%</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1385492.57</v>
+        <v>1389928.57</v>
       </c>
     </row>
     <row r="11">
@@ -779,23 +779,23 @@
         <v>450000</v>
       </c>
       <c r="D11" t="n">
-        <v>258196.96</v>
+        <v>267697.95</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>59.5%</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>25108</v>
+        <v>41908</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>233088.96</v>
+        <v>225789.95</v>
       </c>
     </row>
     <row r="12">
@@ -813,15 +813,15 @@
         <v>450000</v>
       </c>
       <c r="D12" t="n">
-        <v>284528</v>
+        <v>325324</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>63.2%</t>
+          <t>72.3%</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1998</v>
+        <v>2228</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>282530</v>
+        <v>323096</v>
       </c>
     </row>
     <row r="13">
@@ -847,23 +847,23 @@
         <v>850000</v>
       </c>
       <c r="D13" t="n">
-        <v>502163.76</v>
+        <v>539386.86</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>63.5%</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>76509</v>
+        <v>76609</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>15.2%</t>
+          <t>14.2%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>425654.76</v>
+        <v>462777.86</v>
       </c>
     </row>
     <row r="14">
@@ -881,23 +881,23 @@
         <v>800000</v>
       </c>
       <c r="D14" t="n">
-        <v>334007.7</v>
+        <v>350904.7</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>41.8%</t>
+          <t>43.9%</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>31378</v>
+        <v>45378</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>302629.7</v>
+        <v>305526.7</v>
       </c>
     </row>
     <row r="15">
@@ -915,7 +915,7 @@
         <v>260000</v>
       </c>
       <c r="D15" t="n">
-        <v>171426</v>
+        <v>171445</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>156120</v>
+        <v>156139</v>
       </c>
     </row>
     <row r="16">
@@ -949,11 +949,11 @@
         <v>400000</v>
       </c>
       <c r="D16" t="n">
-        <v>250448.97</v>
+        <v>283665.97</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>62.6%</t>
+          <t>70.9%</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -961,11 +961,11 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>15.2%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>207448.97</v>
+        <v>240665.97</v>
       </c>
     </row>
     <row r="17">
@@ -983,11 +983,11 @@
         <v>700000</v>
       </c>
       <c r="D17" t="n">
-        <v>381202.14</v>
+        <v>382432.35</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>338836.14</v>
+        <v>340066.35</v>
       </c>
     </row>
     <row r="18">
@@ -1017,11 +1017,11 @@
         <v>800000</v>
       </c>
       <c r="D18" t="n">
-        <v>542985.72</v>
+        <v>572024.72</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>67.9%</t>
+          <t>71.5%</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -1029,11 +1029,11 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>23.6%</t>
+          <t>22.4%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>414980.24</v>
+        <v>444019.24</v>
       </c>
     </row>
     <row r="19">
@@ -1051,23 +1051,23 @@
         <v>850000</v>
       </c>
       <c r="D19" t="n">
-        <v>300393.05</v>
+        <v>302632.33</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>35.6%</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>143527</v>
+        <v>145527</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>47.8%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>156866.05</v>
+        <v>157105.33</v>
       </c>
     </row>
     <row r="20">
@@ -1085,23 +1085,23 @@
         <v>700000</v>
       </c>
       <c r="D20" t="n">
-        <v>490146.99</v>
+        <v>587045.99</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>83.9%</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>76000</v>
+        <v>87100</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>15.5%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>414146.99</v>
+        <v>499945.99</v>
       </c>
     </row>
   </sheetData>

--- a/导出_按分组.xlsx
+++ b/导出_按分组.xlsx
@@ -473,23 +473,23 @@
         <v>1000000</v>
       </c>
       <c r="D2" t="n">
-        <v>396266.18</v>
+        <v>414285.18</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>41.4%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>251415.67</v>
+        <v>251988.67</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>63.4%</t>
+          <t>60.8%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>144850.51</v>
+        <v>162296.51</v>
       </c>
     </row>
     <row r="3">
@@ -507,11 +507,11 @@
         <v>100000</v>
       </c>
       <c r="D3" t="n">
-        <v>20518.2</v>
+        <v>20556.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>20.5%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -519,11 +519,11 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>172.8%</t>
+          <t>172.4%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>-14929.8</v>
+        <v>-14891.8</v>
       </c>
     </row>
     <row r="4">
@@ -541,23 +541,23 @@
         <v>800000</v>
       </c>
       <c r="D4" t="n">
-        <v>633382.87</v>
+        <v>656623.21</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>79.2%</t>
+          <t>82.1%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>158586.8</v>
+        <v>166289.8</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>25.3%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>474796.07</v>
+        <v>490333.41</v>
       </c>
     </row>
     <row r="5">
@@ -575,23 +575,23 @@
         <v>650000</v>
       </c>
       <c r="D5" t="n">
-        <v>421312.17</v>
+        <v>429517.17</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>64.8%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>111094</v>
+        <v>111294</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>26.4%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>310218.17</v>
+        <v>318223.17</v>
       </c>
     </row>
     <row r="6">
@@ -609,15 +609,15 @@
         <v>700000</v>
       </c>
       <c r="D6" t="n">
-        <v>290941.9</v>
+        <v>311882.9</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>41.6%</t>
+          <t>44.6%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>75540.98</v>
+        <v>80952.97999999998</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -625,7 +625,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>215400.92</v>
+        <v>230929.92</v>
       </c>
     </row>
     <row r="7">
@@ -643,23 +643,23 @@
         <v>550000</v>
       </c>
       <c r="D7" t="n">
-        <v>299151</v>
+        <v>304463</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>54.4%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>68243</v>
+        <v>75283</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>22.8%</t>
+          <t>24.7%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>230908</v>
+        <v>229180</v>
       </c>
     </row>
     <row r="8">
@@ -677,23 +677,23 @@
         <v>650000</v>
       </c>
       <c r="D8" t="n">
-        <v>345862.76</v>
+        <v>364289.76</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>76166.33</v>
+        <v>81517.33</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>22.0%</t>
+          <t>22.4%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>269696.43</v>
+        <v>282772.43</v>
       </c>
     </row>
     <row r="9">
@@ -711,23 +711,23 @@
         <v>1700000</v>
       </c>
       <c r="D9" t="n">
-        <v>788848</v>
+        <v>811497</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>47.7%</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>190872</v>
+        <v>216270</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>24.2%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>597976</v>
+        <v>595227</v>
       </c>
     </row>
     <row r="10">
@@ -745,11 +745,11 @@
         <v>2000000</v>
       </c>
       <c r="D10" t="n">
-        <v>1389928.57</v>
+        <v>1410537.17</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>69.5%</t>
+          <t>70.5%</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1389928.57</v>
+        <v>1410537.17</v>
       </c>
     </row>
     <row r="11">
@@ -779,23 +779,23 @@
         <v>450000</v>
       </c>
       <c r="D11" t="n">
-        <v>267697.95</v>
+        <v>290091.95</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>59.5%</t>
+          <t>64.5%</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>41908</v>
+        <v>45908</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>15.8%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>225789.95</v>
+        <v>244183.95</v>
       </c>
     </row>
     <row r="12">
@@ -813,7 +813,7 @@
         <v>450000</v>
       </c>
       <c r="D12" t="n">
-        <v>325324</v>
+        <v>325343</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>323096</v>
+        <v>323115</v>
       </c>
     </row>
     <row r="13">
@@ -847,11 +847,11 @@
         <v>850000</v>
       </c>
       <c r="D13" t="n">
-        <v>539386.86</v>
+        <v>540830.86</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>63.5%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>462777.86</v>
+        <v>464221.86</v>
       </c>
     </row>
     <row r="14">
@@ -881,11 +881,11 @@
         <v>800000</v>
       </c>
       <c r="D14" t="n">
-        <v>350904.7</v>
+        <v>369612.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>43.9%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -893,11 +893,11 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>305526.7</v>
+        <v>324234.6</v>
       </c>
     </row>
     <row r="15">
@@ -915,11 +915,11 @@
         <v>260000</v>
       </c>
       <c r="D15" t="n">
-        <v>171445</v>
+        <v>181405</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>65.9%</t>
+          <t>69.8%</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -927,11 +927,11 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>8.4%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>156139</v>
+        <v>166099</v>
       </c>
     </row>
     <row r="16">
@@ -949,23 +949,23 @@
         <v>400000</v>
       </c>
       <c r="D16" t="n">
-        <v>283665.97</v>
+        <v>302861.97</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>70.9%</t>
+          <t>75.7%</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>43000</v>
+        <v>53000</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>15.2%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>240665.97</v>
+        <v>249861.97</v>
       </c>
     </row>
     <row r="17">
@@ -983,11 +983,11 @@
         <v>700000</v>
       </c>
       <c r="D17" t="n">
-        <v>382432.35</v>
+        <v>383807.35</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -995,11 +995,11 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>340066.35</v>
+        <v>341441.35</v>
       </c>
     </row>
     <row r="18">
@@ -1017,11 +1017,11 @@
         <v>800000</v>
       </c>
       <c r="D18" t="n">
-        <v>572024.72</v>
+        <v>602062.72</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>71.5%</t>
+          <t>75.3%</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -1029,11 +1029,11 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>22.4%</t>
+          <t>21.3%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>444019.24</v>
+        <v>474057.24</v>
       </c>
     </row>
     <row r="19">
@@ -1051,11 +1051,11 @@
         <v>850000</v>
       </c>
       <c r="D19" t="n">
-        <v>302632.33</v>
+        <v>313887.09</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>35.6%</t>
+          <t>36.9%</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -1063,11 +1063,11 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>157105.33</v>
+        <v>168360.09</v>
       </c>
     </row>
     <row r="20">
@@ -1085,11 +1085,11 @@
         <v>700000</v>
       </c>
       <c r="D20" t="n">
-        <v>587045.99</v>
+        <v>637819.99</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>83.9%</t>
+          <t>91.1%</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -1097,11 +1097,11 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>499945.99</v>
+        <v>550719.99</v>
       </c>
     </row>
   </sheetData>

--- a/导出_按分组.xlsx
+++ b/导出_按分组.xlsx
@@ -473,23 +473,23 @@
         <v>1000000</v>
       </c>
       <c r="D2" t="n">
-        <v>414285.18</v>
+        <v>421274.18</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>41.4%</t>
+          <t>42.1%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>251988.67</v>
+        <v>252344.67</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>60.8%</t>
+          <t>59.9%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>162296.51</v>
+        <v>168929.51</v>
       </c>
     </row>
     <row r="3">
@@ -507,23 +507,23 @@
         <v>100000</v>
       </c>
       <c r="D3" t="n">
-        <v>20556.2</v>
+        <v>20662.41</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>20.7%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>35448</v>
+        <v>35467</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>172.4%</t>
+          <t>171.6%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>-14891.8</v>
+        <v>-14804.59</v>
       </c>
     </row>
     <row r="4">
@@ -541,23 +541,23 @@
         <v>800000</v>
       </c>
       <c r="D4" t="n">
-        <v>656623.21</v>
+        <v>663497.21</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>82.1%</t>
+          <t>82.9%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>166289.8</v>
+        <v>171572.8</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>25.3%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>490333.41</v>
+        <v>491924.41</v>
       </c>
     </row>
     <row r="5">
@@ -575,23 +575,23 @@
         <v>650000</v>
       </c>
       <c r="D5" t="n">
-        <v>429517.17</v>
+        <v>473344.17</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>72.8%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>111294</v>
+        <v>111332</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>318223.17</v>
+        <v>362012.17</v>
       </c>
     </row>
     <row r="6">
@@ -609,23 +609,23 @@
         <v>700000</v>
       </c>
       <c r="D6" t="n">
-        <v>311882.9</v>
+        <v>327663.9</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>44.6%</t>
+          <t>46.8%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>80952.97999999998</v>
+        <v>81645.98</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>26.0%</t>
+          <t>24.9%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>230929.92</v>
+        <v>246017.92</v>
       </c>
     </row>
     <row r="7">
@@ -643,23 +643,23 @@
         <v>550000</v>
       </c>
       <c r="D7" t="n">
-        <v>304463</v>
+        <v>331414</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>60.3%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>75283</v>
+        <v>106495</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>24.7%</t>
+          <t>32.1%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>229180</v>
+        <v>224919</v>
       </c>
     </row>
     <row r="8">
@@ -677,23 +677,23 @@
         <v>650000</v>
       </c>
       <c r="D8" t="n">
-        <v>364289.76</v>
+        <v>369881.76</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>56.9%</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>81517.33</v>
+        <v>81688.33</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>22.4%</t>
+          <t>22.1%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>282772.43</v>
+        <v>288193.43</v>
       </c>
     </row>
     <row r="9">
@@ -711,23 +711,23 @@
         <v>1700000</v>
       </c>
       <c r="D9" t="n">
-        <v>811497</v>
+        <v>880213</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>47.7%</t>
+          <t>51.8%</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>216270</v>
+        <v>219270</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>24.9%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>595227</v>
+        <v>660943</v>
       </c>
     </row>
     <row r="10">
@@ -745,11 +745,11 @@
         <v>2000000</v>
       </c>
       <c r="D10" t="n">
-        <v>1410537.17</v>
+        <v>1484241.95</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>70.5%</t>
+          <t>74.2%</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1410537.17</v>
+        <v>1484241.95</v>
       </c>
     </row>
     <row r="11">
@@ -779,11 +779,11 @@
         <v>450000</v>
       </c>
       <c r="D11" t="n">
-        <v>290091.95</v>
+        <v>303708.95</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>64.5%</t>
+          <t>67.5%</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -791,11 +791,11 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>15.8%</t>
+          <t>15.1%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>244183.95</v>
+        <v>257800.95</v>
       </c>
     </row>
     <row r="12">
@@ -813,11 +813,11 @@
         <v>450000</v>
       </c>
       <c r="D12" t="n">
-        <v>325343</v>
+        <v>325741</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>72.3%</t>
+          <t>72.4%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>323115</v>
+        <v>323513</v>
       </c>
     </row>
     <row r="13">
@@ -847,11 +847,11 @@
         <v>850000</v>
       </c>
       <c r="D13" t="n">
-        <v>540830.86</v>
+        <v>553607.5599999999</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>65.1%</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -859,11 +859,11 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>13.8%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>464221.86</v>
+        <v>476998.5599999999</v>
       </c>
     </row>
     <row r="14">
@@ -881,11 +881,11 @@
         <v>800000</v>
       </c>
       <c r="D14" t="n">
-        <v>369612.6</v>
+        <v>370806.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -893,11 +893,11 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>324234.6</v>
+        <v>325428.6</v>
       </c>
     </row>
     <row r="15">
@@ -915,11 +915,11 @@
         <v>260000</v>
       </c>
       <c r="D15" t="n">
-        <v>181405</v>
+        <v>195001</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>69.8%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -927,11 +927,11 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>8.4%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>166099</v>
+        <v>179695</v>
       </c>
     </row>
     <row r="16">
@@ -949,11 +949,11 @@
         <v>400000</v>
       </c>
       <c r="D16" t="n">
-        <v>302861.97</v>
+        <v>311278.97</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>75.7%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -961,11 +961,11 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>17.5%</t>
+          <t>17.0%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>249861.97</v>
+        <v>258278.97</v>
       </c>
     </row>
     <row r="17">
@@ -983,23 +983,23 @@
         <v>700000</v>
       </c>
       <c r="D17" t="n">
-        <v>383807.35</v>
+        <v>392461.35</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>56.1%</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>42366</v>
+        <v>79166</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>20.2%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>341441.35</v>
+        <v>313295.35</v>
       </c>
     </row>
     <row r="18">
@@ -1017,23 +1017,23 @@
         <v>800000</v>
       </c>
       <c r="D18" t="n">
-        <v>602062.72</v>
+        <v>626060.72</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>75.3%</t>
+          <t>78.3%</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>128005.48</v>
+        <v>152805.48</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>21.3%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>474057.24</v>
+        <v>473255.24</v>
       </c>
     </row>
     <row r="19">
@@ -1051,11 +1051,11 @@
         <v>850000</v>
       </c>
       <c r="D19" t="n">
-        <v>313887.09</v>
+        <v>343485.09</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>36.9%</t>
+          <t>40.4%</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -1063,11 +1063,11 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>42.4%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>168360.09</v>
+        <v>197958.09</v>
       </c>
     </row>
     <row r="20">
@@ -1085,23 +1085,23 @@
         <v>700000</v>
       </c>
       <c r="D20" t="n">
-        <v>637819.99</v>
+        <v>650805.99</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>91.1%</t>
+          <t>93.0%</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>87100</v>
+        <v>95100</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>14.6%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>550719.99</v>
+        <v>555705.99</v>
       </c>
     </row>
   </sheetData>

--- a/导出_按分组.xlsx
+++ b/导出_按分组.xlsx
@@ -473,23 +473,23 @@
         <v>1000000</v>
       </c>
       <c r="D2" t="n">
-        <v>421274.18</v>
+        <v>468658.18</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>42.1%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>252344.67</v>
+        <v>252562.67</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>59.9%</t>
+          <t>53.9%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>168929.51</v>
+        <v>216095.51</v>
       </c>
     </row>
     <row r="3">
@@ -507,11 +507,11 @@
         <v>100000</v>
       </c>
       <c r="D3" t="n">
-        <v>20662.41</v>
+        <v>20951.41</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>20.7%</t>
+          <t>21.0%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -519,11 +519,11 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>171.6%</t>
+          <t>169.3%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>-14804.59</v>
+        <v>-14515.59</v>
       </c>
     </row>
     <row r="4">
@@ -541,23 +541,23 @@
         <v>800000</v>
       </c>
       <c r="D4" t="n">
-        <v>663497.21</v>
+        <v>682632.21</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>82.9%</t>
+          <t>85.3%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>171572.8</v>
+        <v>175795.8</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>25.8%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>491924.41</v>
+        <v>506836.41</v>
       </c>
     </row>
     <row r="5">
@@ -575,23 +575,23 @@
         <v>650000</v>
       </c>
       <c r="D5" t="n">
-        <v>473344.17</v>
+        <v>483217.17</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>72.8%</t>
+          <t>74.3%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>111332</v>
+        <v>127387</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>26.4%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>362012.17</v>
+        <v>355830.17</v>
       </c>
     </row>
     <row r="6">
@@ -609,23 +609,23 @@
         <v>700000</v>
       </c>
       <c r="D6" t="n">
-        <v>327663.9</v>
+        <v>392958.95</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>56.1%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>81645.98</v>
+        <v>105617.98</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>24.9%</t>
+          <t>26.9%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>246017.92</v>
+        <v>287340.97</v>
       </c>
     </row>
     <row r="7">
@@ -643,23 +643,23 @@
         <v>550000</v>
       </c>
       <c r="D7" t="n">
-        <v>331414</v>
+        <v>352268</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>60.3%</t>
+          <t>64.0%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>106495</v>
+        <v>107608</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>32.1%</t>
+          <t>30.5%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>224919</v>
+        <v>244660</v>
       </c>
     </row>
     <row r="8">
@@ -677,23 +677,23 @@
         <v>650000</v>
       </c>
       <c r="D8" t="n">
-        <v>369881.76</v>
+        <v>372143.76</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>56.9%</t>
+          <t>57.3%</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>81688.33</v>
+        <v>81773.33</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>22.1%</t>
+          <t>22.0%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>288193.43</v>
+        <v>290370.43</v>
       </c>
     </row>
     <row r="9">
@@ -711,23 +711,23 @@
         <v>1700000</v>
       </c>
       <c r="D9" t="n">
-        <v>880213</v>
+        <v>923993</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>51.8%</t>
+          <t>54.4%</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>219270</v>
+        <v>236268</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>24.9%</t>
+          <t>25.6%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>660943</v>
+        <v>687725</v>
       </c>
     </row>
     <row r="10">
@@ -745,11 +745,11 @@
         <v>2000000</v>
       </c>
       <c r="D10" t="n">
-        <v>1484241.95</v>
+        <v>1525402.95</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>74.2%</t>
+          <t>76.3%</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1484241.95</v>
+        <v>1525402.95</v>
       </c>
     </row>
     <row r="11">
@@ -779,15 +779,15 @@
         <v>450000</v>
       </c>
       <c r="D11" t="n">
-        <v>303708.95</v>
+        <v>305144.95</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>67.8%</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>45908</v>
+        <v>45927</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>257800.95</v>
+        <v>259217.95</v>
       </c>
     </row>
     <row r="12">
@@ -813,11 +813,11 @@
         <v>450000</v>
       </c>
       <c r="D12" t="n">
-        <v>325741</v>
+        <v>357440</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>72.4%</t>
+          <t>79.4%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -825,11 +825,11 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>323513</v>
+        <v>355212</v>
       </c>
     </row>
     <row r="13">
@@ -847,11 +847,11 @@
         <v>850000</v>
       </c>
       <c r="D13" t="n">
-        <v>553607.5599999999</v>
+        <v>565894.16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>65.1%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -859,11 +859,11 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>476998.5599999999</v>
+        <v>489285.16</v>
       </c>
     </row>
     <row r="14">
@@ -881,7 +881,7 @@
         <v>800000</v>
       </c>
       <c r="D14" t="n">
-        <v>370806.6</v>
+        <v>370825.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>325428.6</v>
+        <v>325447.6</v>
       </c>
     </row>
     <row r="15">
@@ -915,11 +915,11 @@
         <v>260000</v>
       </c>
       <c r="D15" t="n">
-        <v>195001</v>
+        <v>195418</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>75.2%</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>179695</v>
+        <v>180112</v>
       </c>
     </row>
     <row r="16">
@@ -949,11 +949,11 @@
         <v>400000</v>
       </c>
       <c r="D16" t="n">
-        <v>311278.97</v>
+        <v>321278.97</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>80.3%</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -961,11 +961,11 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>17.0%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>258278.97</v>
+        <v>268278.97</v>
       </c>
     </row>
     <row r="17">
@@ -983,23 +983,23 @@
         <v>700000</v>
       </c>
       <c r="D17" t="n">
-        <v>392461.35</v>
+        <v>427878.35</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>61.1%</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>79166</v>
+        <v>80166</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>20.2%</t>
+          <t>18.7%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>313295.35</v>
+        <v>347712.35</v>
       </c>
     </row>
     <row r="18">
@@ -1017,11 +1017,11 @@
         <v>800000</v>
       </c>
       <c r="D18" t="n">
-        <v>626060.72</v>
+        <v>634894.72</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>78.3%</t>
+          <t>79.4%</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -1029,11 +1029,11 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>24.4%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>473255.24</v>
+        <v>482089.24</v>
       </c>
     </row>
     <row r="19">
@@ -1051,11 +1051,11 @@
         <v>850000</v>
       </c>
       <c r="D19" t="n">
-        <v>343485.09</v>
+        <v>373985.09</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>40.4%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -1063,11 +1063,11 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>42.4%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>197958.09</v>
+        <v>228458.09</v>
       </c>
     </row>
     <row r="20">
@@ -1085,11 +1085,11 @@
         <v>700000</v>
       </c>
       <c r="D20" t="n">
-        <v>650805.99</v>
+        <v>689126.99</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>93.0%</t>
+          <t>98.4%</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -1097,11 +1097,11 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>13.8%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>555705.99</v>
+        <v>594026.99</v>
       </c>
     </row>
   </sheetData>

--- a/导出_按分组.xlsx
+++ b/导出_按分组.xlsx
@@ -473,23 +473,23 @@
         <v>1000000</v>
       </c>
       <c r="D2" t="n">
-        <v>468658.18</v>
+        <v>479612.18</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>48.0%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>252562.67</v>
+        <v>254102.67</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>53.9%</t>
+          <t>53.0%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>216095.51</v>
+        <v>225509.51</v>
       </c>
     </row>
     <row r="3">
@@ -507,23 +507,23 @@
         <v>100000</v>
       </c>
       <c r="D3" t="n">
-        <v>20951.41</v>
+        <v>16999.41</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>17.0%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>35467</v>
+        <v>40765</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>169.3%</t>
+          <t>239.8%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>-14515.59</v>
+        <v>-23765.59</v>
       </c>
     </row>
     <row r="4">
@@ -541,23 +541,23 @@
         <v>800000</v>
       </c>
       <c r="D4" t="n">
-        <v>682632.21</v>
+        <v>697528.46</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>85.3%</t>
+          <t>87.2%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>175795.8</v>
+        <v>176805.8</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>25.8%</t>
+          <t>25.3%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>506836.41</v>
+        <v>520722.66</v>
       </c>
     </row>
     <row r="5">
@@ -575,23 +575,23 @@
         <v>650000</v>
       </c>
       <c r="D5" t="n">
-        <v>483217.17</v>
+        <v>479572.17</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>74.3%</t>
+          <t>73.8%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>127387</v>
+        <v>128206</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>26.4%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>355830.17</v>
+        <v>351366.17</v>
       </c>
     </row>
     <row r="6">
@@ -609,23 +609,23 @@
         <v>700000</v>
       </c>
       <c r="D6" t="n">
-        <v>392958.95</v>
+        <v>402807.95</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>105617.98</v>
+        <v>110168.98</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>27.4%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>287340.97</v>
+        <v>292638.97</v>
       </c>
     </row>
     <row r="7">
@@ -643,23 +643,23 @@
         <v>550000</v>
       </c>
       <c r="D7" t="n">
-        <v>352268</v>
+        <v>371716</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>64.0%</t>
+          <t>67.6%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>107608</v>
+        <v>107859</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>30.5%</t>
+          <t>29.0%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>244660</v>
+        <v>263857</v>
       </c>
     </row>
     <row r="8">
@@ -677,23 +677,23 @@
         <v>650000</v>
       </c>
       <c r="D8" t="n">
-        <v>372143.76</v>
+        <v>376318.76</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>57.3%</t>
+          <t>57.9%</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>81773.33</v>
+        <v>82205.33</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>22.0%</t>
+          <t>21.8%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>290370.43</v>
+        <v>294113.43</v>
       </c>
     </row>
     <row r="9">
@@ -711,23 +711,23 @@
         <v>1700000</v>
       </c>
       <c r="D9" t="n">
-        <v>923993</v>
+        <v>932613</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>54.4%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>236268</v>
+        <v>287768</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>25.6%</t>
+          <t>30.9%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>687725</v>
+        <v>644845</v>
       </c>
     </row>
     <row r="10">
@@ -745,11 +745,11 @@
         <v>2000000</v>
       </c>
       <c r="D10" t="n">
-        <v>1525402.95</v>
+        <v>1587682.52</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>76.3%</t>
+          <t>79.4%</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1525402.95</v>
+        <v>1587682.52</v>
       </c>
     </row>
     <row r="11">
@@ -779,11 +779,11 @@
         <v>450000</v>
       </c>
       <c r="D11" t="n">
-        <v>305144.95</v>
+        <v>316751.95</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>67.8%</t>
+          <t>70.4%</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -791,11 +791,11 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>15.1%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>259217.95</v>
+        <v>270824.95</v>
       </c>
     </row>
     <row r="12">
@@ -813,11 +813,11 @@
         <v>450000</v>
       </c>
       <c r="D12" t="n">
-        <v>357440</v>
+        <v>367838.99</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>79.4%</t>
+          <t>81.7%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>355212</v>
+        <v>365610.99</v>
       </c>
     </row>
     <row r="13">
@@ -847,23 +847,23 @@
         <v>850000</v>
       </c>
       <c r="D13" t="n">
-        <v>565894.16</v>
+        <v>575311.16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>67.7%</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>76609</v>
+        <v>76809</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>13.4%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>489285.16</v>
+        <v>498502.16</v>
       </c>
     </row>
     <row r="14">
@@ -881,23 +881,23 @@
         <v>800000</v>
       </c>
       <c r="D14" t="n">
-        <v>370825.6</v>
+        <v>425019.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>53.1%</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>45378</v>
+        <v>77178</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>325447.6</v>
+        <v>347841.6</v>
       </c>
     </row>
     <row r="15">
@@ -915,15 +915,15 @@
         <v>260000</v>
       </c>
       <c r="D15" t="n">
-        <v>195418</v>
+        <v>196214</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>75.2%</t>
+          <t>75.5%</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>15306</v>
+        <v>15325</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>180112</v>
+        <v>180889</v>
       </c>
     </row>
     <row r="16">
@@ -949,11 +949,11 @@
         <v>400000</v>
       </c>
       <c r="D16" t="n">
-        <v>321278.97</v>
+        <v>322297.97</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>80.3%</t>
+          <t>80.6%</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -961,11 +961,11 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>16.5%</t>
+          <t>16.4%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>268278.97</v>
+        <v>269297.97</v>
       </c>
     </row>
     <row r="17">
@@ -983,11 +983,11 @@
         <v>700000</v>
       </c>
       <c r="D17" t="n">
-        <v>427878.35</v>
+        <v>439291.35</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>61.1%</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -995,11 +995,11 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>347712.35</v>
+        <v>359125.35</v>
       </c>
     </row>
     <row r="18">
@@ -1017,11 +1017,11 @@
         <v>800000</v>
       </c>
       <c r="D18" t="n">
-        <v>634894.72</v>
+        <v>654948.72</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>79.4%</t>
+          <t>81.9%</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -1029,11 +1029,11 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>482089.24</v>
+        <v>502143.24</v>
       </c>
     </row>
     <row r="19">
@@ -1051,23 +1051,23 @@
         <v>850000</v>
       </c>
       <c r="D19" t="n">
-        <v>373985.09</v>
+        <v>380585.09</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>44.8%</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>145527</v>
+        <v>145546</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>38.2%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>228458.09</v>
+        <v>235039.09</v>
       </c>
     </row>
     <row r="20">
@@ -1085,23 +1085,23 @@
         <v>700000</v>
       </c>
       <c r="D20" t="n">
-        <v>689126.99</v>
+        <v>686240.99</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>98.4%</t>
+          <t>98.0%</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>95100</v>
+        <v>95119</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>594026.99</v>
+        <v>591121.99</v>
       </c>
     </row>
   </sheetData>

--- a/导出_按分组.xlsx
+++ b/导出_按分组.xlsx
@@ -779,7 +779,7 @@
         <v>450000</v>
       </c>
       <c r="D11" t="n">
-        <v>316751.95</v>
+        <v>316727.94</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>270824.95</v>
+        <v>270800.94</v>
       </c>
     </row>
     <row r="12">
@@ -847,11 +847,11 @@
         <v>850000</v>
       </c>
       <c r="D13" t="n">
-        <v>575311.16</v>
+        <v>578559.98</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>67.7%</t>
+          <t>68.1%</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -859,11 +859,11 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>498502.16</v>
+        <v>501750.98</v>
       </c>
     </row>
     <row r="14">
@@ -881,11 +881,11 @@
         <v>800000</v>
       </c>
       <c r="D14" t="n">
-        <v>425019.6</v>
+        <v>427649.7</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>53.1%</t>
+          <t>53.5%</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -893,11 +893,11 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>18.0%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>347841.6</v>
+        <v>350471.7</v>
       </c>
     </row>
     <row r="15">
@@ -991,15 +991,15 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>80166</v>
+        <v>96666</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>22.0%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>359125.35</v>
+        <v>342625.35</v>
       </c>
     </row>
     <row r="18">
@@ -1051,7 +1051,7 @@
         <v>850000</v>
       </c>
       <c r="D19" t="n">
-        <v>380585.09</v>
+        <v>381026.53</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>235039.09</v>
+        <v>235480.53</v>
       </c>
     </row>
     <row r="20">

--- a/导出_按分组.xlsx
+++ b/导出_按分组.xlsx
@@ -473,23 +473,23 @@
         <v>1000000</v>
       </c>
       <c r="D2" t="n">
-        <v>479612.18</v>
+        <v>485022.08</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>48.0%</t>
+          <t>48.5%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>254102.67</v>
+        <v>254224.67</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>53.0%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>225509.51</v>
+        <v>230797.4099999999</v>
       </c>
     </row>
     <row r="3">
@@ -507,7 +507,7 @@
         <v>100000</v>
       </c>
       <c r="D3" t="n">
-        <v>16999.41</v>
+        <v>17018.41</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -515,11 +515,11 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>40765</v>
+        <v>40784</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>239.8%</t>
+          <t>239.6%</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -541,23 +541,23 @@
         <v>800000</v>
       </c>
       <c r="D4" t="n">
-        <v>697528.46</v>
+        <v>707749.88</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>87.2%</t>
+          <t>88.5%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>176805.8</v>
+        <v>176976.8</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>25.3%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>520722.66</v>
+        <v>530773.0800000001</v>
       </c>
     </row>
     <row r="5">
@@ -575,7 +575,7 @@
         <v>650000</v>
       </c>
       <c r="D5" t="n">
-        <v>479572.17</v>
+        <v>479630.17</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>351366.17</v>
+        <v>351424.17</v>
       </c>
     </row>
     <row r="6">
@@ -609,23 +609,23 @@
         <v>700000</v>
       </c>
       <c r="D6" t="n">
-        <v>402807.95</v>
+        <v>412478.95</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>58.9%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>110168.98</v>
+        <v>110396.98</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>27.4%</t>
+          <t>26.8%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>292638.97</v>
+        <v>302081.97</v>
       </c>
     </row>
     <row r="7">
@@ -643,15 +643,15 @@
         <v>550000</v>
       </c>
       <c r="D7" t="n">
-        <v>371716</v>
+        <v>372796</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>67.6%</t>
+          <t>67.8%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>107859</v>
+        <v>108224</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>263857</v>
+        <v>264572</v>
       </c>
     </row>
     <row r="8">
@@ -677,23 +677,23 @@
         <v>650000</v>
       </c>
       <c r="D8" t="n">
-        <v>376318.76</v>
+        <v>403026.76</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>57.9%</t>
+          <t>62.0%</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>82205.33</v>
+        <v>82420.33</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>21.8%</t>
+          <t>20.5%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>294113.43</v>
+        <v>320606.43</v>
       </c>
     </row>
     <row r="9">
@@ -711,23 +711,23 @@
         <v>1700000</v>
       </c>
       <c r="D9" t="n">
-        <v>932613</v>
+        <v>944942</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>287768</v>
+        <v>287797</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>30.9%</t>
+          <t>30.5%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>644845</v>
+        <v>657145</v>
       </c>
     </row>
     <row r="10">
@@ -745,11 +745,11 @@
         <v>2000000</v>
       </c>
       <c r="D10" t="n">
-        <v>1587682.52</v>
+        <v>1689045.52</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>79.4%</t>
+          <t>84.5%</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1587682.52</v>
+        <v>1689045.52</v>
       </c>
     </row>
     <row r="11">
@@ -779,11 +779,11 @@
         <v>450000</v>
       </c>
       <c r="D11" t="n">
-        <v>316727.94</v>
+        <v>335150.05</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>70.4%</t>
+          <t>74.5%</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -791,11 +791,11 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>270800.94</v>
+        <v>289223.05</v>
       </c>
     </row>
     <row r="12">
@@ -813,11 +813,11 @@
         <v>450000</v>
       </c>
       <c r="D12" t="n">
-        <v>367838.99</v>
+        <v>379032.99</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>81.7%</t>
+          <t>84.2%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>365610.99</v>
+        <v>376804.99</v>
       </c>
     </row>
     <row r="13">
@@ -847,11 +847,11 @@
         <v>850000</v>
       </c>
       <c r="D13" t="n">
-        <v>578559.98</v>
+        <v>663795.58</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>68.1%</t>
+          <t>78.1%</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -859,11 +859,11 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>501750.98</v>
+        <v>586986.58</v>
       </c>
     </row>
     <row r="14">
@@ -881,11 +881,11 @@
         <v>800000</v>
       </c>
       <c r="D14" t="n">
-        <v>427649.7</v>
+        <v>509092.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>53.5%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -893,11 +893,11 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>18.0%</t>
+          <t>15.2%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>350471.7</v>
+        <v>431914.2</v>
       </c>
     </row>
     <row r="15">
@@ -915,11 +915,11 @@
         <v>260000</v>
       </c>
       <c r="D15" t="n">
-        <v>196214</v>
+        <v>208612</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>75.5%</t>
+          <t>80.2%</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -927,11 +927,11 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>7.3%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>180889</v>
+        <v>193287</v>
       </c>
     </row>
     <row r="16">
@@ -949,11 +949,11 @@
         <v>400000</v>
       </c>
       <c r="D16" t="n">
-        <v>322297.97</v>
+        <v>323491.97</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>80.6%</t>
+          <t>80.9%</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>269297.97</v>
+        <v>270491.97</v>
       </c>
     </row>
     <row r="17">
@@ -983,11 +983,11 @@
         <v>700000</v>
       </c>
       <c r="D17" t="n">
-        <v>439291.35</v>
+        <v>490291.35</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>70.0%</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -995,11 +995,11 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>22.0%</t>
+          <t>19.7%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>342625.35</v>
+        <v>393625.35</v>
       </c>
     </row>
     <row r="18">
@@ -1017,11 +1017,11 @@
         <v>800000</v>
       </c>
       <c r="D18" t="n">
-        <v>654948.72</v>
+        <v>716151.72</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>81.9%</t>
+          <t>89.5%</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -1029,11 +1029,11 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>23.3%</t>
+          <t>21.3%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>502143.24</v>
+        <v>563346.24</v>
       </c>
     </row>
     <row r="19">
@@ -1051,11 +1051,11 @@
         <v>850000</v>
       </c>
       <c r="D19" t="n">
-        <v>381026.53</v>
+        <v>383421.55</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>44.8%</t>
+          <t>45.1%</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -1063,11 +1063,11 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>38.2%</t>
+          <t>38.0%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>235480.53</v>
+        <v>237875.55</v>
       </c>
     </row>
     <row r="20">
@@ -1085,11 +1085,11 @@
         <v>700000</v>
       </c>
       <c r="D20" t="n">
-        <v>686240.99</v>
+        <v>698733.99</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>98.0%</t>
+          <t>99.8%</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -1097,11 +1097,11 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>591121.99</v>
+        <v>603614.99</v>
       </c>
     </row>
   </sheetData>

--- a/导出_按分组.xlsx
+++ b/导出_按分组.xlsx
@@ -473,23 +473,23 @@
         <v>1000000</v>
       </c>
       <c r="D2" t="n">
-        <v>485022.08</v>
+        <v>487672.08</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>48.5%</t>
+          <t>48.8%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>254224.67</v>
+        <v>254414.67</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>230797.4099999999</v>
+        <v>233257.4099999999</v>
       </c>
     </row>
     <row r="3">
@@ -507,11 +507,11 @@
         <v>100000</v>
       </c>
       <c r="D3" t="n">
-        <v>17018.41</v>
+        <v>18355.41</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>17.0%</t>
+          <t>18.4%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -519,11 +519,11 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>239.6%</t>
+          <t>222.2%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>-23765.59</v>
+        <v>-22428.59</v>
       </c>
     </row>
     <row r="4">
@@ -541,23 +541,23 @@
         <v>800000</v>
       </c>
       <c r="D4" t="n">
-        <v>707749.88</v>
+        <v>724463.88</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>88.5%</t>
+          <t>90.6%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>176976.8</v>
+        <v>177175.8</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>24.5%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>530773.0800000001</v>
+        <v>547288.0800000001</v>
       </c>
     </row>
     <row r="5">
@@ -575,7 +575,7 @@
         <v>650000</v>
       </c>
       <c r="D5" t="n">
-        <v>479630.17</v>
+        <v>479649.17</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>351424.17</v>
+        <v>351443.17</v>
       </c>
     </row>
     <row r="6">
@@ -609,23 +609,23 @@
         <v>700000</v>
       </c>
       <c r="D6" t="n">
-        <v>412478.95</v>
+        <v>437064.94</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>62.4%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>110396.98</v>
+        <v>110825.98</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>26.8%</t>
+          <t>25.4%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>302081.97</v>
+        <v>326238.96</v>
       </c>
     </row>
     <row r="7">
@@ -643,23 +643,23 @@
         <v>550000</v>
       </c>
       <c r="D7" t="n">
-        <v>372796</v>
+        <v>379528</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>67.8%</t>
+          <t>69.0%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>108224</v>
+        <v>108907</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>29.0%</t>
+          <t>28.7%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>264572</v>
+        <v>270621</v>
       </c>
     </row>
     <row r="8">
@@ -677,23 +677,23 @@
         <v>650000</v>
       </c>
       <c r="D8" t="n">
-        <v>403026.76</v>
+        <v>403535.76</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>62.0%</t>
+          <t>62.1%</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>82420.33</v>
+        <v>82515.33</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>20.5%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>320606.43</v>
+        <v>321020.43</v>
       </c>
     </row>
     <row r="9">
@@ -745,11 +745,11 @@
         <v>2000000</v>
       </c>
       <c r="D10" t="n">
-        <v>1689045.52</v>
+        <v>1866907.09</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>84.5%</t>
+          <t>93.3%</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1689045.52</v>
+        <v>1866907.09</v>
       </c>
     </row>
     <row r="11">
@@ -779,11 +779,11 @@
         <v>450000</v>
       </c>
       <c r="D11" t="n">
-        <v>335150.05</v>
+        <v>342546.05</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>74.5%</t>
+          <t>76.1%</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -791,11 +791,11 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>13.4%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>289223.05</v>
+        <v>296619.05</v>
       </c>
     </row>
     <row r="12">
@@ -813,11 +813,11 @@
         <v>450000</v>
       </c>
       <c r="D12" t="n">
-        <v>379032.99</v>
+        <v>380226.99</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>84.2%</t>
+          <t>84.5%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>376804.99</v>
+        <v>377998.99</v>
       </c>
     </row>
     <row r="13">
@@ -847,11 +847,11 @@
         <v>850000</v>
       </c>
       <c r="D13" t="n">
-        <v>663795.58</v>
+        <v>693613.48</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>78.1%</t>
+          <t>81.6%</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -859,11 +859,11 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>586986.58</v>
+        <v>616804.48</v>
       </c>
     </row>
     <row r="14">
@@ -881,11 +881,11 @@
         <v>800000</v>
       </c>
       <c r="D14" t="n">
-        <v>509092.2</v>
+        <v>583358.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>72.9%</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -893,11 +893,11 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>15.2%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>431914.2</v>
+        <v>506180.6</v>
       </c>
     </row>
     <row r="15">
@@ -915,11 +915,11 @@
         <v>260000</v>
       </c>
       <c r="D15" t="n">
-        <v>208612</v>
+        <v>212572</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>80.2%</t>
+          <t>81.8%</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -927,11 +927,11 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>7.3%</t>
+          <t>7.2%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>193287</v>
+        <v>197247</v>
       </c>
     </row>
     <row r="16">
@@ -949,11 +949,11 @@
         <v>400000</v>
       </c>
       <c r="D16" t="n">
-        <v>323491.97</v>
+        <v>323898.97</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>80.9%</t>
+          <t>81.0%</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>270491.97</v>
+        <v>270898.97</v>
       </c>
     </row>
     <row r="17">
@@ -983,11 +983,11 @@
         <v>700000</v>
       </c>
       <c r="D17" t="n">
-        <v>490291.35</v>
+        <v>565057.4299999999</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>80.7%</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -995,11 +995,11 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>19.7%</t>
+          <t>17.1%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>393625.35</v>
+        <v>468391.4299999999</v>
       </c>
     </row>
     <row r="18">
@@ -1017,23 +1017,23 @@
         <v>800000</v>
       </c>
       <c r="D18" t="n">
-        <v>716151.72</v>
+        <v>744770.72</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>89.5%</t>
+          <t>93.1%</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>152805.48</v>
+        <v>152824.48</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>21.3%</t>
+          <t>20.5%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>563346.24</v>
+        <v>591946.24</v>
       </c>
     </row>
     <row r="19">
@@ -1051,11 +1051,11 @@
         <v>850000</v>
       </c>
       <c r="D19" t="n">
-        <v>383421.55</v>
+        <v>410851.64</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>45.1%</t>
+          <t>48.3%</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -1063,11 +1063,11 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>38.0%</t>
+          <t>35.4%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>237875.55</v>
+        <v>265305.64</v>
       </c>
     </row>
     <row r="20">
@@ -1085,23 +1085,23 @@
         <v>700000</v>
       </c>
       <c r="D20" t="n">
-        <v>698733.99</v>
+        <v>717595.99</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>99.8%</t>
+          <t>102.5%</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>95119</v>
+        <v>95138</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>603614.99</v>
+        <v>622457.99</v>
       </c>
     </row>
   </sheetData>

--- a/导出_按分组.xlsx
+++ b/导出_按分组.xlsx
@@ -473,23 +473,23 @@
         <v>1000000</v>
       </c>
       <c r="D2" t="n">
-        <v>487672.08</v>
+        <v>657054.0800000001</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>48.8%</t>
+          <t>65.7%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>254414.67</v>
+        <v>254609.67</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>38.8%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>233257.4099999999</v>
+        <v>402444.41</v>
       </c>
     </row>
     <row r="3">
@@ -507,7 +507,7 @@
         <v>100000</v>
       </c>
       <c r="D3" t="n">
-        <v>18355.41</v>
+        <v>18393.41</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -515,15 +515,15 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>40784</v>
+        <v>40813</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>222.2%</t>
+          <t>221.9%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>-22428.59</v>
+        <v>-22419.59</v>
       </c>
     </row>
     <row r="4">
@@ -541,23 +541,23 @@
         <v>800000</v>
       </c>
       <c r="D4" t="n">
-        <v>724463.88</v>
+        <v>792933.87</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>90.6%</t>
+          <t>99.1%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>177175.8</v>
+        <v>181546.8</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>24.5%</t>
+          <t>22.9%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>547288.0800000001</v>
+        <v>611387.0700000001</v>
       </c>
     </row>
     <row r="5">
@@ -575,23 +575,23 @@
         <v>650000</v>
       </c>
       <c r="D5" t="n">
-        <v>479649.17</v>
+        <v>483707.17</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>73.8%</t>
+          <t>74.4%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>128206</v>
+        <v>128235</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>351443.17</v>
+        <v>355472.17</v>
       </c>
     </row>
     <row r="6">
@@ -609,23 +609,23 @@
         <v>700000</v>
       </c>
       <c r="D6" t="n">
-        <v>437064.94</v>
+        <v>464745.9400000001</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>62.4%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>110825.98</v>
+        <v>118534.18</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>25.4%</t>
+          <t>25.5%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>326238.96</v>
+        <v>346211.7600000001</v>
       </c>
     </row>
     <row r="7">
@@ -643,23 +643,23 @@
         <v>550000</v>
       </c>
       <c r="D7" t="n">
-        <v>379528</v>
+        <v>436684</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>69.0%</t>
+          <t>79.4%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>108907</v>
+        <v>109290</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>28.7%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>270621</v>
+        <v>327394</v>
       </c>
     </row>
     <row r="8">
@@ -677,23 +677,23 @@
         <v>650000</v>
       </c>
       <c r="D8" t="n">
-        <v>403535.76</v>
+        <v>443340.76</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>62.1%</t>
+          <t>68.2%</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>82515.33</v>
+        <v>84564.33</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>19.1%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>321020.43</v>
+        <v>358776.43</v>
       </c>
     </row>
     <row r="9">
@@ -711,23 +711,23 @@
         <v>1700000</v>
       </c>
       <c r="D9" t="n">
-        <v>944942</v>
+        <v>1319532</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>77.6%</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>287797</v>
+        <v>354185</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>30.5%</t>
+          <t>26.8%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>657145</v>
+        <v>965347</v>
       </c>
     </row>
     <row r="10">
@@ -745,11 +745,11 @@
         <v>2000000</v>
       </c>
       <c r="D10" t="n">
-        <v>1866907.09</v>
+        <v>1974646.09</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>93.3%</t>
+          <t>98.7%</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1866907.09</v>
+        <v>1974646.09</v>
       </c>
     </row>
     <row r="11">
@@ -779,23 +779,23 @@
         <v>450000</v>
       </c>
       <c r="D11" t="n">
-        <v>342546.05</v>
+        <v>447962.05</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>76.1%</t>
+          <t>99.5%</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>45927</v>
+        <v>76327</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>17.0%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>296619.05</v>
+        <v>371635.05</v>
       </c>
     </row>
     <row r="12">
@@ -813,11 +813,11 @@
         <v>450000</v>
       </c>
       <c r="D12" t="n">
-        <v>380226.99</v>
+        <v>382022.99</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>84.5%</t>
+          <t>84.9%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>377998.99</v>
+        <v>379794.99</v>
       </c>
     </row>
     <row r="13">
@@ -847,23 +847,23 @@
         <v>850000</v>
       </c>
       <c r="D13" t="n">
-        <v>693613.48</v>
+        <v>701632.48</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>81.6%</t>
+          <t>82.5%</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>76809</v>
+        <v>76828</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>616804.48</v>
+        <v>624804.48</v>
       </c>
     </row>
     <row r="14">
@@ -881,23 +881,23 @@
         <v>800000</v>
       </c>
       <c r="D14" t="n">
-        <v>583358.6</v>
+        <v>779679.1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>72.9%</t>
+          <t>97.5%</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>77178</v>
+        <v>100278</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>506180.6</v>
+        <v>679401.1</v>
       </c>
     </row>
     <row r="15">
@@ -915,11 +915,11 @@
         <v>260000</v>
       </c>
       <c r="D15" t="n">
-        <v>212572</v>
+        <v>253829</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>81.8%</t>
+          <t>97.6%</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -927,11 +927,11 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>7.2%</t>
+          <t>6.0%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>197247</v>
+        <v>238504</v>
       </c>
     </row>
     <row r="16">
@@ -949,11 +949,11 @@
         <v>400000</v>
       </c>
       <c r="D16" t="n">
-        <v>323898.97</v>
+        <v>364723.97</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>81.0%</t>
+          <t>91.2%</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -961,11 +961,11 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>16.4%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>270898.97</v>
+        <v>311723.97</v>
       </c>
     </row>
     <row r="17">
@@ -983,7 +983,7 @@
         <v>700000</v>
       </c>
       <c r="D17" t="n">
-        <v>565057.4299999999</v>
+        <v>565084.4299999999</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>468391.4299999999</v>
+        <v>468418.4299999999</v>
       </c>
     </row>
     <row r="18">
@@ -1017,23 +1017,23 @@
         <v>800000</v>
       </c>
       <c r="D18" t="n">
-        <v>744770.72</v>
+        <v>867684.72</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>93.1%</t>
+          <t>108.5%</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>152824.48</v>
+        <v>156303.48</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>20.5%</t>
+          <t>18.0%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>591946.24</v>
+        <v>711381.24</v>
       </c>
     </row>
     <row r="19">
@@ -1051,23 +1051,23 @@
         <v>850000</v>
       </c>
       <c r="D19" t="n">
-        <v>410851.64</v>
+        <v>420389.73</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>48.3%</t>
+          <t>49.5%</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>145546</v>
+        <v>185996</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>35.4%</t>
+          <t>44.2%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>265305.64</v>
+        <v>234393.73</v>
       </c>
     </row>
     <row r="20">
@@ -1085,23 +1085,23 @@
         <v>700000</v>
       </c>
       <c r="D20" t="n">
-        <v>717595.99</v>
+        <v>737671.99</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>102.5%</t>
+          <t>105.4%</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>95138</v>
+        <v>95157</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>622457.99</v>
+        <v>642514.99</v>
       </c>
     </row>
   </sheetData>

--- a/导出_按分组.xlsx
+++ b/导出_按分组.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:K20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,6 +457,21 @@
           <t>本月净流水</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>新客净流水</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>老客净流水</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>非1V1及菌群净</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -470,27 +485,30 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1000000</v>
+        <v>760000</v>
       </c>
       <c r="D2" t="n">
-        <v>657054.0800000001</v>
+        <v>70600</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>8.2%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>254609.67</v>
+        <v>8524</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>38.8%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>402444.41</v>
-      </c>
+        <v>62076</v>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -504,27 +522,30 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>18393.41</v>
+        <v>1856</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>18.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>40813</v>
+        <v>2560</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>221.9%</t>
+          <t>137.9%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>-22419.59</v>
-      </c>
+        <v>-704</v>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -538,27 +559,30 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>800000</v>
+        <v>760000</v>
       </c>
       <c r="D4" t="n">
-        <v>792933.87</v>
+        <v>61409.2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>99.1%</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>181546.8</v>
+        <v>37613</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>22.9%</t>
+          <t>61.2%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>611387.0700000001</v>
-      </c>
+        <v>23796.2</v>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -572,27 +596,30 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>650000</v>
+        <v>520000</v>
       </c>
       <c r="D5" t="n">
-        <v>483707.17</v>
+        <v>12292</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>74.4%</t>
+          <t>-10.6%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>128235</v>
+        <v>67219</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>546.9%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>355472.17</v>
-      </c>
+        <v>-54927</v>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -606,27 +633,30 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>700000</v>
+        <v>600000</v>
       </c>
       <c r="D6" t="n">
-        <v>464745.9400000001</v>
+        <v>69704</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>118534.18</v>
+        <v>2453</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>25.5%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>346211.7600000001</v>
-      </c>
+        <v>67251</v>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -640,27 +670,30 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>550000</v>
+        <v>360000</v>
       </c>
       <c r="D7" t="n">
-        <v>436684</v>
+        <v>52078</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>79.4%</t>
+          <t>11.3%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>109290</v>
+        <v>11386</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>327394</v>
-      </c>
+        <v>40692</v>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -674,27 +707,30 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>650000</v>
+        <v>640000</v>
       </c>
       <c r="D8" t="n">
-        <v>443340.76</v>
+        <v>25603.42</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>68.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>84564.33</v>
+        <v>11193</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>19.1%</t>
+          <t>43.7%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>358776.43</v>
-      </c>
+        <v>14410.42</v>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -708,27 +744,30 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1700000</v>
+        <v>1120000</v>
       </c>
       <c r="D9" t="n">
-        <v>1319532</v>
+        <v>112716.36</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>77.6%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>354185</v>
+        <v>73800</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>26.8%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>965347</v>
-      </c>
+        <v>38916.36</v>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -745,11 +784,11 @@
         <v>2000000</v>
       </c>
       <c r="D10" t="n">
-        <v>1974646.09</v>
+        <v>138054.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>98.7%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -761,7 +800,16 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1974646.09</v>
+        <v>138054.1</v>
+      </c>
+      <c r="I10" t="n">
+        <v>9692</v>
+      </c>
+      <c r="J10" t="n">
+        <v>128362</v>
+      </c>
+      <c r="K10" t="n">
+        <v>137656</v>
       </c>
     </row>
     <row r="11">
@@ -776,26 +824,35 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>450000</v>
+        <v>380000</v>
       </c>
       <c r="D11" t="n">
-        <v>447962.05</v>
+        <v>8203.35</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>99.5%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>76327</v>
+        <v>0</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>17.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>371635.05</v>
+        <v>8203.35</v>
+      </c>
+      <c r="I11" t="n">
+        <v>5795</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2198</v>
+      </c>
+      <c r="K11" t="n">
+        <v>7009</v>
       </c>
     </row>
     <row r="12">
@@ -810,26 +867,35 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>450000</v>
+        <v>400000</v>
       </c>
       <c r="D12" t="n">
-        <v>382022.99</v>
+        <v>41531</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>84.9%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2228</v>
+        <v>0</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>379794.99</v>
+        <v>41531</v>
+      </c>
+      <c r="I12" t="n">
+        <v>30735</v>
+      </c>
+      <c r="J12" t="n">
+        <v>10796</v>
+      </c>
+      <c r="K12" t="n">
+        <v>337</v>
       </c>
     </row>
     <row r="13">
@@ -844,26 +910,35 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>850000</v>
+        <v>800000</v>
       </c>
       <c r="D13" t="n">
-        <v>701632.48</v>
+        <v>63793.4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>82.5%</t>
+          <t>8.0%</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>76828</v>
+        <v>67</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>624804.48</v>
+        <v>63726.4</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1053</v>
+      </c>
+      <c r="J13" t="n">
+        <v>60996</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2532</v>
       </c>
     </row>
     <row r="14">
@@ -881,23 +956,32 @@
         <v>800000</v>
       </c>
       <c r="D14" t="n">
-        <v>779679.1</v>
+        <v>10991</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>97.5%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>100278</v>
+        <v>5000</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>679401.1</v>
+        <v>5991</v>
+      </c>
+      <c r="I14" t="n">
+        <v>-1491</v>
+      </c>
+      <c r="J14" t="n">
+        <v>6936</v>
+      </c>
+      <c r="K14" t="n">
+        <v>8495</v>
       </c>
     </row>
     <row r="15">
@@ -915,23 +999,32 @@
         <v>260000</v>
       </c>
       <c r="D15" t="n">
-        <v>253829</v>
+        <v>37415</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>97.6%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>15325</v>
+        <v>19</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>238504</v>
+        <v>37396</v>
+      </c>
+      <c r="I15" t="n">
+        <v>19</v>
+      </c>
+      <c r="J15" t="n">
+        <v>37377</v>
+      </c>
+      <c r="K15" t="n">
+        <v>27396</v>
       </c>
     </row>
     <row r="16">
@@ -949,23 +1042,32 @@
         <v>400000</v>
       </c>
       <c r="D16" t="n">
-        <v>364723.97</v>
+        <v>20627</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>91.2%</t>
+          <t>5.1%</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>53000</v>
+        <v>398</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>311723.97</v>
+        <v>20229</v>
+      </c>
+      <c r="I16" t="n">
+        <v>229</v>
+      </c>
+      <c r="J16" t="n">
+        <v>20000</v>
+      </c>
+      <c r="K16" t="n">
+        <v>29</v>
       </c>
     </row>
     <row r="17">
@@ -983,23 +1085,32 @@
         <v>700000</v>
       </c>
       <c r="D17" t="n">
-        <v>565084.4299999999</v>
+        <v>76394.32000000001</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>80.7%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>96666</v>
+        <v>4248</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>17.1%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>468418.4299999999</v>
+        <v>72146.32000000001</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1186</v>
+      </c>
+      <c r="J17" t="n">
+        <v>70398</v>
+      </c>
+      <c r="K17" t="n">
+        <v>552</v>
       </c>
     </row>
     <row r="18">
@@ -1014,26 +1125,35 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>800000</v>
+        <v>900000</v>
       </c>
       <c r="D18" t="n">
-        <v>867684.72</v>
+        <v>110819</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>108.5%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>156303.48</v>
+        <v>0</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>18.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>711381.24</v>
+        <v>110819</v>
+      </c>
+      <c r="I18" t="n">
+        <v>62021</v>
+      </c>
+      <c r="J18" t="n">
+        <v>48798</v>
+      </c>
+      <c r="K18" t="n">
+        <v>69407</v>
       </c>
     </row>
     <row r="19">
@@ -1048,26 +1168,35 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>850000</v>
+        <v>900000</v>
       </c>
       <c r="D19" t="n">
-        <v>420389.73</v>
+        <v>20819</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>49.5%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>185996</v>
+        <v>200</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>44.2%</t>
+          <t>1.0%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>234393.73</v>
+        <v>20619</v>
+      </c>
+      <c r="I19" t="n">
+        <v>7519</v>
+      </c>
+      <c r="J19" t="n">
+        <v>13100</v>
+      </c>
+      <c r="K19" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="20">
@@ -1085,23 +1214,32 @@
         <v>700000</v>
       </c>
       <c r="D20" t="n">
-        <v>737671.99</v>
+        <v>70714.89999999999</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>105.4%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>95157</v>
+        <v>21162</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>29.9%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>642514.99</v>
+        <v>49552.89999999999</v>
+      </c>
+      <c r="I20" t="n">
+        <v>4956</v>
+      </c>
+      <c r="J20" t="n">
+        <v>44596</v>
+      </c>
+      <c r="K20" t="n">
+        <v>14166</v>
       </c>
     </row>
   </sheetData>

--- a/导出_按分组.xlsx
+++ b/导出_按分组.xlsx
@@ -485,14 +485,14 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>760000</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>70600</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>8.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -559,14 +559,14 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>760000</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
         <v>61409.2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -596,14 +596,14 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>520000</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
         <v>12292</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-10.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -633,14 +633,14 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>600000</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
         <v>69704</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -670,14 +670,14 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>360000</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
         <v>52078</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>11.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -707,14 +707,14 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>640000</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
         <v>25603.42</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -744,14 +744,14 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1120000</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
         <v>112716.36</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F9" t="n">

--- a/导出_按分组.xlsx
+++ b/导出_按分组.xlsx
@@ -485,14 +485,14 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>760000</v>
       </c>
       <c r="D2" t="n">
         <v>70600</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>8.2%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -559,14 +559,14 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>760000</v>
       </c>
       <c r="D4" t="n">
         <v>61409.2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -596,14 +596,14 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>520000</v>
       </c>
       <c r="D5" t="n">
         <v>12292</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>-10.6%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -633,14 +633,14 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>600000</v>
       </c>
       <c r="D6" t="n">
         <v>69704</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -670,14 +670,14 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>360000</v>
       </c>
       <c r="D7" t="n">
         <v>52078</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>11.3%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -707,14 +707,14 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>640000</v>
       </c>
       <c r="D8" t="n">
         <v>25603.42</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -744,14 +744,14 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>1120000</v>
       </c>
       <c r="D9" t="n">
         <v>112716.36</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F9" t="n">

--- a/导出_按分组.xlsx
+++ b/导出_按分组.xlsx
@@ -506,9 +506,15 @@
       <c r="H2" t="n">
         <v>62076</v>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="I2" t="n">
+        <v>62076</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>62076</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -543,9 +549,15 @@
       <c r="H3" t="n">
         <v>-704</v>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="I3" t="n">
+        <v>-839</v>
+      </c>
+      <c r="J3" t="n">
+        <v>135</v>
+      </c>
+      <c r="K3" t="n">
+        <v>-704</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -580,9 +592,15 @@
       <c r="H4" t="n">
         <v>23796.2</v>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="I4" t="n">
+        <v>34632</v>
+      </c>
+      <c r="J4" t="n">
+        <v>-10835</v>
+      </c>
+      <c r="K4" t="n">
+        <v>40500</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -617,9 +635,15 @@
       <c r="H5" t="n">
         <v>-54927</v>
       </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+      <c r="I5" t="n">
+        <v>-54927</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>-54927</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -654,9 +678,15 @@
       <c r="H6" t="n">
         <v>67251</v>
       </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+      <c r="I6" t="n">
+        <v>67251</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>45251</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -691,9 +721,15 @@
       <c r="H7" t="n">
         <v>40692</v>
       </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+      <c r="I7" t="n">
+        <v>10892</v>
+      </c>
+      <c r="J7" t="n">
+        <v>29800</v>
+      </c>
+      <c r="K7" t="n">
+        <v>40692</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -728,9 +764,15 @@
       <c r="H8" t="n">
         <v>14410.42</v>
       </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+      <c r="I8" t="n">
+        <v>14092</v>
+      </c>
+      <c r="J8" t="n">
+        <v>318</v>
+      </c>
+      <c r="K8" t="n">
+        <v>14410</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -765,9 +807,15 @@
       <c r="H9" t="n">
         <v>38916.36</v>
       </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+      <c r="I9" t="n">
+        <v>11116</v>
+      </c>
+      <c r="J9" t="n">
+        <v>27800</v>
+      </c>
+      <c r="K9" t="n">
+        <v>3916</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">

--- a/导出_按分组.xlsx
+++ b/导出_按分组.xlsx
@@ -488,32 +488,32 @@
         <v>760000</v>
       </c>
       <c r="D2" t="n">
-        <v>70600</v>
+        <v>130635</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>8.2%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>8524</v>
+        <v>37302</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>62076</v>
+        <v>93333</v>
       </c>
       <c r="I2" t="n">
-        <v>62076</v>
+        <v>92315</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>1018</v>
       </c>
       <c r="K2" t="n">
-        <v>62076</v>
+        <v>93333</v>
       </c>
     </row>
     <row r="3">
@@ -531,7 +531,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>1856</v>
+        <v>1971</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -539,24 +539,24 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2560</v>
+        <v>2589</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>137.9%</t>
+          <t>131.4%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>-704</v>
+        <v>-618</v>
       </c>
       <c r="I3" t="n">
-        <v>-839</v>
+        <v>-753</v>
       </c>
       <c r="J3" t="n">
         <v>135</v>
       </c>
       <c r="K3" t="n">
-        <v>-704</v>
+        <v>-618</v>
       </c>
     </row>
     <row r="4">
@@ -574,32 +574,32 @@
         <v>760000</v>
       </c>
       <c r="D4" t="n">
-        <v>61409.2</v>
+        <v>91972.56999999999</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>37613</v>
+        <v>58112</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>61.2%</t>
+          <t>63.2%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>23796.2</v>
+        <v>33860.56999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>34632</v>
+        <v>42887</v>
       </c>
       <c r="J4" t="n">
-        <v>-10835</v>
+        <v>-9027</v>
       </c>
       <c r="K4" t="n">
-        <v>40500</v>
+        <v>44166</v>
       </c>
     </row>
     <row r="5">
@@ -617,32 +617,32 @@
         <v>520000</v>
       </c>
       <c r="D5" t="n">
-        <v>12292</v>
+        <v>21465</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-10.6%</t>
+          <t>-11.4%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>67219</v>
+        <v>80965</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>546.9%</t>
+          <t>377.2%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>-54927</v>
+        <v>-59500</v>
       </c>
       <c r="I5" t="n">
-        <v>-54927</v>
+        <v>-63300</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>3800</v>
       </c>
       <c r="K5" t="n">
-        <v>-54927</v>
+        <v>-59500</v>
       </c>
     </row>
     <row r="6">
@@ -660,32 +660,32 @@
         <v>600000</v>
       </c>
       <c r="D6" t="n">
-        <v>69704</v>
+        <v>125411.56</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2453</v>
+        <v>14582</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>67251</v>
+        <v>110829.56</v>
       </c>
       <c r="I6" t="n">
-        <v>67251</v>
+        <v>110810</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="K6" t="n">
-        <v>45251</v>
+        <v>88431</v>
       </c>
     </row>
     <row r="7">
@@ -703,32 +703,32 @@
         <v>360000</v>
       </c>
       <c r="D7" t="n">
-        <v>52078</v>
+        <v>91673</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>11.3%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>11386</v>
+        <v>21663</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>23.6%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>40692</v>
+        <v>70010</v>
       </c>
       <c r="I7" t="n">
-        <v>10892</v>
+        <v>40191</v>
       </c>
       <c r="J7" t="n">
-        <v>29800</v>
+        <v>29819</v>
       </c>
       <c r="K7" t="n">
-        <v>40692</v>
+        <v>52510</v>
       </c>
     </row>
     <row r="8">
@@ -746,32 +746,32 @@
         <v>640000</v>
       </c>
       <c r="D8" t="n">
-        <v>25603.42</v>
+        <v>57287.42</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>6.4%</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>11193</v>
+        <v>16524</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>43.7%</t>
+          <t>28.8%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>14410.42</v>
+        <v>40763.42</v>
       </c>
       <c r="I8" t="n">
-        <v>14092</v>
+        <v>40426</v>
       </c>
       <c r="J8" t="n">
-        <v>318</v>
+        <v>337</v>
       </c>
       <c r="K8" t="n">
-        <v>14410</v>
+        <v>40763</v>
       </c>
     </row>
     <row r="9">
@@ -789,32 +789,32 @@
         <v>1120000</v>
       </c>
       <c r="D9" t="n">
-        <v>112716.36</v>
+        <v>282723.36</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>73800</v>
+        <v>129600</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>38916.36</v>
+        <v>153123.36</v>
       </c>
       <c r="I9" t="n">
-        <v>11116</v>
+        <v>67963</v>
       </c>
       <c r="J9" t="n">
-        <v>27800</v>
+        <v>85160</v>
       </c>
       <c r="K9" t="n">
-        <v>3916</v>
+        <v>118123</v>
       </c>
     </row>
     <row r="10">
@@ -832,11 +832,11 @@
         <v>2000000</v>
       </c>
       <c r="D10" t="n">
-        <v>138054.1</v>
+        <v>406715.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>20.3%</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -848,16 +848,16 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>138054.1</v>
+        <v>406715.6</v>
       </c>
       <c r="I10" t="n">
-        <v>9692</v>
+        <v>153969</v>
       </c>
       <c r="J10" t="n">
-        <v>128362</v>
+        <v>252746</v>
       </c>
       <c r="K10" t="n">
-        <v>137656</v>
+        <v>406317</v>
       </c>
     </row>
     <row r="11">
@@ -875,32 +875,32 @@
         <v>380000</v>
       </c>
       <c r="D11" t="n">
-        <v>8203.35</v>
+        <v>60287.35</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>4999.98</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>8203.35</v>
+        <v>55287.37</v>
       </c>
       <c r="I11" t="n">
-        <v>5795</v>
+        <v>7495</v>
       </c>
       <c r="J11" t="n">
-        <v>2198</v>
+        <v>47582</v>
       </c>
       <c r="K11" t="n">
-        <v>7009</v>
+        <v>47097</v>
       </c>
     </row>
     <row r="12">
@@ -918,15 +918,15 @@
         <v>400000</v>
       </c>
       <c r="D12" t="n">
-        <v>41531</v>
+        <v>102757</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>25.7%</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -934,16 +934,16 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>41531</v>
+        <v>102729</v>
       </c>
       <c r="I12" t="n">
-        <v>30735</v>
+        <v>41541</v>
       </c>
       <c r="J12" t="n">
-        <v>10796</v>
+        <v>61188</v>
       </c>
       <c r="K12" t="n">
-        <v>337</v>
+        <v>2327</v>
       </c>
     </row>
     <row r="13">
@@ -961,32 +961,32 @@
         <v>800000</v>
       </c>
       <c r="D13" t="n">
-        <v>63793.4</v>
+        <v>126681.9</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>8.0%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>67</v>
+        <v>4523</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>63726.4</v>
+        <v>122158.9</v>
       </c>
       <c r="I13" t="n">
-        <v>1053</v>
+        <v>9633</v>
       </c>
       <c r="J13" t="n">
-        <v>60996</v>
+        <v>106996</v>
       </c>
       <c r="K13" t="n">
-        <v>2532</v>
+        <v>14266</v>
       </c>
     </row>
     <row r="14">
@@ -1004,11 +1004,11 @@
         <v>800000</v>
       </c>
       <c r="D14" t="n">
-        <v>10991</v>
+        <v>76719.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>9.0%</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -1016,20 +1016,20 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>6.5%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>5991</v>
+        <v>71719.2</v>
       </c>
       <c r="I14" t="n">
-        <v>-1491</v>
+        <v>29353</v>
       </c>
       <c r="J14" t="n">
-        <v>6936</v>
+        <v>38130</v>
       </c>
       <c r="K14" t="n">
-        <v>8495</v>
+        <v>12233</v>
       </c>
     </row>
     <row r="15">
@@ -1047,11 +1047,11 @@
         <v>260000</v>
       </c>
       <c r="D15" t="n">
-        <v>37415</v>
+        <v>76236</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>29.3%</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -1059,20 +1059,20 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>37396</v>
+        <v>76217</v>
       </c>
       <c r="I15" t="n">
-        <v>19</v>
+        <v>442</v>
       </c>
       <c r="J15" t="n">
-        <v>37377</v>
+        <v>75775</v>
       </c>
       <c r="K15" t="n">
-        <v>27396</v>
+        <v>27421</v>
       </c>
     </row>
     <row r="16">
@@ -1090,11 +1090,11 @@
         <v>400000</v>
       </c>
       <c r="D16" t="n">
-        <v>20627</v>
+        <v>54653</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>5.1%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -1102,20 +1102,20 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>20229</v>
+        <v>54255</v>
       </c>
       <c r="I16" t="n">
-        <v>229</v>
+        <v>12059</v>
       </c>
       <c r="J16" t="n">
-        <v>20000</v>
+        <v>42196</v>
       </c>
       <c r="K16" t="n">
-        <v>29</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17">
@@ -1133,32 +1133,32 @@
         <v>700000</v>
       </c>
       <c r="D17" t="n">
-        <v>76394.32000000001</v>
+        <v>141067.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>4248</v>
+        <v>34077</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>24.2%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>72146.32000000001</v>
+        <v>106990.6</v>
       </c>
       <c r="I17" t="n">
-        <v>1186</v>
+        <v>1428</v>
       </c>
       <c r="J17" t="n">
-        <v>70398</v>
+        <v>104090</v>
       </c>
       <c r="K17" t="n">
-        <v>552</v>
+        <v>-28093</v>
       </c>
     </row>
     <row r="18">
@@ -1176,15 +1176,15 @@
         <v>900000</v>
       </c>
       <c r="D18" t="n">
-        <v>110819</v>
+        <v>212742</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>23.6%</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1192,16 +1192,16 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>110819</v>
+        <v>212714</v>
       </c>
       <c r="I18" t="n">
-        <v>62021</v>
+        <v>80823</v>
       </c>
       <c r="J18" t="n">
-        <v>48798</v>
+        <v>131891</v>
       </c>
       <c r="K18" t="n">
-        <v>69407</v>
+        <v>125114</v>
       </c>
     </row>
     <row r="19">
@@ -1219,32 +1219,32 @@
         <v>900000</v>
       </c>
       <c r="D19" t="n">
-        <v>20819</v>
+        <v>79311.38</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1.0%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>20619</v>
+        <v>79102.38</v>
       </c>
       <c r="I19" t="n">
-        <v>7519</v>
+        <v>8755</v>
       </c>
       <c r="J19" t="n">
-        <v>13100</v>
+        <v>67592</v>
       </c>
       <c r="K19" t="n">
-        <v>19</v>
+        <v>2812</v>
       </c>
     </row>
     <row r="20">
@@ -1262,32 +1262,32 @@
         <v>700000</v>
       </c>
       <c r="D20" t="n">
-        <v>70714.89999999999</v>
+        <v>128080.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>21162</v>
+        <v>21247</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>29.9%</t>
+          <t>16.6%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>49552.89999999999</v>
+        <v>106833.9</v>
       </c>
       <c r="I20" t="n">
-        <v>4956</v>
+        <v>25843</v>
       </c>
       <c r="J20" t="n">
-        <v>44596</v>
+        <v>80990</v>
       </c>
       <c r="K20" t="n">
-        <v>14166</v>
+        <v>25053</v>
       </c>
     </row>
   </sheetData>

--- a/导出_按分组.xlsx
+++ b/导出_按分组.xlsx
@@ -488,32 +488,32 @@
         <v>760000</v>
       </c>
       <c r="D2" t="n">
-        <v>130635</v>
+        <v>169874</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>17.4%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>37302</v>
+        <v>37586</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>22.1%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>93333</v>
+        <v>132288</v>
       </c>
       <c r="I2" t="n">
-        <v>92315</v>
+        <v>131270</v>
       </c>
       <c r="J2" t="n">
         <v>1018</v>
       </c>
       <c r="K2" t="n">
-        <v>93333</v>
+        <v>132288</v>
       </c>
     </row>
     <row r="3">
@@ -531,7 +531,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>1971</v>
+        <v>2009</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -539,24 +539,24 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2589</v>
+        <v>2618</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>131.4%</t>
+          <t>130.3%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>-618</v>
+        <v>-609</v>
       </c>
       <c r="I3" t="n">
-        <v>-753</v>
+        <v>-744</v>
       </c>
       <c r="J3" t="n">
         <v>135</v>
       </c>
       <c r="K3" t="n">
-        <v>-618</v>
+        <v>-609</v>
       </c>
     </row>
     <row r="4">
@@ -574,32 +574,32 @@
         <v>760000</v>
       </c>
       <c r="D4" t="n">
-        <v>91972.56999999999</v>
+        <v>180116.07</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>4.5%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>58112</v>
+        <v>67402</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>63.2%</t>
+          <t>37.4%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>33860.56999999999</v>
+        <v>112714.07</v>
       </c>
       <c r="I4" t="n">
-        <v>42887</v>
+        <v>120793</v>
       </c>
       <c r="J4" t="n">
-        <v>-9027</v>
+        <v>-8079</v>
       </c>
       <c r="K4" t="n">
-        <v>44166</v>
+        <v>122622</v>
       </c>
     </row>
     <row r="5">
@@ -617,32 +617,32 @@
         <v>520000</v>
       </c>
       <c r="D5" t="n">
-        <v>21465</v>
+        <v>61168</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-11.4%</t>
+          <t>-11.9%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>80965</v>
+        <v>122994</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>377.2%</t>
+          <t>201.1%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>-59500</v>
+        <v>-61826</v>
       </c>
       <c r="I5" t="n">
-        <v>-63300</v>
+        <v>-63214</v>
       </c>
       <c r="J5" t="n">
-        <v>3800</v>
+        <v>1388</v>
       </c>
       <c r="K5" t="n">
-        <v>-59500</v>
+        <v>-61826</v>
       </c>
     </row>
     <row r="6">
@@ -660,32 +660,32 @@
         <v>600000</v>
       </c>
       <c r="D6" t="n">
-        <v>125411.56</v>
+        <v>153305.46</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>22.4%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>14582</v>
+        <v>19103</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>110829.56</v>
+        <v>134202.46</v>
       </c>
       <c r="I6" t="n">
-        <v>110810</v>
+        <v>134163</v>
       </c>
       <c r="J6" t="n">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="K6" t="n">
-        <v>88431</v>
+        <v>99406</v>
       </c>
     </row>
     <row r="7">
@@ -703,32 +703,32 @@
         <v>360000</v>
       </c>
       <c r="D7" t="n">
-        <v>91673</v>
+        <v>111898</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>21663</v>
+        <v>22076</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>23.6%</t>
+          <t>19.7%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>70010</v>
+        <v>89822</v>
       </c>
       <c r="I7" t="n">
-        <v>40191</v>
+        <v>60003</v>
       </c>
       <c r="J7" t="n">
         <v>29819</v>
       </c>
       <c r="K7" t="n">
-        <v>52510</v>
+        <v>60322</v>
       </c>
     </row>
     <row r="8">
@@ -746,32 +746,32 @@
         <v>640000</v>
       </c>
       <c r="D8" t="n">
-        <v>57287.42</v>
+        <v>115504.42</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>6.4%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>16524</v>
+        <v>23285</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>28.8%</t>
+          <t>20.2%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>40763.42</v>
+        <v>92219.42</v>
       </c>
       <c r="I8" t="n">
-        <v>40426</v>
+        <v>91882</v>
       </c>
       <c r="J8" t="n">
         <v>337</v>
       </c>
       <c r="K8" t="n">
-        <v>40763</v>
+        <v>92219</v>
       </c>
     </row>
     <row r="9">
@@ -789,32 +789,32 @@
         <v>1120000</v>
       </c>
       <c r="D9" t="n">
-        <v>282723.36</v>
+        <v>367911.36</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>21.2%</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>129600</v>
+        <v>130600</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>35.5%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>153123.36</v>
+        <v>237311.36</v>
       </c>
       <c r="I9" t="n">
-        <v>67963</v>
+        <v>152151</v>
       </c>
       <c r="J9" t="n">
         <v>85160</v>
       </c>
       <c r="K9" t="n">
-        <v>118123</v>
+        <v>175491</v>
       </c>
     </row>
     <row r="10">
@@ -832,11 +832,11 @@
         <v>2000000</v>
       </c>
       <c r="D10" t="n">
-        <v>406715.6</v>
+        <v>424812.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>20.3%</t>
+          <t>21.2%</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -848,16 +848,16 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>406715.6</v>
+        <v>424812.6</v>
       </c>
       <c r="I10" t="n">
-        <v>153969</v>
+        <v>164765</v>
       </c>
       <c r="J10" t="n">
-        <v>252746</v>
+        <v>260047</v>
       </c>
       <c r="K10" t="n">
-        <v>406317</v>
+        <v>424414</v>
       </c>
     </row>
     <row r="11">
@@ -875,29 +875,29 @@
         <v>380000</v>
       </c>
       <c r="D11" t="n">
-        <v>60287.35</v>
+        <v>70885.35000000001</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>16.3%</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4999.98</v>
+        <v>8999.98</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>55287.37</v>
+        <v>61885.37000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>7495</v>
+        <v>13495</v>
       </c>
       <c r="J11" t="n">
-        <v>47582</v>
+        <v>48180</v>
       </c>
       <c r="K11" t="n">
         <v>47097</v>
@@ -918,11 +918,11 @@
         <v>400000</v>
       </c>
       <c r="D12" t="n">
-        <v>102757</v>
+        <v>129637</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>25.7%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -934,16 +934,16 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>102729</v>
+        <v>129609</v>
       </c>
       <c r="I12" t="n">
-        <v>41541</v>
+        <v>41741</v>
       </c>
       <c r="J12" t="n">
-        <v>61188</v>
+        <v>87868</v>
       </c>
       <c r="K12" t="n">
-        <v>2327</v>
+        <v>4207</v>
       </c>
     </row>
     <row r="13">
@@ -961,32 +961,32 @@
         <v>800000</v>
       </c>
       <c r="D13" t="n">
-        <v>126681.9</v>
+        <v>130905.38</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>4523</v>
+        <v>24389.67</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>122158.9</v>
+        <v>106515.71</v>
       </c>
       <c r="I13" t="n">
-        <v>9633</v>
+        <v>9652</v>
       </c>
       <c r="J13" t="n">
-        <v>106996</v>
+        <v>90229</v>
       </c>
       <c r="K13" t="n">
-        <v>14266</v>
+        <v>-4476</v>
       </c>
     </row>
     <row r="14">
@@ -1004,11 +1004,11 @@
         <v>800000</v>
       </c>
       <c r="D14" t="n">
-        <v>76719.2</v>
+        <v>88341.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>9.0%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -1016,20 +1016,20 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>6.5%</t>
+          <t>5.7%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>71719.2</v>
+        <v>83341.3</v>
       </c>
       <c r="I14" t="n">
-        <v>29353</v>
+        <v>29382</v>
       </c>
       <c r="J14" t="n">
-        <v>38130</v>
+        <v>48528</v>
       </c>
       <c r="K14" t="n">
-        <v>12233</v>
+        <v>13457</v>
       </c>
     </row>
     <row r="15">
@@ -1047,15 +1047,15 @@
         <v>260000</v>
       </c>
       <c r="D15" t="n">
-        <v>76236</v>
+        <v>77051</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>29.3%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1063,13 +1063,13 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>76217</v>
+        <v>77013</v>
       </c>
       <c r="I15" t="n">
         <v>442</v>
       </c>
       <c r="J15" t="n">
-        <v>75775</v>
+        <v>76571</v>
       </c>
       <c r="K15" t="n">
         <v>27421</v>
@@ -1090,11 +1090,11 @@
         <v>400000</v>
       </c>
       <c r="D16" t="n">
-        <v>54653</v>
+        <v>66672</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>16.6%</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -1102,20 +1102,20 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>54255</v>
+        <v>66274</v>
       </c>
       <c r="I16" t="n">
-        <v>12059</v>
+        <v>12078</v>
       </c>
       <c r="J16" t="n">
-        <v>42196</v>
+        <v>54196</v>
       </c>
       <c r="K16" t="n">
-        <v>67</v>
+        <v>86</v>
       </c>
     </row>
     <row r="17">
@@ -1133,29 +1133,29 @@
         <v>700000</v>
       </c>
       <c r="D17" t="n">
-        <v>141067.6</v>
+        <v>151067.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>15.9%</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>34077</v>
+        <v>40077</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>24.2%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>106990.6</v>
+        <v>110990.6</v>
       </c>
       <c r="I17" t="n">
         <v>1428</v>
       </c>
       <c r="J17" t="n">
-        <v>104090</v>
+        <v>108090</v>
       </c>
       <c r="K17" t="n">
         <v>-28093</v>
@@ -1176,11 +1176,11 @@
         <v>900000</v>
       </c>
       <c r="D18" t="n">
-        <v>212742</v>
+        <v>244813.14</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>23.6%</t>
+          <t>27.2%</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -1192,16 +1192,16 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>212714</v>
+        <v>244785.14</v>
       </c>
       <c r="I18" t="n">
-        <v>80823</v>
+        <v>82196</v>
       </c>
       <c r="J18" t="n">
-        <v>131891</v>
+        <v>162589</v>
       </c>
       <c r="K18" t="n">
-        <v>125114</v>
+        <v>125991</v>
       </c>
     </row>
     <row r="19">
@@ -1219,11 +1219,11 @@
         <v>900000</v>
       </c>
       <c r="D19" t="n">
-        <v>79311.38</v>
+        <v>98055.08</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -1231,20 +1231,20 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>79102.38</v>
+        <v>97846.08</v>
       </c>
       <c r="I19" t="n">
-        <v>8755</v>
+        <v>10351</v>
       </c>
       <c r="J19" t="n">
-        <v>67592</v>
+        <v>84392</v>
       </c>
       <c r="K19" t="n">
-        <v>2812</v>
+        <v>19960</v>
       </c>
     </row>
     <row r="20">
@@ -1262,32 +1262,32 @@
         <v>700000</v>
       </c>
       <c r="D20" t="n">
-        <v>128080.9</v>
+        <v>173468.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>19.3%</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>21247</v>
+        <v>38547</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>16.6%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>106833.9</v>
+        <v>134921.9</v>
       </c>
       <c r="I20" t="n">
-        <v>25843</v>
+        <v>68853</v>
       </c>
       <c r="J20" t="n">
-        <v>80990</v>
+        <v>66068</v>
       </c>
       <c r="K20" t="n">
-        <v>25053</v>
+        <v>17233</v>
       </c>
     </row>
   </sheetData>

--- a/导出_按分组.xlsx
+++ b/导出_按分组.xlsx
@@ -832,11 +832,11 @@
         <v>2000000</v>
       </c>
       <c r="D10" t="n">
-        <v>424812.6</v>
+        <v>446792.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>21.2%</t>
+          <t>22.3%</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -848,16 +848,16 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>424812.6</v>
+        <v>446792.6</v>
       </c>
       <c r="I10" t="n">
-        <v>164765</v>
+        <v>166745</v>
       </c>
       <c r="J10" t="n">
-        <v>260047</v>
+        <v>280047</v>
       </c>
       <c r="K10" t="n">
-        <v>424414</v>
+        <v>426394</v>
       </c>
     </row>
     <row r="11">
@@ -1262,11 +1262,11 @@
         <v>700000</v>
       </c>
       <c r="D20" t="n">
-        <v>173468.9</v>
+        <v>151488.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>19.3%</t>
+          <t>16.1%</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -1274,20 +1274,20 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>25.4%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>134921.9</v>
+        <v>112941.9</v>
       </c>
       <c r="I20" t="n">
-        <v>68853</v>
+        <v>66873</v>
       </c>
       <c r="J20" t="n">
-        <v>66068</v>
+        <v>46068</v>
       </c>
       <c r="K20" t="n">
-        <v>17233</v>
+        <v>15253</v>
       </c>
     </row>
   </sheetData>

--- a/导出_按分组.xlsx
+++ b/导出_按分组.xlsx
@@ -488,32 +488,32 @@
         <v>760000</v>
       </c>
       <c r="D2" t="n">
-        <v>169874</v>
+        <v>186408</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>17.4%</t>
+          <t>19.6%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>37586</v>
+        <v>37448</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>22.1%</t>
+          <t>20.1%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>132288</v>
+        <v>148960</v>
       </c>
       <c r="I2" t="n">
-        <v>131270</v>
+        <v>147942</v>
       </c>
       <c r="J2" t="n">
         <v>1018</v>
       </c>
       <c r="K2" t="n">
-        <v>132288</v>
+        <v>138960</v>
       </c>
     </row>
     <row r="3">
@@ -531,7 +531,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>2009</v>
+        <v>2327</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -543,20 +543,20 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>130.3%</t>
+          <t>112.5%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>-609</v>
+        <v>-291</v>
       </c>
       <c r="I3" t="n">
-        <v>-744</v>
+        <v>-426</v>
       </c>
       <c r="J3" t="n">
         <v>135</v>
       </c>
       <c r="K3" t="n">
-        <v>-609</v>
+        <v>-291</v>
       </c>
     </row>
     <row r="4">
@@ -574,32 +574,32 @@
         <v>760000</v>
       </c>
       <c r="D4" t="n">
-        <v>180116.07</v>
+        <v>233179.07</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>20.5%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>67402</v>
+        <v>77711</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>37.4%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>112714.07</v>
+        <v>155468.07</v>
       </c>
       <c r="I4" t="n">
-        <v>120793</v>
+        <v>163347</v>
       </c>
       <c r="J4" t="n">
-        <v>-8079</v>
+        <v>-7879</v>
       </c>
       <c r="K4" t="n">
-        <v>122622</v>
+        <v>163576</v>
       </c>
     </row>
     <row r="5">
@@ -617,32 +617,32 @@
         <v>520000</v>
       </c>
       <c r="D5" t="n">
-        <v>61168</v>
+        <v>83693</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-11.9%</t>
+          <t>-7.6%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>122994</v>
+        <v>123031.9</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>201.1%</t>
+          <t>147.0%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>-61826</v>
+        <v>-39338.89999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>-63214</v>
+        <v>-40726</v>
       </c>
       <c r="J5" t="n">
         <v>1388</v>
       </c>
       <c r="K5" t="n">
-        <v>-61826</v>
+        <v>-39338</v>
       </c>
     </row>
     <row r="6">
@@ -660,32 +660,32 @@
         <v>600000</v>
       </c>
       <c r="D6" t="n">
-        <v>153305.46</v>
+        <v>177719.46</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>22.4%</t>
+          <t>25.7%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>19103</v>
+        <v>23311.9</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>13.1%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>134202.46</v>
+        <v>154407.56</v>
       </c>
       <c r="I6" t="n">
-        <v>134163</v>
+        <v>150588</v>
       </c>
       <c r="J6" t="n">
-        <v>38</v>
+        <v>3819</v>
       </c>
       <c r="K6" t="n">
-        <v>99406</v>
+        <v>119611</v>
       </c>
     </row>
     <row r="7">
@@ -703,32 +703,32 @@
         <v>360000</v>
       </c>
       <c r="D7" t="n">
-        <v>111898</v>
+        <v>124591</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>28.4%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>22076</v>
+        <v>22394</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>19.7%</t>
+          <t>18.0%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>89822</v>
+        <v>102197</v>
       </c>
       <c r="I7" t="n">
-        <v>60003</v>
+        <v>72378</v>
       </c>
       <c r="J7" t="n">
         <v>29819</v>
       </c>
       <c r="K7" t="n">
-        <v>60322</v>
+        <v>60099</v>
       </c>
     </row>
     <row r="8">
@@ -746,32 +746,32 @@
         <v>640000</v>
       </c>
       <c r="D8" t="n">
-        <v>115504.42</v>
+        <v>183275.42</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>24.3%</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>23285</v>
+        <v>27482</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>20.2%</t>
+          <t>15.0%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>92219.42</v>
+        <v>155793.42</v>
       </c>
       <c r="I8" t="n">
-        <v>91882</v>
+        <v>155456</v>
       </c>
       <c r="J8" t="n">
         <v>337</v>
       </c>
       <c r="K8" t="n">
-        <v>92219</v>
+        <v>135793</v>
       </c>
     </row>
     <row r="9">
@@ -789,32 +789,32 @@
         <v>1120000</v>
       </c>
       <c r="D9" t="n">
-        <v>367911.36</v>
+        <v>391691.36</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>21.2%</t>
+          <t>22.7%</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>130600</v>
+        <v>137200</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>35.5%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>237311.36</v>
+        <v>254491.36</v>
       </c>
       <c r="I9" t="n">
-        <v>152151</v>
+        <v>169331</v>
       </c>
       <c r="J9" t="n">
         <v>85160</v>
       </c>
       <c r="K9" t="n">
-        <v>175491</v>
+        <v>172871</v>
       </c>
     </row>
     <row r="10">
@@ -832,11 +832,11 @@
         <v>2000000</v>
       </c>
       <c r="D10" t="n">
-        <v>446792.6</v>
+        <v>475597.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>22.3%</t>
+          <t>23.8%</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -848,16 +848,16 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>446792.6</v>
+        <v>475597.6</v>
       </c>
       <c r="I10" t="n">
-        <v>166745</v>
+        <v>172758</v>
       </c>
       <c r="J10" t="n">
-        <v>280047</v>
+        <v>302839</v>
       </c>
       <c r="K10" t="n">
-        <v>426394</v>
+        <v>435199</v>
       </c>
     </row>
     <row r="11">
@@ -875,32 +875,32 @@
         <v>380000</v>
       </c>
       <c r="D11" t="n">
-        <v>70885.35000000001</v>
+        <v>121716.35</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>16.3%</t>
+          <t>26.9%</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>8999.98</v>
+        <v>19399.98</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>15.9%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>61885.37000000001</v>
+        <v>102316.37</v>
       </c>
       <c r="I11" t="n">
-        <v>13495</v>
+        <v>17528</v>
       </c>
       <c r="J11" t="n">
-        <v>48180</v>
+        <v>84578</v>
       </c>
       <c r="K11" t="n">
-        <v>47097</v>
+        <v>74932</v>
       </c>
     </row>
     <row r="12">
@@ -918,11 +918,11 @@
         <v>400000</v>
       </c>
       <c r="D12" t="n">
-        <v>129637</v>
+        <v>150140</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -934,16 +934,16 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>129609</v>
+        <v>150112</v>
       </c>
       <c r="I12" t="n">
-        <v>41741</v>
+        <v>42244</v>
       </c>
       <c r="J12" t="n">
-        <v>87868</v>
+        <v>107868</v>
       </c>
       <c r="K12" t="n">
-        <v>4207</v>
+        <v>4312</v>
       </c>
     </row>
     <row r="13">
@@ -961,32 +961,32 @@
         <v>800000</v>
       </c>
       <c r="D13" t="n">
-        <v>130905.38</v>
+        <v>147703.18</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>15.2%</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>24389.67</v>
+        <v>25908.67</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>106515.71</v>
+        <v>121794.51</v>
       </c>
       <c r="I13" t="n">
-        <v>9652</v>
+        <v>10349</v>
       </c>
       <c r="J13" t="n">
-        <v>90229</v>
+        <v>104629</v>
       </c>
       <c r="K13" t="n">
-        <v>-4476</v>
+        <v>-3995</v>
       </c>
     </row>
     <row r="14">
@@ -1004,32 +1004,32 @@
         <v>800000</v>
       </c>
       <c r="D14" t="n">
-        <v>88341.3</v>
+        <v>101087.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>5000</v>
+        <v>14866</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>5.7%</t>
+          <t>14.7%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>83341.3</v>
+        <v>86221.2</v>
       </c>
       <c r="I14" t="n">
-        <v>29382</v>
+        <v>29121</v>
       </c>
       <c r="J14" t="n">
-        <v>48528</v>
+        <v>49824</v>
       </c>
       <c r="K14" t="n">
-        <v>13457</v>
+        <v>15041</v>
       </c>
     </row>
     <row r="15">
@@ -1055,24 +1055,24 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>77013</v>
+        <v>76994</v>
       </c>
       <c r="I15" t="n">
-        <v>442</v>
+        <v>423</v>
       </c>
       <c r="J15" t="n">
         <v>76571</v>
       </c>
       <c r="K15" t="n">
-        <v>27421</v>
+        <v>27402</v>
       </c>
     </row>
     <row r="16">
@@ -1090,7 +1090,7 @@
         <v>400000</v>
       </c>
       <c r="D16" t="n">
-        <v>66672</v>
+        <v>66691</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1106,16 +1106,16 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>66274</v>
+        <v>66293</v>
       </c>
       <c r="I16" t="n">
-        <v>12078</v>
+        <v>12097</v>
       </c>
       <c r="J16" t="n">
         <v>54196</v>
       </c>
       <c r="K16" t="n">
-        <v>86</v>
+        <v>105</v>
       </c>
     </row>
     <row r="17">
@@ -1133,32 +1133,32 @@
         <v>700000</v>
       </c>
       <c r="D17" t="n">
-        <v>151067.6</v>
+        <v>168196.38</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>15.9%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>40077</v>
+        <v>40058</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>23.8%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>110990.6</v>
+        <v>128138.38</v>
       </c>
       <c r="I17" t="n">
-        <v>1428</v>
+        <v>1644</v>
       </c>
       <c r="J17" t="n">
-        <v>108090</v>
+        <v>121284</v>
       </c>
       <c r="K17" t="n">
-        <v>-28093</v>
+        <v>-23741</v>
       </c>
     </row>
     <row r="18">
@@ -1176,32 +1176,32 @@
         <v>900000</v>
       </c>
       <c r="D18" t="n">
-        <v>244813.14</v>
+        <v>253557.14</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>27.2%</t>
+          <t>26.0%</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>28</v>
+        <v>19666</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>244785.14</v>
+        <v>233891.14</v>
       </c>
       <c r="I18" t="n">
-        <v>82196</v>
+        <v>84302</v>
       </c>
       <c r="J18" t="n">
-        <v>162589</v>
+        <v>149589</v>
       </c>
       <c r="K18" t="n">
-        <v>125991</v>
+        <v>134299</v>
       </c>
     </row>
     <row r="19">
@@ -1219,11 +1219,11 @@
         <v>900000</v>
       </c>
       <c r="D19" t="n">
-        <v>98055.08</v>
+        <v>103479.08</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -1235,16 +1235,16 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>97846.08</v>
+        <v>103270.08</v>
       </c>
       <c r="I19" t="n">
-        <v>10351</v>
+        <v>10370</v>
       </c>
       <c r="J19" t="n">
-        <v>84392</v>
+        <v>89492</v>
       </c>
       <c r="K19" t="n">
-        <v>19960</v>
+        <v>20284</v>
       </c>
     </row>
     <row r="20">
@@ -1262,32 +1262,32 @@
         <v>700000</v>
       </c>
       <c r="D20" t="n">
-        <v>151488.9</v>
+        <v>180959.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>16.1%</t>
+          <t>20.3%</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>38547</v>
+        <v>38661</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>25.4%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>112941.9</v>
+        <v>142298.9</v>
       </c>
       <c r="I20" t="n">
-        <v>66873</v>
+        <v>75434</v>
       </c>
       <c r="J20" t="n">
-        <v>46068</v>
+        <v>66864</v>
       </c>
       <c r="K20" t="n">
-        <v>15253</v>
+        <v>15804</v>
       </c>
     </row>
   </sheetData>

--- a/导出_按分组.xlsx
+++ b/导出_按分组.xlsx
@@ -488,32 +488,32 @@
         <v>760000</v>
       </c>
       <c r="D2" t="n">
-        <v>186408</v>
+        <v>187351</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>19.6%</t>
+          <t>19.0%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>37448</v>
+        <v>42656</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>20.1%</t>
+          <t>22.8%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>148960</v>
+        <v>144695</v>
       </c>
       <c r="I2" t="n">
-        <v>147942</v>
+        <v>143677</v>
       </c>
       <c r="J2" t="n">
         <v>1018</v>
       </c>
       <c r="K2" t="n">
-        <v>138960</v>
+        <v>134695</v>
       </c>
     </row>
     <row r="3">
@@ -539,18 +539,18 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2618</v>
+        <v>12618</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>112.5%</t>
+          <t>542.2%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>-291</v>
+        <v>-10291</v>
       </c>
       <c r="I3" t="n">
-        <v>-426</v>
+        <v>-10426</v>
       </c>
       <c r="J3" t="n">
         <v>135</v>
@@ -574,32 +574,32 @@
         <v>760000</v>
       </c>
       <c r="D4" t="n">
-        <v>233179.07</v>
+        <v>258327.12</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>20.5%</t>
+          <t>23.4%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>77711</v>
+        <v>80315</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>31.1%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>155468.07</v>
+        <v>178012.12</v>
       </c>
       <c r="I4" t="n">
-        <v>163347</v>
+        <v>184352</v>
       </c>
       <c r="J4" t="n">
-        <v>-7879</v>
+        <v>-6340</v>
       </c>
       <c r="K4" t="n">
-        <v>163576</v>
+        <v>187722</v>
       </c>
     </row>
     <row r="5">
@@ -617,32 +617,32 @@
         <v>520000</v>
       </c>
       <c r="D5" t="n">
-        <v>83693</v>
+        <v>82312</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-7.6%</t>
+          <t>-7.8%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>123031.9</v>
+        <v>123050.9</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>147.0%</t>
+          <t>149.5%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>-39338.89999999999</v>
+        <v>-40738.89999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>-40726</v>
+        <v>-42126</v>
       </c>
       <c r="J5" t="n">
         <v>1388</v>
       </c>
       <c r="K5" t="n">
-        <v>-39338</v>
+        <v>-40738</v>
       </c>
     </row>
     <row r="6">
@@ -660,32 +660,32 @@
         <v>600000</v>
       </c>
       <c r="D6" t="n">
-        <v>177719.46</v>
+        <v>214764.46</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>25.7%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>23311.9</v>
+        <v>27444.9</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>13.1%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>154407.56</v>
+        <v>187319.56</v>
       </c>
       <c r="I6" t="n">
-        <v>150588</v>
+        <v>183500</v>
       </c>
       <c r="J6" t="n">
         <v>3819</v>
       </c>
       <c r="K6" t="n">
-        <v>119611</v>
+        <v>132523</v>
       </c>
     </row>
     <row r="7">
@@ -703,32 +703,32 @@
         <v>360000</v>
       </c>
       <c r="D7" t="n">
-        <v>124591</v>
+        <v>176122</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>28.4%</t>
+          <t>42.7%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>22394</v>
+        <v>22479</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>18.0%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>102197</v>
+        <v>153643</v>
       </c>
       <c r="I7" t="n">
-        <v>72378</v>
+        <v>111824</v>
       </c>
       <c r="J7" t="n">
-        <v>29819</v>
+        <v>41819</v>
       </c>
       <c r="K7" t="n">
-        <v>60099</v>
+        <v>72725</v>
       </c>
     </row>
     <row r="8">
@@ -746,32 +746,32 @@
         <v>640000</v>
       </c>
       <c r="D8" t="n">
-        <v>183275.42</v>
+        <v>191840.62</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>24.3%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>27482</v>
+        <v>37643</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>19.6%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>155793.42</v>
+        <v>154197.62</v>
       </c>
       <c r="I8" t="n">
-        <v>155456</v>
+        <v>153860</v>
       </c>
       <c r="J8" t="n">
         <v>337</v>
       </c>
       <c r="K8" t="n">
-        <v>135793</v>
+        <v>143799</v>
       </c>
     </row>
     <row r="9">
@@ -789,11 +789,11 @@
         <v>1120000</v>
       </c>
       <c r="D9" t="n">
-        <v>391691.36</v>
+        <v>435931.36</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>22.7%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -801,20 +801,20 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>254491.36</v>
+        <v>298731.36</v>
       </c>
       <c r="I9" t="n">
-        <v>169331</v>
+        <v>213571</v>
       </c>
       <c r="J9" t="n">
         <v>85160</v>
       </c>
       <c r="K9" t="n">
-        <v>172871</v>
+        <v>179471</v>
       </c>
     </row>
     <row r="10">
@@ -832,11 +832,11 @@
         <v>2000000</v>
       </c>
       <c r="D10" t="n">
-        <v>475597.6</v>
+        <v>555659.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>23.8%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -848,16 +848,16 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>475597.6</v>
+        <v>555659.6</v>
       </c>
       <c r="I10" t="n">
-        <v>172758</v>
+        <v>219995</v>
       </c>
       <c r="J10" t="n">
-        <v>302839</v>
+        <v>335664</v>
       </c>
       <c r="K10" t="n">
-        <v>435199</v>
+        <v>505261</v>
       </c>
     </row>
     <row r="11">
@@ -875,11 +875,11 @@
         <v>380000</v>
       </c>
       <c r="D11" t="n">
-        <v>121716.35</v>
+        <v>142633.35</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -887,20 +887,20 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>15.9%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>102316.37</v>
+        <v>123233.37</v>
       </c>
       <c r="I11" t="n">
-        <v>17528</v>
+        <v>18047</v>
       </c>
       <c r="J11" t="n">
-        <v>84578</v>
+        <v>104976</v>
       </c>
       <c r="K11" t="n">
-        <v>74932</v>
+        <v>75451</v>
       </c>
     </row>
     <row r="12">
@@ -918,32 +918,32 @@
         <v>400000</v>
       </c>
       <c r="D12" t="n">
-        <v>150140</v>
+        <v>150178</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>28</v>
+        <v>10028</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>150112</v>
+        <v>140150</v>
       </c>
       <c r="I12" t="n">
-        <v>42244</v>
+        <v>42282</v>
       </c>
       <c r="J12" t="n">
-        <v>107868</v>
+        <v>97868</v>
       </c>
       <c r="K12" t="n">
-        <v>4312</v>
+        <v>4350</v>
       </c>
     </row>
     <row r="13">
@@ -961,11 +961,11 @@
         <v>800000</v>
       </c>
       <c r="D13" t="n">
-        <v>147703.18</v>
+        <v>184996.18</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>15.2%</t>
+          <t>19.9%</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -973,20 +973,20 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>17.5%</t>
+          <t>14.0%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>121794.51</v>
+        <v>159087.51</v>
       </c>
       <c r="I13" t="n">
-        <v>10349</v>
+        <v>16444</v>
       </c>
       <c r="J13" t="n">
-        <v>104629</v>
+        <v>135827</v>
       </c>
       <c r="K13" t="n">
-        <v>-3995</v>
+        <v>-3496</v>
       </c>
     </row>
     <row r="14">
@@ -1051,25 +1051,25 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>27.0%</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>57</v>
+        <v>6857</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>76994</v>
+        <v>70194</v>
       </c>
       <c r="I15" t="n">
         <v>423</v>
       </c>
       <c r="J15" t="n">
-        <v>76571</v>
+        <v>69771</v>
       </c>
       <c r="K15" t="n">
         <v>27402</v>
@@ -1090,11 +1090,11 @@
         <v>400000</v>
       </c>
       <c r="D16" t="n">
-        <v>66691</v>
+        <v>106279</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>16.6%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -1102,20 +1102,20 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>66293</v>
+        <v>105881</v>
       </c>
       <c r="I16" t="n">
         <v>12097</v>
       </c>
       <c r="J16" t="n">
-        <v>54196</v>
+        <v>93784</v>
       </c>
       <c r="K16" t="n">
-        <v>105</v>
+        <v>39693</v>
       </c>
     </row>
     <row r="17">
@@ -1133,11 +1133,11 @@
         <v>700000</v>
       </c>
       <c r="D17" t="n">
-        <v>168196.38</v>
+        <v>192514.4</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>21.8%</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -1145,20 +1145,20 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>23.8%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>128138.38</v>
+        <v>152456.4</v>
       </c>
       <c r="I17" t="n">
-        <v>1644</v>
+        <v>2042</v>
       </c>
       <c r="J17" t="n">
-        <v>121284</v>
+        <v>131682</v>
       </c>
       <c r="K17" t="n">
-        <v>-23741</v>
+        <v>-10219</v>
       </c>
     </row>
     <row r="18">
@@ -1176,11 +1176,11 @@
         <v>900000</v>
       </c>
       <c r="D18" t="n">
-        <v>253557.14</v>
+        <v>261576.14</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>26.0%</t>
+          <t>26.9%</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -1188,20 +1188,20 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>233891.14</v>
+        <v>241910.14</v>
       </c>
       <c r="I18" t="n">
-        <v>84302</v>
+        <v>91923</v>
       </c>
       <c r="J18" t="n">
-        <v>149589</v>
+        <v>149987</v>
       </c>
       <c r="K18" t="n">
-        <v>134299</v>
+        <v>134318</v>
       </c>
     </row>
     <row r="19">
@@ -1219,11 +1219,11 @@
         <v>900000</v>
       </c>
       <c r="D19" t="n">
-        <v>103479.08</v>
+        <v>113505.08</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>12.6%</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -1235,16 +1235,16 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>103270.08</v>
+        <v>113296.08</v>
       </c>
       <c r="I19" t="n">
-        <v>10370</v>
+        <v>12896</v>
       </c>
       <c r="J19" t="n">
-        <v>89492</v>
+        <v>96992</v>
       </c>
       <c r="K19" t="n">
-        <v>20284</v>
+        <v>22810</v>
       </c>
     </row>
     <row r="20">
@@ -1262,32 +1262,32 @@
         <v>700000</v>
       </c>
       <c r="D20" t="n">
-        <v>180959.9</v>
+        <v>212068.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>20.3%</t>
+          <t>24.8%</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>38661</v>
+        <v>38699</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>142298.9</v>
+        <v>173369.9</v>
       </c>
       <c r="I20" t="n">
-        <v>75434</v>
+        <v>82105</v>
       </c>
       <c r="J20" t="n">
-        <v>66864</v>
+        <v>91264</v>
       </c>
       <c r="K20" t="n">
-        <v>15804</v>
+        <v>31875</v>
       </c>
     </row>
   </sheetData>

--- a/导出_按分组.xlsx
+++ b/导出_按分组.xlsx
@@ -488,32 +488,32 @@
         <v>760000</v>
       </c>
       <c r="D2" t="n">
-        <v>187351</v>
+        <v>226185</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>19.0%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>42656</v>
+        <v>48873.16</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>22.8%</t>
+          <t>21.6%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>144695</v>
+        <v>177311.84</v>
       </c>
       <c r="I2" t="n">
-        <v>143677</v>
+        <v>176293</v>
       </c>
       <c r="J2" t="n">
         <v>1018</v>
       </c>
       <c r="K2" t="n">
-        <v>134695</v>
+        <v>167311</v>
       </c>
     </row>
     <row r="3">
@@ -531,7 +531,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>2327</v>
+        <v>2374</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -539,24 +539,24 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>12618</v>
+        <v>17617</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>542.2%</t>
+          <t>742.1%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>-10291</v>
+        <v>-15243</v>
       </c>
       <c r="I3" t="n">
-        <v>-10426</v>
+        <v>-15378</v>
       </c>
       <c r="J3" t="n">
         <v>135</v>
       </c>
       <c r="K3" t="n">
-        <v>-291</v>
+        <v>-5243</v>
       </c>
     </row>
     <row r="4">
@@ -574,32 +574,32 @@
         <v>760000</v>
       </c>
       <c r="D4" t="n">
-        <v>258327.12</v>
+        <v>283989.12</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>26.1%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>80315</v>
+        <v>85383</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>31.1%</t>
+          <t>30.1%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>178012.12</v>
+        <v>198606.12</v>
       </c>
       <c r="I4" t="n">
-        <v>184352</v>
+        <v>204946</v>
       </c>
       <c r="J4" t="n">
         <v>-6340</v>
       </c>
       <c r="K4" t="n">
-        <v>187722</v>
+        <v>207718</v>
       </c>
     </row>
     <row r="5">
@@ -617,32 +617,32 @@
         <v>520000</v>
       </c>
       <c r="D5" t="n">
-        <v>82312</v>
+        <v>88050</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-7.8%</t>
+          <t>-6.7%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>123050.9</v>
+        <v>123069.9</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>149.5%</t>
+          <t>139.8%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>-40738.89999999999</v>
+        <v>-35019.89999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>-42126</v>
+        <v>-36407</v>
       </c>
       <c r="J5" t="n">
         <v>1388</v>
       </c>
       <c r="K5" t="n">
-        <v>-40738</v>
+        <v>-35019</v>
       </c>
     </row>
     <row r="6">
@@ -660,32 +660,32 @@
         <v>600000</v>
       </c>
       <c r="D6" t="n">
-        <v>214764.46</v>
+        <v>282837.46</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>41.8%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>27444.9</v>
+        <v>31751.9</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>187319.56</v>
+        <v>251085.56</v>
       </c>
       <c r="I6" t="n">
-        <v>183500</v>
+        <v>247266</v>
       </c>
       <c r="J6" t="n">
         <v>3819</v>
       </c>
       <c r="K6" t="n">
-        <v>132523</v>
+        <v>196289</v>
       </c>
     </row>
     <row r="7">
@@ -703,32 +703,32 @@
         <v>360000</v>
       </c>
       <c r="D7" t="n">
-        <v>176122</v>
+        <v>204887</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>42.7%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>22479</v>
+        <v>31890</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>153643</v>
+        <v>172997</v>
       </c>
       <c r="I7" t="n">
-        <v>111824</v>
+        <v>143178</v>
       </c>
       <c r="J7" t="n">
-        <v>41819</v>
+        <v>29819</v>
       </c>
       <c r="K7" t="n">
-        <v>72725</v>
+        <v>81083</v>
       </c>
     </row>
     <row r="8">
@@ -746,32 +746,32 @@
         <v>640000</v>
       </c>
       <c r="D8" t="n">
-        <v>191840.62</v>
+        <v>194751.62</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>19.2%</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>37643</v>
+        <v>71584</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>19.6%</t>
+          <t>36.8%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>154197.62</v>
+        <v>123167.62</v>
       </c>
       <c r="I8" t="n">
-        <v>153860</v>
+        <v>152130</v>
       </c>
       <c r="J8" t="n">
-        <v>337</v>
+        <v>-28963</v>
       </c>
       <c r="K8" t="n">
-        <v>143799</v>
+        <v>112769</v>
       </c>
     </row>
     <row r="9">
@@ -789,32 +789,32 @@
         <v>1120000</v>
       </c>
       <c r="D9" t="n">
-        <v>435931.36</v>
+        <v>467449.36</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>29.3%</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>137200</v>
+        <v>139000</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>29.7%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>298731.36</v>
+        <v>328449.36</v>
       </c>
       <c r="I9" t="n">
-        <v>213571</v>
+        <v>222169</v>
       </c>
       <c r="J9" t="n">
-        <v>85160</v>
+        <v>106280</v>
       </c>
       <c r="K9" t="n">
-        <v>179471</v>
+        <v>183971</v>
       </c>
     </row>
     <row r="10">
@@ -832,11 +832,11 @@
         <v>2000000</v>
       </c>
       <c r="D10" t="n">
-        <v>555659.6</v>
+        <v>558851.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>27.9%</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -848,16 +848,16 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>555659.6</v>
+        <v>558851.6</v>
       </c>
       <c r="I10" t="n">
-        <v>219995</v>
+        <v>220995</v>
       </c>
       <c r="J10" t="n">
-        <v>335664</v>
+        <v>337856</v>
       </c>
       <c r="K10" t="n">
-        <v>505261</v>
+        <v>508453</v>
       </c>
     </row>
     <row r="11">
@@ -875,32 +875,32 @@
         <v>380000</v>
       </c>
       <c r="D11" t="n">
-        <v>142633.35</v>
+        <v>143231.35</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>30.7%</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>19399.98</v>
+        <v>26399.98</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>18.4%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>123233.37</v>
+        <v>116831.37</v>
       </c>
       <c r="I11" t="n">
-        <v>18047</v>
+        <v>18445</v>
       </c>
       <c r="J11" t="n">
-        <v>104976</v>
+        <v>98176</v>
       </c>
       <c r="K11" t="n">
-        <v>75451</v>
+        <v>75651</v>
       </c>
     </row>
     <row r="12">
@@ -918,11 +918,11 @@
         <v>400000</v>
       </c>
       <c r="D12" t="n">
-        <v>150178</v>
+        <v>201094</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>47.8%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -930,20 +930,20 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>5.0%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>140150</v>
+        <v>191066</v>
       </c>
       <c r="I12" t="n">
-        <v>42282</v>
+        <v>52699</v>
       </c>
       <c r="J12" t="n">
-        <v>97868</v>
+        <v>138367</v>
       </c>
       <c r="K12" t="n">
-        <v>4350</v>
+        <v>4868</v>
       </c>
     </row>
     <row r="13">
@@ -961,11 +961,11 @@
         <v>800000</v>
       </c>
       <c r="D13" t="n">
-        <v>184996.18</v>
+        <v>211257.18</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>19.9%</t>
+          <t>23.2%</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -973,20 +973,20 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>159087.51</v>
+        <v>185348.51</v>
       </c>
       <c r="I13" t="n">
-        <v>16444</v>
+        <v>17307</v>
       </c>
       <c r="J13" t="n">
-        <v>135827</v>
+        <v>161225</v>
       </c>
       <c r="K13" t="n">
-        <v>-3496</v>
+        <v>-3429</v>
       </c>
     </row>
     <row r="14">
@@ -1004,11 +1004,11 @@
         <v>800000</v>
       </c>
       <c r="D14" t="n">
-        <v>101087.2</v>
+        <v>123464.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -1016,20 +1016,20 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>86221.2</v>
+        <v>108598.2</v>
       </c>
       <c r="I14" t="n">
-        <v>29121</v>
+        <v>49420</v>
       </c>
       <c r="J14" t="n">
-        <v>49824</v>
+        <v>51902</v>
       </c>
       <c r="K14" t="n">
-        <v>15041</v>
+        <v>17020</v>
       </c>
     </row>
     <row r="15">
@@ -1047,32 +1047,32 @@
         <v>260000</v>
       </c>
       <c r="D15" t="n">
-        <v>77051</v>
+        <v>77070</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>27.0%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>6857</v>
+        <v>15857</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>70194</v>
+        <v>61213</v>
       </c>
       <c r="I15" t="n">
-        <v>423</v>
+        <v>442</v>
       </c>
       <c r="J15" t="n">
-        <v>69771</v>
+        <v>60771</v>
       </c>
       <c r="K15" t="n">
-        <v>27402</v>
+        <v>27421</v>
       </c>
     </row>
     <row r="16">
@@ -1090,11 +1090,11 @@
         <v>400000</v>
       </c>
       <c r="D16" t="n">
-        <v>106279</v>
+        <v>107075</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -1106,13 +1106,13 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>105881</v>
+        <v>106677</v>
       </c>
       <c r="I16" t="n">
-        <v>12097</v>
+        <v>12495</v>
       </c>
       <c r="J16" t="n">
-        <v>93784</v>
+        <v>94182</v>
       </c>
       <c r="K16" t="n">
         <v>39693</v>
@@ -1133,32 +1133,32 @@
         <v>700000</v>
       </c>
       <c r="D17" t="n">
-        <v>192514.4</v>
+        <v>192525.4</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>21.8%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>40058</v>
+        <v>46658</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>24.2%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>152456.4</v>
+        <v>145867.4</v>
       </c>
       <c r="I17" t="n">
-        <v>2042</v>
+        <v>2053</v>
       </c>
       <c r="J17" t="n">
-        <v>131682</v>
+        <v>125082</v>
       </c>
       <c r="K17" t="n">
-        <v>-10219</v>
+        <v>-16808</v>
       </c>
     </row>
     <row r="18">
@@ -1176,11 +1176,11 @@
         <v>900000</v>
       </c>
       <c r="D18" t="n">
-        <v>261576.14</v>
+        <v>285737.9</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -1188,20 +1188,20 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>241910.14</v>
+        <v>266071.9</v>
       </c>
       <c r="I18" t="n">
-        <v>91923</v>
+        <v>99340</v>
       </c>
       <c r="J18" t="n">
-        <v>149987</v>
+        <v>166731</v>
       </c>
       <c r="K18" t="n">
-        <v>134318</v>
+        <v>148479</v>
       </c>
     </row>
     <row r="19">
@@ -1219,11 +1219,11 @@
         <v>900000</v>
       </c>
       <c r="D19" t="n">
-        <v>113505.08</v>
+        <v>114093.06</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>12.6%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -1235,16 +1235,16 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>113296.08</v>
+        <v>113884.06</v>
       </c>
       <c r="I19" t="n">
-        <v>12896</v>
+        <v>10376</v>
       </c>
       <c r="J19" t="n">
-        <v>96992</v>
+        <v>100092</v>
       </c>
       <c r="K19" t="n">
-        <v>22810</v>
+        <v>20298</v>
       </c>
     </row>
     <row r="20">
@@ -1262,32 +1262,32 @@
         <v>700000</v>
       </c>
       <c r="D20" t="n">
-        <v>212068.9</v>
+        <v>228790.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>24.8%</t>
+          <t>26.9%</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>38699</v>
+        <v>40737</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>173369.9</v>
+        <v>188053.9</v>
       </c>
       <c r="I20" t="n">
-        <v>82105</v>
+        <v>82993</v>
       </c>
       <c r="J20" t="n">
-        <v>91264</v>
+        <v>105060</v>
       </c>
       <c r="K20" t="n">
-        <v>31875</v>
+        <v>31967</v>
       </c>
     </row>
   </sheetData>

--- a/导出_按分组.xlsx
+++ b/导出_按分组.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -832,7 +832,7 @@
         <v>2000000</v>
       </c>
       <c r="D10" t="n">
-        <v>558851.6</v>
+        <v>559150.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -840,11 +840,11 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>299</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -1219,7 +1219,7 @@
         <v>900000</v>
       </c>
       <c r="D19" t="n">
-        <v>114093.06</v>
+        <v>113893.06</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1227,11 +1227,11 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>209</v>
+        <v>9</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H19" t="n">
@@ -1288,6 +1288,49 @@
       </c>
       <c r="K20" t="n">
         <v>31967</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>门店</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" t="n">
+        <v>14920</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>13111</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>87.9%</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>1809</v>
+      </c>
+      <c r="I21" t="n">
+        <v>-11391</v>
+      </c>
+      <c r="J21" t="n">
+        <v>13200</v>
+      </c>
+      <c r="K21" t="n">
+        <v>-770</v>
       </c>
     </row>
   </sheetData>
